--- a/408/OS/2024/ModularAutomation/reports/testcases.xlsx
+++ b/408/OS/2024/ModularAutomation/reports/testcases.xlsx
@@ -15,7 +15,7 @@
     <sheet name="#TEMP" sheetId="4" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'#TEMP'!$A$1:$D$92</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'#TEMP'!$A$1:$D$96</definedName>
   </definedNames>
   <calcPr calcId="152511"/>
   <extLst>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="387" uniqueCount="127">
   <si>
     <t>接口</t>
   </si>
@@ -77,280 +77,72 @@
     <t>cmdArr</t>
   </si>
   <si>
-    <t>{"device":"pc","params":[{"method":"devConfig.set","params":{"module":"kvNavDev","noParse":false,"async":null,"remoteIp":false,"data":{"start":"ca_get_ip_range'flagthn'"}}}]}</t>
-  </si>
-  <si>
     <t>#results↓</t>
   </si>
   <si>
     <t>devConfig.get</t>
   </si>
   <si>
-    <t>{"module":"stp","noParse":true,"async":null,"remoteIp":"127.0.0.1","remotePwd":"ssssss","cur":"1212","device":"pc","data":{"'flagthn'":"sdf"}}</t>
-  </si>
-  <si>
     <t>devSta.set</t>
   </si>
   <si>
-    <t>{"module":"enetCap","noParse":true,"async":null,"remoteIp":false,"data":{"caps":"flagthn","module":"..///.//..//.///../////../root/test1111"},"device":"pc"}</t>
-  </si>
-  <si>
     <t>devConfig.set</t>
   </si>
   <si>
-    <t>{"module":"kvNavDev","noParse":true,"async":null,"remoteIp":false,"data":{"sta":"'flagthn'"},"device":"pc"}</t>
-  </si>
-  <si>
-    <t>{"module":"repeater_hostrouter","noParse":true,"async":null,"remoteIp":false,"data":{"repeater":{"ssid":"123","channel":"flagthn",
-"enable":"true","bssid":"ssdf"},"repeater_5g":"1"},"device":"pc"}</t>
-  </si>
-  <si>
-    <t>{"module":"meshpair","noParse":true,"async":null,"remoteIp":false,"data":{"choicepair":"'flagthn # 11:11:22:22:22:22"},"device":"pc"}</t>
-  </si>
-  <si>
     <t>devSta.get</t>
   </si>
   <si>
-    <t>{"module":"host_access_delay","noParse":false,"async":null,"remoteIp":false,"data":{"hostname":"www.baidu.com'flagthn'"},"device":"pc"}</t>
-  </si>
-  <si>
     <t>/cgi-bin/luci/api/auth</t>
   </si>
   <si>
     <t>merge</t>
   </si>
   <si>
-    <t>{"back": "1","data": {"cmd": "'flagthn'"}}</t>
-  </si>
-  <si>
     <t>/cgi-bin/luci/api/common</t>
   </si>
   <si>
     <t>allConf</t>
   </si>
   <si>
-    <t>{"search":"'flagthn"}</t>
-  </si>
-  <si>
     <t>setSysTime</t>
   </si>
   <si>
-    <t>{"time":"1","force":"'flagthn'"}</t>
-  </si>
-  <si>
     <t>acConfig.set</t>
   </si>
   <si>
-    <t>{"module":"dummy","noParse":false,"async":null,"remoteIp":false,"data":{"cmd":"dummy'flagthn'"},"device":"pc"}</t>
-  </si>
-  <si>
-    <t>{"module":"'flagthn'","data":{"name":"hah","sn":["G1QH1J5000534"]},"device":"pc"}</t>
-  </si>
-  <si>
     <t>/cgi-bin/luci/api/diagnose</t>
   </si>
   <si>
     <t>nslookup</t>
   </si>
   <si>
-    <t>{"count":"1","size":"1","target":"baidu.comflagthn"}</t>
-  </si>
-  <si>
     <t>ping</t>
   </si>
   <si>
     <t>traceroute</t>
   </si>
   <si>
-    <t>{"search":"'flagthn'"}</t>
-  </si>
-  <si>
-    <t>{"type":"3","count":"4","size":"64","ttl":"20","target":"www.google.com flagthn","ipType":"v4","dns":"8.8.8.8 flagthn"}</t>
-  </si>
-  <si>
     <t>runPackDiagnose</t>
   </si>
   <si>
-    <t>{"device":"pc","params":[{"method":"devSta.set","params":{"module":"enetCap","noParse":false,"async":null,"remoteIp":false,"data":{"module":"s'flagthn'","caps":"s","obj":{"rg_device":{"wlan_enet_cap":{"band_1":["auth_bitmap"]}}},"method":"and","sn":[],"groupId":"0"}}},{"method":"devSta.del","params":{"module":"enetCap","noParse":false,"async":null,"remoteIp":false,"data":{"module":"s'flagthn'","caps":"","obj":{"rg_device":{"wlan_enet_cap":{"band_2":["auth_bitmap"]}}},"method":"and","sn":[],"groupId":"0"}}}]}</t>
-  </si>
-  <si>
     <t>devConfig.add</t>
   </si>
   <si>
-    <t>{"iface":"flagthn","protocal":"flagthn","size":"2","ip":"flagthn","package":"flagthn"}</t>
-  </si>
-  <si>
     <t>/cgi-bin/luci/api/system</t>
   </si>
   <si>
     <t>startCheck</t>
   </si>
   <si>
-    <t>{"isLanPing":"flagthn","isWanPing":"flagthn"}</t>
-  </si>
-  <si>
-    <t>{"module":"dns_proxy","noParse":false,"async":null,"remoteIp":false,"data":{"enable":"1","dnsIp":"114.114.114.114'flagthn'","version":"1.0.0"},"device":"pc"}</t>
-  </si>
-  <si>
-    <t>{"module":"ntpserver","noParse":false,"async":null,"remoteIp":false,"data":{"ntpserver":["0.cn.pool.ntp.org'flagthn'","1.cn.pool.ntp.org","cn.pool.ntp.org","pool.ntp.org","asia.pool.ntp.org","europe.pool.ntp.org","ntp1.aliyun.com"]},"device":"pc"}</t>
-  </si>
-  <si>
-    <t>{"module":"dhcp_static","noParse":false,"async":null,"remoteIp":false,"data":{"list":[{"ipaddr":"192.168.110.161';flagthn;'","macaddr":"f8:e4:3b:60:bb:f6"}]},"device":"pc"}</t>
-  </si>
-  <si>
-    <t>{u"noParse": False, u"module": u"dhcp_static", u"remoteIp": False, u"device": u"pc", u"async": None, u"data": {u"list": [{u"macaddr": u"f8:e4:3b:60:bb:f6", u"ipaddr": u"192.168.110.161'flagthn'"}]}}</t>
-  </si>
-  <si>
-    <t>{u"noParse": False, u"module": u"dhcp_lease", u"remoteIp": False, u"device": u"pc", u"async": None, u"data": {u"index": 1, u"macaddr": u"11111'flagthn'", u"size": 10}}</t>
-  </si>
-  <si>
-    <t>{u"noParse": True, u"module": u"net_arp", u"remoteIp": False, u"device": u"pc", u"async": None, u"data": {u"index": 1, u"search": u"11111'flagthn'", u"size": 10}}</t>
-  </si>
-  <si>
-    <t>{u"noParse": False, u"module": u"mac_filter", u"remoteIp": False, u"device": u"pc", u"async": None, u"data": {u"macList": [{u"comment": u"", u"mac": u"f8:e4:3b:60:bb:f6'flagthn'"}]}}</t>
-  </si>
-  <si>
-    <t>{u"noParse": False, u"module": u"content_audit", u"remoteIp": False, u"device": u"pc", u"async": True, u"data": {u"comment": u"", u"enable": u"1", u"ip_slots": [u"1.1.1.1'flagthn'"], u"ip_group": u"", u"tr_slots": {}, u"applist": [u"\u793e\u4ea4\u8f6f\u4ef6"], u"func": u"ca_set_app_policy", u"policy": u"", u"tr_group": u"\u6240\u6709\u65f6\u6bb5", u"time_mode": u"calendar", u"user_group_list": []}}</t>
-  </si>
-  <si>
-    <t>{u"noParse": False, u"module": u"content_audit", u"remoteIp": False, u"device": u"pc", u"async": True, u"data": {u"comment": u"", u"enable": u"1", u"ip_slots": [u"1.1.1.1'flagthn'"], u"ip_group": u"", u"tr_slots": {}, u"action": u"deny", u"func": u"ca_set_url_policy", u"url_class": [u"games"], u"policy": u"", u"tr_group": u"\u6240\u6709\u65f6\u6bb5", u"time_mode": u"calendar", u"user_group_list": []}}</t>
-  </si>
-  <si>
-    <t>{u"noParse": False, u"module": u"content_audit", u"remoteIp": False, u"device": u"pc", u"async": True, u"data": {u"entry_name": u"", u"url_list": [u"www.baidu.com"], u"alias_name": u"1111'flagthn'", u"func": u"ca_set_url_list"}}</t>
-  </si>
-  <si>
-    <t>{u"noParse": False, u"module": u"content_audit", u"remoteIp": False, u"device": u"pc", u"async": True, u"data": {u"comment": u"", u"model": u"black", u"account": [u"111111"], u"enable": u"1", u"ip_slots": [u"1.1.1.1'flagthn'"], u"ip_group": u"", u"tr_slots": {}, u"func": u"ca_set_im_policy", u"policy": u"", u"tr_group": u"\u6240\u6709\u65f6\u6bb5", u"time_mode": u"calendar", u"user_group_list": []}}</t>
-  </si>
-  <si>
-    <t>{u"device": u"pc", u"params": [{u"params": {u"noParse": False, u"data": {u"p2pSwtich": u"off", u"reserve_switch": u"off", u"up_res_proportion": u"0.2", u"list": [{u"downloadBand": u"1000", u"ifname": u"br-wan", u"enable": u"on", u"uploadBand": u"1000'flagthn'"}], u"wanNum": u"1", u"down_res_proportion": u"0.15", u"version": u"1.0.0", u"tcSwitch": u"on"}, u"remoteIp": False, u"module": u"flowctrl", u"async": None}, u"method": u"devConfig.set"}, {u"params": {u"noParse": False, u"data": {u"p2pSwtich": u"off", u"reserve_switch": u"off", u"up_res_proportion": u"0.2", u"list": [{u"downloadBand": u"1000", u"ifname": u"br-wan", u"enable": u"on", u"uploadBand": u"1000"}], u"wanNum": u"1", u"down_res_proportion": u"0.15", u"version": u"1.0.0", u"tcSwitch": u"on"}, u"remoteIp": False, u"module": u"flowctrl", u"async": None}, u"method": u"devConfig.set"}]}</t>
-  </si>
-  <si>
     <t>devConfig.update</t>
   </si>
   <si>
-    <t>{u"noParse": False, u"module": u"flowctrl_app", u"remoteIp": False, u"device": u"pc", u"async": None, u"data": {u"template": u"home'flagthn'"}}</t>
-  </si>
-  <si>
-    <t>{u"noParse": False, u"module": u"ipsec", u"remoteIp": False, u"device": u"pc", u"async": None, u"data": {u"data": {u"ike_proposal_5": u"md5-3des-dh2", u"ike_proposal_4": u"md5-des-dh1", u"intf_binding": u"AUTO", u"local_id_value": u"", u"lifetime": u"3600", u"connection_type": u"initiator", u"dpd_enable": u"enable", u"ph2_proposal_1": u"esp-sha1-aes128", u"ph2_proposal_2": u"esp-md5-3des", u"ph2_proposal_3": u"---", u"ph2_proposal_4": u"---", u"ph2_proposal_5": u"---", u"remote_id_value": u"", u"remote_gateway": u"192.168.110.11", u"status": u"enable", u"psk": u"111111", u"local_id_type": u"IP_ADDRESS", u"ike_proposal_1": u"sha1-3des-dh1", u"ike_proposal_3": u"sha1-3des-dh2", u"ike_proposal_2": u"sha1-des-dh1", u"local_network": [u"192.168.110.0/24"], u"dpd_interval": u"10", u"remote_network": [u"192.168.112.0/24"], u"exchange_mode": u"main", u"remote_gateway1": u"", u"ikelifetime": u"86400", u"name": u"qqqq'flagthn'", u"pfs": u"none", u"mode": u"tunnel", u"create_by": u"web", u"remote_id_type": u"IP_ADDRESS"}, u"func": u"ipsec_set_cfg", u"op": u"add"}}</t>
-  </si>
-  <si>
-    <t>{u"noParse": False, u"module": u"policy_route", u"remoteIp": False, u"device": u"pc", u"async": None, u"data": {u"list": [{u"intf": u"wan", u"name": u"aaa'flagthn'", u"proto": u"ip", u"sip": u"all", u"enable": u"on", u"dip": u"all"}]}}</t>
-  </si>
-  <si>
-    <t>{u"noParse": False, u"module": u"pppoeserver_global", u"remoteIp": False, u"device": u"pc", u"async": None, u"data": {u"monitor_port": u"", u"pap": u"1", u"mschapv2": u"1", u"first_dns_server": u"", u"idle_time": u"30", u"mschap": u"1", u"max_sessions": u"15", u"localip": u"10.44.66.99'flagthn'", u"state": u"0", u"version": u"1.0.0", u"second_dns_server": u"", u"force_state": u"0", u"max_noreply_lcp": u"10", u"chap": u"1"}}</t>
-  </si>
-  <si>
-    <t>{u"noParse": False, u"module": u"pppoeserver_user", u"remoteIp": False, u"device": u"pc", u"async": None, u"data": {u"ippool_name": u"pppoe_pool", u"enable": u"1", u"name": u"test'flagthn'", u"passwd": u"test", u"dealline": u"", u"note": u"", u"flow_enable": u"0", u"flow_name": u""}}</t>
-  </si>
-  <si>
-    <t>{u"noParse": False, u"module": u"flowctrl_pppoe", u"remoteIp": False, u"device": u"pc", u"async": None, u"data": {u"list": [{u"downRateG": u"", u"comment": u"test'flagthn'", u"intf": u"br-wan", u"enable": u"on", u"allDownRate": u"1", u"upRateG": u"", u"downRate": u"1", u"upRate": u"1", u"mode": u"per_ip", u"allUpRateG": u"1", u"allDownRateG": u"1", u"allUpRate": u"1"}]}}</t>
-  </si>
-  <si>
-    <t>{u"noParse": False, u"module": u"pppoeserver_exceptip", u"remoteIp": False, u"device": u"pc", u"async": None, u"data": {u"start_ip": u"192.1.1.1'flagthn'", u"note": u"", u"state": u"1", u"end_ip": u"192.1.1.12"}}</t>
-  </si>
-  <si>
-    <t>{u"noParse": False, u"module": u"app_auth_macc", u"remoteIp": False, u"device": u"pc", u"async": True, u"data": {u"cfgIdOpt": u"2", u"authType": u"wifidog", u"enable": u"1", u"flowDetectEn": u"1", u"wxRedirect": u"118.31.178.137", u"portalCheck": u"1", u"macByPass": u"1", u"ad_url": u"maccauth.ruijie.com.cn", u"authIpList": [u"1.1.1.1-1.1.1.2'flagthn'"], u"allAuthList": [], u"flowDetectTime": u"15", u"setSsidIpList": []}}</t>
-  </si>
-  <si>
-    <t>{u"noParse": False, u"module": u"guest_auth", u"remoteIp": False, u"device": u"pc", u"async": None, u"data": {u"cfgIdOpt": u"2", u"en": u"1", u"authList": [u"1.1.1.3-1.1.1.3'flagthn'"], u"name": u"user_pwd_auth", u"func": u"user_pwd_cfg"}}</t>
-  </si>
-  <si>
-    <t>{u"noParse": False, u"module": u"guest_auth", u"remoteIp": False, u"device": u"pc", u"async": None, u"data": {u"username": u"test'flagthn'", u"mac_cnt": u"5", u"name": u"", u"func": u"user_pwd_manage", u"password": u"test", u"op": u"add"}}</t>
-  </si>
-  <si>
-    <t>{u"noParse": False, u"module": u"guest_auth", u"remoteIp": False, u"device": u"pc", u"async": None, u"data": {u"en": u"1", u"name": u"qrcode_passive_auth", u"activeAuthIpRange": [u"1.1.1.5'flagthn'"], u"authList": [u"1.1.1.4"], u"func": u"guest_auth_set_qrcode_passive_auth_cfg", u"time": u"0", u"allAuthList": [u"1.1.1.1-1.1.1.2", u"1.1.1.3-1.1.1.3"], u"displaypastext": u" "}}</t>
-  </si>
-  <si>
-    <t>{u"noParse": False, u"module": u"guest_auth", u"remoteIp": False, u"device": u"pc", u"async": None, u"data": {u"qrcodeindex": u"defqrcode", u"en": u"1", u"func": u"guest_auth_set_qrcode_active_auth_cfg", u"name": u"qrcode_active_auth", u"ip": u"10.44.77.253", u"authList": [u"1.1.1.6'flagthn'"], u"scriptpath": u"guest_auth/qrcode_active_auth.lua", u"time": u"0", u"allAuthList": [u"1.1.1.1-1.1.1.2", u"1.1.1.3-1.1.1.3", u"1.1.1.4"], u"displayacttext": u" "}}</t>
-  </si>
-  <si>
-    <t>{u"noParse": False, u"module": u"app_auth_direct_srcip", u"remoteIp": False, u"device": u"pc", u"async": None, u"data": {u"data": [u"1.1.1.1'flagthn'"], u"type": u"srcip"}}</t>
-  </si>
-  <si>
-    <t>{u"noParse": False, u"module": u"ip_connlimit", u"remoteIp": False, u"device": u"pc", u"async": None, u"data": {u"list": [{u"status": u"off", u"information": u"test'flagthn'", u"ipStart": u"1.1.1.2", u"connlimit": u"1000", u"ipEnd": u"1.1.1.3"}]}}</t>
-  </si>
-  <si>
-    <t>{u"noParse": False, u"module": u"port_mapping", u"remoteIp": False, u"device": u"pc", u"async": None, u"data": {u"list": [{u"src": u"wan", u"proto": u"tcp", u"srcPort": u"1", u"destIp": u"192.168.110.12", u"ruleName": u"test'flagthn'", u"srcIp": u"", u"destPort": u"80"}]}}</t>
-  </si>
-  <si>
-    <t>{u"noParse": False, u"module": u"nat_dmz", u"remoteIp": False, u"device": u"pc", u"async": None, u"data": {u"interface": u"wan", u"rule_name": u"test'flagthn'", u"enable": u"1", u"dest_ip": u"1.1.1.1"}}</t>
-  </si>
-  <si>
-    <t>{u"noParse": False, u"module": u"noipdns", u"remoteIp": False, u"device": u"pc", u"async": True, u"data": {u"wan": u"wan", u"hostname": u"", u"user": u"test'flagthn'", u"pass": u"test"}}</t>
-  </si>
-  <si>
-    <t>{u"noParse": False, u"module": u"upnp", u"remoteIp": False, u"device": u"pc", u"async": None, u"data": {u"upnpds": [], u"wan": u"WAN'flagthn'", u"enable_upnp": u"true", u"upnp_line": u"1"}}</t>
-  </si>
-  <si>
-    <t>{u"noParse": False, u"module": u"local_dns_server", u"remoteIp": False, u"device": u"pc", u"async": None, u"data": {u"dns_server": [u"1.1.1.1'flagthn'"]}}</t>
-  </si>
-  <si>
-    <t>{u"noParse": False, u"module": u"network", u"remoteIp": False, u"device": u"pc", u"async": None, u"data": {u"wan": [{u"metric": u"0", u"macaddr": u"10:82:3d:f4:32:a0", u"special_line": u"0", u"proto": u"dhcp"}], u"lan": [{u"macaddr": u"10:82:3d:f4:32:9e", u"leasetime": u"30", u"ipstart": u"192.168.110.1", u"proto": u"static", u"lastaddr": u"192.168.110.1", u"ipaddr": u"192.168.110.1", u"vlanid": u"233", u"ignore": u"0", u"netmask": u"255.255.255.0", u"limit": u"254", u"conflict": u"false"}, {u"macaddr": u"10:82:3D:D5:20:54", u"leasetime": u"480", u"ipstart": u"192.168.12.1", u"lastaddr": u"192.168.12.254", u"hasReturnRouter": False, u"ipaddr": u"192.168.12.1", u"dhcpServerDevice": u"", u"vlanid": u"12", u"ignore": u"0", u"netmask": u"255.255.255.0", u"limit": u"254", u"pool": u"EGW", u"desc": u"22ttttt'flagthn'"}], u"version": u"1.0.0", u"wanNum": u"1", u"lanNum": u"2"}}</t>
-  </si>
-  <si>
-    <t>{u"noParse": False, u"module": u"wireless", u"remoteIp": False, u"device": u"pc", u"async": None, u"data": {u"networkId": u"dev_10:82:3D:F4:32:9E_1680599422", u"ssidList": [{u"ssidEncode": u"utf-8", u"enable": u"true", u"guest": u"false", u"relatedRadio": u"1,2", u"bandSelectEnable": u"false", u"ishidden": u"false", u"roam": u"false", u"encryptionMode": u"open", u"vlanId": u"1", u"ssidName": u"@Ruijie-m329E'flagthn'", u"tmMode": u"def", u"xpress": u"false", u"mode": u"ap", u"tmValue": {u"slot": u"", u"tmngtName": u"\u6240\u6709\u65f6\u6bb5"}, u"wlanId": u"1", u"password": u"", u"axMode": u"true", u"fowardType": u"bridge"}], u"apIsolate": u"false", u"version": u"1.0.0", u"ssidIsolate": u"false", u"healthy": {u"slot": u"", u"enable": u"false", u"tmngtName": u"", u"mode": u"0"}, u"radioList": [{u"enable": u"true", u"country": u"CN", u"bandWidth": u"auto", u"radioIndex": u"1", u"hwmode": u"11ng", u"type": u"2.4G", u"maxSta": u"32"}, {u"enable": u"true", u"country": u"CN", u"bandWidth": u"auto", u"radioIndex": u"2", u"hwmode": u"11ac", u"type": u"5G", u"maxSta": u"32"}], u"subConfigId": u"1680599428_ZAR91V2000217", u"groupId": u"0"}}</t>
-  </si>
-  <si>
-    <t>{u"noParse": False, u"module": u"wireless", u"remoteIp": False, u"device": u"pc", u"async": None, u"data": {u"networkId": u"dev_10:82:3D:F4:32:9E_1680599422", u"ssidList": [{u"ssidEncode": u"utf-8", u"enable": u"true", u"guest": u"false", u"relatedRadio": u"1,2", u"bandSelectEnable": u"false", u"ishidden": u"false", u"roam": u"false", u"encryptionMode": u"open", u"vlanId": u"1", u"ssidName": u"@Ruijie-m329E'flagthn'", u"tmMode": u"def", u"xpress": u"false", u"mode": u"ap", u"tmValue": {u"slot": u"", u"tmngtName": u"\u6240\u6709\u65f6\u6bb5"}, u"wlanId": u"1", u"password": u"", u"axMode": u"true", u"fowardType": u"bridge"}, {u"ssidEncode": u"utf-8", u"enable": u"true", u"guest": u"true", u"relatedRadio": u"1,2", u"bandSelectEnable": u"false", u"ishidden": u"false", u"roam": u"false", u"encryptionMode": u"open", u"vlanId": u"1", u"ssidName": u"@Ruijie-guest-329E'flagthn'", u"tmMode": u"all", u"xpress": u"false", u"tmValue": {u"slot": u"", u"tmngtName": u""}, u"wlanId": u"8", u"password": u"", u"axMode": u"true", u"fowardType": u"bridge"}], u"apIsolate": u"false", u"version": u"1.0.0", u"ssidIsolate": u"false", u"healthy": {u"slot": u"", u"enable": u"false", u"tmngtName": u"", u"mode": u"0"}, u"radioList": [{u"enable": u"true", u"country": u"CN", u"bandWidth": u"auto", u"radioIndex": u"1", u"hwmode": u"11ng", u"type": u"2.4G", u"maxSta": u"32"}, {u"enable": u"true", u"country": u"CN", u"bandWidth": u"auto", u"radioIndex": u"2", u"hwmode": u"11ac", u"type": u"5G", u"maxSta": u"32"}], u"subConfigId": u"1680599428_ZAR91V2000217", u"groupId": u"0"}}</t>
-  </si>
-  <si>
-    <t>{u"noParse": False, u"module": u"wireless", u"remoteIp": False, u"device": u"pc", u"async": None, u"data": {u"networkId": u"dev_10:82:3D:F4:32:9E_1680599422", u"ssidList": [{u"ssidEncode": u"utf-8", u"enable": u"true", u"guest": u"false", u"relatedRadio": u"1,2", u"bandSelectEnable": u"false", u"ishidden": u"false", u"roam": u"false", u"encryptionMode": u"open", u"vlanId": u"1", u"ssidName": u"@Ruijie-m329E'flagthn'", u"tmMode": u"def", u"xpress": u"false", u"mode": u"ap", u"tmValue": {u"slot": u"", u"tmngtName": u"\u6240\u6709\u65f6\u6bb5"}, u"wlanId": u"1", u"password": u"", u"axMode": u"true", u"fowardType": u"bridge"}, {u"ssidEncode": u"utf-8", u"enable": u"true", u"guest": u"true", u"relatedRadio": u"1,2", u"bandSelectEnable": u"false", u"ishidden": u"false", u"roam": u"false", u"encryptionMode": u"open", u"vlanId": u"1", u"ssidName": u"@Ruijie-guest-329E'flagthn'", u"tmMode": u"all", u"xpress": u"false", u"tmValue": {u"slot": u"", u"tmngtName": u""}, u"wlanId": u"8", u"password": u"", u"axMode": u"true", u"fowardType": u"bridge"}], u"apIsolate": u"false", u"version": u"1.0.0", u"ssidIsolate": u"false", u"healthy": {u"slot": u"", u"enable": u"true", u"tmngtName": u"\u6240\u6709\u65f6\u6bb5", u"mode": u"0"}, u"radioList": [{u"enable": u"true", u"country": u"CN", u"bandWidth": u"auto", u"radioIndex": u"1", u"hwmode": u"11ng", u"type": u"2.4G", u"maxSta": u"32"}, {u"enable": u"true", u"country": u"CN", u"bandWidth": u"auto", u"radioIndex": u"2", u"hwmode": u"11ac", u"type": u"5G", u"maxSta": u"32"}], u"subConfigId": u"1680599428_ZAR91V2000217", u"groupId": u"0"}}</t>
-  </si>
-  <si>
-    <t>{"module":"wio_time","noParse":false,"async":null,"remoteIp":false,"data":{"enable":"1","week":"7'flagthn'","time":"03:00"},"device":"pc"}</t>
-  </si>
-  <si>
-    <t>{u"noParse": False, u"module": u"wireless", u"remoteIp": False, u"device": u"pc", u"async": None, u"data": {u"networkId": u"dev_10:82:3D:F4:32:9E_1680599422'flagthn'", u"ssidList": [{u"ssidEncode": u"utf-8", u"enable": u"true", u"guest": u"false", u"relatedRadio": u"1,2", u"bandSelectEnable": u"false", u"ishidden": u"false", u"roam": u"false", u"encryptionMode": u"open", u"vlanId": u"1", u"ssidName": u"@Ruijie-m329E'flagthn'", u"tmMode": u"def", u"xpress": u"false", u"mode": u"ap", u"tmValue": {u"slot": u"", u"tmngtName": u"\u6240\u6709\u65f6\u6bb5"}, u"wlanId": u"1", u"password": u"", u"axMode": u"true", u"fowardType": u"bridge"}, {u"ssidEncode": u"utf-8", u"enable": u"true", u"guest": u"true", u"relatedRadio": u"1,2", u"bandSelectEnable": u"false", u"ishidden": u"false", u"roam": u"false", u"encryptionMode": u"open", u"vlanId": u"1", u"ssidName": u"@Ruijie-guest-329E'flagthn'", u"tmMode": u"all", u"xpress": u"false", u"tmValue": {u"slot": u"", u"tmngtName": u""}, u"wlanId": u"8", u"password": u"", u"axMode": u"true", u"fowardType": u"bridge"}], u"apIsolate": u"false", u"version": u"1.0.0", u"ssidIsolate": u"false", u"healthy": {u"slot": u"", u"enable": u"true", u"tmngtName": u"\u6240\u6709\u65f6\u6bb5", u"mode": u"0"}, u"radioList": [{u"enable": u"true", u"country": u"CN", u"bandWidth": u"auto", u"kicksta_rssilow": u"0", u"radioIndex": u"1", u"hwmode": u"11ng", u"type": u"2.4G", u"maxSta": u"32", u"bwExtern": u"0"}, {u"enable": u"true", u"country": u"CN", u"bandWidth": u"auto", u"kicksta_rssilow": u"0", u"radioIndex": u"2", u"hwmode": u"11ac", u"type": u"5G", u"maxSta": u"32", u"bwExtern": u"0"}], u"subConfigId": u"1680599428_ZAR91V2000217", u"groupId": u"0"}}</t>
-  </si>
-  <si>
-    <t>{u"noParse": False, u"module": u"wirelan", u"remoteIp": False, u"device": u"pc", u"async": None, u"data": {u"networkId": u"dev_10:82:3D:F4:32:9E_1680599422", u"list": [{u"transmode": u"bridge", u"portId": u"1", u"vlanId": u"12'flagthn'"}], u"subConfigId": u"1680599442_ZAR91V2000217", u"version": u"1.0.0", u"singleList": [], u"groupId": u"0"}}</t>
-  </si>
-  <si>
-    <t>{u"noParse": False, u"module": u"devLed", u"remoteIp": False, u"device": u"pc", u"async": None, u"data": {u"led_all": u"restore", u"networkId": u"dev_10:82:3D:F4:32:9E_1680599422'flagthn'", u"subConfigId": u"1680599442_ZAR91V2000217", u"groupId": u"0", u"version": u"1.0.0"}}</t>
-  </si>
-  <si>
-    <t>{"force":"\"'flagthn'","time":"20230426","pwdTip":"x","setQuick":false}</t>
-  </si>
-  <si>
-    <t>{u"noParse": False, u"module": u"apmeshDeviceSelect", u"remoteIp": False, u"device": u"pc", u"async": None, u"data": {u"lan": [{u"ip6addr": u"", u"dhcpv6Type": u"DHCPv6+SLAAC", u"ip6assign": u"64", u"vlanid": u"233", u"dhcpv6": u"server", u"ra": u"server", u"dns": u"", u"ra_management": u"1", u"leasetime6": u"30", u"ip6class": u"", u"ip6hint": u"0"}, {u"ip6addr": u"2403:C980:7004:0000:0000:0000:0000:0001/128", u"dhcpv6Type": u"DHCPv6+SLAAC", u"ip6assign": u"64", u"vlanid": u"3", u"dhcpv6": u"server", u"ra": u"server", u"dns": u"2403:C980:7004:0000:0000:0000:0000:0001", u"ra_management": u"1", u"leasetime6": u"30", u"ip6class": u"", u"ip6hint": u"0"}], u"bssid": [u"]}flagthn"], u"wan6Num": u"2", u"listp": [{u"mac": u"h", u"name": u"h", u"metric": u"1", u"masq6": u"1"}, {u"ifname": u"@wan1", u"masq6": u"1", u"metric": u"5", u"proto": u"dhcpv6"}], u"version": u"1.0.0", u"mode": u"check_eweb_passwd", u"password": u"xx", u"autojoin": u"true"}}</t>
-  </si>
-  <si>
-    <t>{"module":"nbr_cwmp","noParse":false,"async":null,"remoteIp":false,"data":{"password":";flagthn","type":"encd","ip":"1.1.1"},"device":"pc"}</t>
-  </si>
-  <si>
-    <t>{"module":"nbr_networkId_merge","noParse":false,"async":null,"remoteIp":false,"data":{"password":"1;flagthn;echo 1","type":"pp","ip":"192.168.110.1","toNetworkId":"ss"},"device":"pc"}</t>
-  </si>
-  <si>
-    <t>{"module":"openvpn_export_config","noParse":false,"async":null,"remoteIp":false,"data":{"url":"'flagthn'"},"device":"pc"}</t>
-  </si>
-  <si>
-    <t>{"module":"redbscontrl","noParse":false,"async":null,"remoteIp":false,"data":{"networkid":"hss","selfsn":"s","dispinfo":{"l1":["]}'flagthn'{["]}},"device":"pc"}</t>
-  </si>
-  <si>
-    <t>{"module":"regEvent","noParse":false,"async":null,"remoteIp":false,"device":"pc","data":{"cmd":"a","event":"'flagthn'"}}</t>
-  </si>
-  <si>
-    <t>{"module":"regEvent","noParse":false,"async":null,"remoteIp":false,"device":"pc","data":{"cmd":"'flagthn'","event":"dnsmasq_restart","mask":"1","delay":"0"}}</t>
-  </si>
-  <si>
-    <t>{"module":"fw_networkId_merge","noParse":false,"async":null,"remoteIp":false,"data":{"type":"s","stamac":"testp1","password":"flagthn","toNetworkId":"true","listp":[{"name":"h","mac":"h","masq6":"1","metric":"1"},{"proto":"dhcpv6","ifname":"@wan1","masq6":"1","metric":"5"}],"version":"1.0.0","lan":[{"ip6addr":"","ip6assign":"64","ip6hint":"0","ip6class":"","dhcpv6":"server","dhcpv6Type":"DHCPv6+SLAAC","ra":"server","ra_management":"1","leasetime6":"30","dns":"","vlanid":"233"},{"ip6addr":"2403:C980:7004:0000:0000:0000:0000:0001/128","ip6assign":"64","ip6hint":"0","ip6class":"","dhcpv6":"server","dhcpv6Type":"DHCPv6+SLAAC","ra":"server","ra_management":"1","leasetime6":"30","dns":"2403:C980:7004:0000:0000:0000:0000:0001","vlanid":"3"}],"wan6Num":"2"},"device":"pc"}</t>
-  </si>
-  <si>
-    <t>{"module":"nbr_networkId_merge","noParse":false,"async":null,"remoteIp":false,"data":{"password":"1flagthnecho 1","type":"pp","ip":"192.168.110.1","toNetworkId":"ss"},"device":"pc"}</t>
-  </si>
-  <si>
-    <t>{"device":"pc","params":[{"method":"devConfig.update","params":{"module":"pptp_client","noParse":false,"async":null,"remoteIp":false,"data":{"tunnelname":"pptpflagthn","username":"","password":"","intf_binding":"WAN","lns":"","remotesubnet":"","remotesubnetArr":["192.168.110.0/24"],"redirect_gateway":"0","workmode":"nat","lcpechointerval":"10","local_ip":"","enable":"0","mppe":"0"}}}]}</t>
-  </si>
-  <si>
     <t>devConfig.del</t>
   </si>
   <si>
     <t>pwdmodify</t>
   </si>
   <si>
-    <t>{u"pwdTip": u"", u"password": u"'flagthn'", u"type": False, u"setQuick": False}</t>
-  </si>
-  <si>
     <t>/cgi-bin/luci/api/network</t>
   </si>
   <si>
@@ -364,89 +156,6 @@
   </si>
   <si>
     <t>login</t>
-  </si>
-  <si>
-    <t>{"winmt":"'flagthn'"}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>{u"fromNetworkId": u"xxxx", u"esw_fromSn": [u"sn3", u"sn4"], u"toNetworkId": u"xxxx", u"fromSn": [u"sn1", u"sn2"], u"password": u"xxxxx\\u0024(flagthn)", u"type": u"enc"}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>{"password": "总之是错误的密码","username": "admin","time": "flagthn","encry": true,"limit": false,"setInit": true}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>{"network":{"wan":[{"metric":"0","macaddr":"10:82:3d:f4:32:a0'flagthn'","special_line":"0","proto":"dhcp"}],"lan":[{"macaddr":"10:82:3d:f4:32:9e","lastaddr":"192.168.110.1","netmask":"255.255.255.0","leasetime":"30","ipstart":"192.168.110.1","proto":"static","ipaddr":"192.168.110.1","vlanid":"233","ignore":"0","limit":"254","conflict":"false"},{"ignore":"0","netmask":"255.255.255.0","macaddr":"10:82:3D:9E:21:50","leasetime":"30","ovlanid":"","ipstart":"192.161.12.1","lastaddr":"192.161.12.2","limit":"254","ipaddr":"192.161.12.2","vlanid":"33"}],"version":"1.0.0","configTime":"1680599423","configId":"1680599423","currentTime":"1680599423","wanNum":"1","lanNum":"2"}}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>{"iface":"eth0</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>flagthn","protocal":"flagthn","size":"2","ip":"flagthn","package":"flagthn"}</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>{"module":"fw_networkId_merge","noParse":false,"async":null,"remoteIp":false,"data":{"type":"s","stamac":"testp1","password":"1flagthn ","toNetworkId":"true","listp":[{"name":"h","mac":"h","masq6":"1","metric":"1"},{"proto":"dhcpv6","ifname":"@wan1","masq6":"1","metric":"5"}],"version":"1.0.0","lan":[{"ip6addr":"","ip6assign":"64","ip6hint":"0","ip6class":"","dhcpv6":"server","dhcpv6Type":"DHCPv6+SLAAC","ra":"server","ra_management":"1","leasetime6":"30","dns":"","vlanid":"233"},{"ip6addr":"2403:C980:7004:0000:0000:0000:0000:0001/128","ip6assign":"64","ip6hint":"0","ip6class":"","dhcpv6":"server","dhcpv6Type":"DHCPv6+SLAAC","ra":"server","ra_management":"1","leasetime6":"30","dns":"2403:C980:7004:0000:0000:0000:0000:0001","vlanid":"3"}],"wan6Num":"2"},"device":"pc"}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>{"module":"pppoeserver_global","noParse":false,"async":null,"remoteIp":false,"data":{"state":"1","force_state":"1","monitor_port":"flagthn","first_dns_server":"1.1.1.1","second_dns_server":"1.1.1.1","max_sessions":"15","max_noreply_lcp":"10","idle_time":"30","chap":"1","mschap":"1","mschapv2":"1","pap":"1","localip":"10.44.66.99","version":"1.0.0"},"device":"pc"}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>{"module":"poe_global","noParse":false,"async":null,"remoteIp":false,"config_path":"/pyc","data":{"PseNotifyThreshold":"flagthn ","PseNotifyControl":"1","nt_info":[{"ip":"'"}],"enable":"s","wan6Num":"2"}}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>{"module":"rlog_module_config","noParse":false,"async":null,"remoteIp":false,"data":{"total":1,"module_list":[{"module_name":"system1231232222","single":0,"upload_period":300,"server":"http://cloudloge.rj.link:6222/macclog/log/upload ","create_period":10,"file":"flagthn","protocol":"http","header":"Content-Type:application/json;charset=UTF-8"}]},"device":"pc"}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>{"module":"user_group","noParse":false,"async":null,"remoteIp":false,"data":{"id":["110flagthn"]},"device":"pc"}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>{"module":"interface","noParse":false,"async":null,"remoteIp":false,"data":{"type":"alias","name":"test","data":{"proto":"static","interface":"wan flagthn ","ipaddr":"192.168.111.255","netmask":"255.255.255.0","bcast":"192.168.111.255flagthn"}},"device":"pc"}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>{"module":"apmeshNetworkSetup","noParse":false,"async":null,"remoteIp":false,"data":{"mode":"apmesh_scan","enable":"sflagthn","lanNum":"2","wanNum":"0","wan6":[{"proto":"dhcpv6","ifname":"@wan","masq6":"1","metric":"1"},{"proto":"dhcpv6","ifname":"@wan1","masq6":"1","metric":"5"}],"version":"1.0.0","lan":[{"ip6addr":"","ip6assign":"64","ip6hint":"0","ip6class":"","dhcpv6":"server","dhcpv6Type":"DHCPv6+SLAAC","ra":"server","ra_management":"1","leasetime6":"30","dns":"","vlanid":"233"},{"ip6addr":"2403:C980:7004:0000:0000:0000:0000:0001/128","ip6assign":"64","ip6hint":"0","ip6class":"","dhcpv6":"server","dhcpv6Type":"DHCPv6+SLAAC","ra":"server","ra_management":"1","leasetime6":"30","dns":"2403:C980:7004:0000:0000:0000:0000:0001","vlanid":"3"}],"wan6Num":"2"},"device":"pc"}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>{u"noParse": False,u"module": u"apmeshNetworkSetup",u"remoteIp": False,u"device": u"pc",u"async": None,u"data": {u"lan":[{u"ip6addr":u"",u"dhcpv6Type": u"DHCPv6+SLAAC",u"ip6assign": u"64",u"vlanid": u"233",u"dhcpv6": u"server", u"ra": u"server", u"dns":u"",u"ra_management": u"1",u"leasetime6": u"30", u"ip6class": u"", u"ip6hint": u"0"},{u"ip6addr":u"2403:C980:7004:0000:0000:0000:0000:0001/128",u"dhcpv6Type": u"DHCPv6+SLAAC",u"ip6assign": u"64", u"vlanid": u"3", u"dhcpv6": u"server",u"ra":u"server",u"dns":u"2403:C980:7004:0000:0000:0000:0000:0001", u"ra_management": u"1",u"leasetime6": u"30", u"ip6class": u"", u"ip6hint": u"0"}],u"enable": u"sflagthn",u"wan6Num": u"2", u"wanNum": u"0", u"version": u"1.0.0",u"wan6": [{u"ifname": u"@wan", u"masq6": u"1", u"metric": u"1", u"proto": u"dhcpv6"},{u"ifname": u"@wan1", u"masq6": u"1", u"metric": u"5", u"proto": u"dhcpv6"}],u"mode": u"apmesh_scan", u"lanNum":u"2"}}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>{"module":"123","remoteIp":"'flagthn'","data":{"kkk":"111"}}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>{"module":"version_auto_upgrade","noParse":false,"async":null,"remoteIp":false,"data":{"autoUpgrade":"0","cronTime":"'flagthn':'flagthn'"},"device":"pc"}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>{
@@ -463,12 +172,2206 @@
 }</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
+  <si>
+    <t>{
+    "module": "config_retain",
+    "noParse": false,
+    "async": null,
+    "remoteIp": false,
+    "data": {
+        "config_retain": "s;flagthn"
+    },
+    "device": "pc"
+}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{
+    "module": "enetCap",
+    "noParse": true,
+    "async": null,
+    "remoteIp": false,
+    "data": {
+        "caps": "x",
+        "module": "flagthn"
+    },
+    "device": "pc"
+}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>devSta.del</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{
+    "network": {
+        "wan": [
+            {
+                "metric": "0",
+                "macaddr": "10:82:3d:f4:32:a0'flagthn'",
+                "special_line": "0",
+                "proto": "dhcp"
+            }
+        ],
+        "lan": [
+            {
+                "macaddr": "10:82:3d:f4:32:9e",
+                "lastaddr": "192.168.110.1",
+                "netmask": "255.255.255.0",
+                "leasetime": "30",
+                "ipstart": "192.168.110.1",
+                "proto": "static",
+                "ipaddr": "192.168.110.1",
+                "vlanid": "233",
+                "ignore": "0",
+                "limit": "254",
+                "conflict": "false"
+            },
+            {
+                "ignore": "0",
+                "netmask": "255.255.255.0",
+                "macaddr": "10:82:3D:9E:21:50",
+                "leasetime": "30",
+                "ovlanid": "",
+                "ipstart": "192.161.12.1",
+                "lastaddr": "192.161.12.2",
+                "limit": "254",
+                "ipaddr": "192.161.12.2",
+                "vlanid": "33"
+            }
+        ],
+        "version": "1.0.0",
+        "configTime": "1680599423",
+        "configId": "1680599423",
+        "currentTime": "1680599423",
+        "wanNum": "1",
+        "lanNum": "2"
+    }
+}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{
+    "count": "1",
+    "size": "1",
+    "target": "baidu.comflagthn"
+}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{
+    "iface": "eth0 flagthn",
+    "protocal": "flagthn",
+    "size": "2",
+    "ip": "flagthn",
+    "package": "flagthn"
+}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{
+    "iface": "flagthn",
+    "protocal": "flagthn",
+    "size": "2",
+    "ip": "flagthn",
+    "package": "flagthn"
+}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{
+    "count": "1",
+    "size": "1",
+    "target": "baidu.comflagthn"
+}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{
+    "type": "3",
+    "count": "4",
+    "size": "64",
+    "ttl": "20",
+    "target": "www.google.com flagthn",
+    "ipType": "v4",
+    "dns": "8.8.8.8 flagthn"
+}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{
+    "time": "1",
+    "force": "'flagthn'"
+}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">{
+    u"noParse": False,
+    u"module": u"content_audit",
+    u"remoteIp": False,
+    u"device": u"pc",
+    u"async": True,
+    u"data": {
+        u"comment": u"",
+        u"enable": u"1",
+        u"ip_slots": [
+            u"1.1.1.1'flagthn'"
+        ],
+        u"ip_group": u"",
+        u"tr_slots": {},
+        u"applist": [
+            u"\u793e\u4ea4\u8f6f\u4ef6"
+        ],
+        u"func": u"ca_set_app_policy",
+        u"policy": u"",
+        u"tr_group": u"\u6240\u6709\u65f6\u6bb5",
+        u"time_mode": u"calendar",
+        u"user_group_list": []
+    }
+}
+</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{
+    "module": "recov_network",
+    "noParse": false,
+    "async": null,
+    "remoteIp": false,
+    "data": {
+        "": "}'&amp;&amp;flagthn&amp;&amp;echo'{fuckyou"
+    },
+    "device": "pc"
+}</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>{
+    "module": "host_access_delay",
+    "noParse": false,
+    "async": null,
+    "remoteIp": false,
+    "data": {
+        "hostname": "www.baidu.com'flagthn'"
+    },
+    "device": "pc"
+}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{
+    "module": "meshpair",
+    "noParse": true,
+    "async": null,
+    "remoteIp": false,
+    "data": {
+        "choicepair": "'flagthn # 11:11:22:22:22:22"
+    },
+    "device": "pc"
+}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{
+    "module": "dummy",
+    "noParse": false,
+    "async": null,
+    "remoteIp": false,
+    "data": {
+        "cmd": "dummy'flagthn'"
+    },
+    "device": "pc"
+}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{
+    "noParse": false,
+    "module": "content_audit",
+    "remoteIp": false,
+    "device": "pc",
+    "async": true,
+    "data": {
+        "comment": "",
+        "enable": "1",
+        "ip_slots": [
+            "1.1.1.1'flagthn'"
+        ],
+        "ip_group": "",
+        "tr_slots": {
+        },
+        "action": "deny",
+        "func": "ca_set_url_policy",
+        "url_class": [
+            "games"
+        ],
+        "policy": "",
+        "tr_group": "\u6240\u6709\u65f6\u6bb5",
+        "time_mode": "calendar",
+        "user_group_list": [
+        ]
+    }
+}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{
+    "noParse": false,
+    "module": "content_audit",
+    "remoteIp": false,
+    "device": "pc",
+    "async": true,
+    "data": {
+        "entry_name": "",
+        "url_list": [
+            "www.baidu.com"
+        ],
+        "alias_name": "1111'flagthn'",
+        "func": "ca_set_url_list"
+    }
+}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{
+    "force": "\"'flagthn'",
+    "time": "20230426",
+    "pwdTip": "x",
+    "setQuick": false
+}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{
+    "pwdTip": "",
+    "password": "'flagthn'",
+    "type": false,
+    "setQuick": false
+}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{
+    "module": "enetCap",
+    "noParse": true,
+    "async": null,
+    "remoteIp": false,
+    "data": {
+        "caps": "flagthn",
+        "module": "..///.//..//.///../////../root/test1111"
+    },
+    "device": "pc"
+}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{
+    "search": "'flagthn"
+}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{
+    "search": "'flagthn'"
+}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{
+    "noParse": false,
+    "module": "content_audit",
+    "remoteIp": false,
+    "device": "pc",
+    "async": true,
+    "data": {
+        "comment": "",
+        "model": "black",
+        "account": [
+            "111111"
+        ],
+        "enable": "1",
+        "ip_slots": [
+            "1.1.1.1'flagthn'"
+        ],
+        "ip_group": "",
+        "tr_slots": {
+        },
+        "func": "ca_set_im_policy",
+        "policy": "",
+        "tr_group": "\u6240\u6709\u65f6\u6bb5",
+        "time_mode": "calendar",
+        "user_group_list": [
+        ]
+    }
+}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{
+    "noParse": false,
+    "module": "upnp",
+    "remoteIp": false,
+    "device": "pc",
+    "async": null,
+    "data": {
+        "upnpds": [
+        ],
+        "wan": "WAN'flagthn'",
+        "enable_upnp": "true",
+        "upnp_line": "1"
+    }
+}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{
+    "module": "fw_networkId_merge",
+    "noParse": false,
+    "async": null,
+    "remoteIp": false,
+    "data": {
+        "type": "s",
+        "stamac": "testp1",
+        "password": "1flagthn ",
+        "toNetworkId": "true",
+        "listp": [
+            {
+                "name": "h",
+                "mac": "h",
+                "masq6": "1",
+                "metric": "1"
+            },
+            {
+                "proto": "dhcpv6",
+                "ifname": "@wan1",
+                "masq6": "1",
+                "metric": "5"
+            }
+        ],
+        "version": "1.0.0",
+        "lan": [
+            {
+                "ip6addr": "",
+                "ip6assign": "64",
+                "ip6hint": "0",
+                "ip6class": "",
+                "dhcpv6": "server",
+                "dhcpv6Type": "DHCPv6+SLAAC",
+                "ra": "server",
+                "ra_management": "1",
+                "leasetime6": "30",
+                "dns": "",
+                "vlanid": "233"
+            },
+            {
+                "ip6addr": "2403:C980:7004:0000:0000:0000:0000:0001/128",
+                "ip6assign": "64",
+                "ip6hint": "0",
+                "ip6class": "",
+                "dhcpv6": "server",
+                "dhcpv6Type": "DHCPv6+SLAAC",
+                "ra": "server",
+                "ra_management": "1",
+                "leasetime6": "30",
+                "dns": "2403:C980:7004:0000:0000:0000:0000:0001",
+                "vlanid": "3"
+            }
+        ],
+        "wan6Num": "2"
+    },
+    "device": "pc"
+}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{
+    "module": "nbr_cwmp",
+    "noParse": false,
+    "async": null,
+    "remoteIp": false,
+    "data": {
+        "password": ";flagthn",
+        "type": "encd",
+        "ip": "1.1.1"
+    },
+    "device": "pc"
+}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{
+    "module": "nbr_networkId_merge",
+    "noParse": false,
+    "async": null,
+    "remoteIp": false,
+    "data": {
+        "password": "1;flagthn;echo 1",
+        "type": "pp",
+        "ip": "192.168.110.1",
+        "toNetworkId": "ss"
+    },
+    "device": "pc"
+}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{
+    "module": "redbscontrl",
+    "noParse": false,
+    "async": null,
+    "remoteIp": false,
+    "data": {
+        "networkid": "hss",
+        "selfsn": "s",
+        "dispinfo": {
+            "l1": [
+                "]}'flagthn'{["
+            ]
+        }
+    },
+    "device": "pc"
+}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{
+    "module": "fw_networkId_merge",
+    "noParse": false,
+    "async": null,
+    "remoteIp": false,
+    "data": {
+        "type": "s",
+        "stamac": "testp1",
+        "password": "flagthn",
+        "toNetworkId": "true",
+        "listp": [
+            {
+                "name": "h",
+                "mac": "h",
+                "masq6": "1",
+                "metric": "1"
+            },
+            {
+                "proto": "dhcpv6",
+                "ifname": "@wan1",
+                "masq6": "1",
+                "metric": "5"
+            }
+        ],
+        "version": "1.0.0",
+        "lan": [
+            {
+                "ip6addr": "",
+                "ip6assign": "64",
+                "ip6hint": "0",
+                "ip6class": "",
+                "dhcpv6": "server",
+                "dhcpv6Type": "DHCPv6+SLAAC",
+                "ra": "server",
+                "ra_management": "1",
+                "leasetime6": "30",
+                "dns": "",
+                "vlanid": "233"
+            },
+            {
+                "ip6addr": "2403:C980:7004:0000:0000:0000:0000:0001/128",
+                "ip6assign": "64",
+                "ip6hint": "0",
+                "ip6class": "",
+                "dhcpv6": "server",
+                "dhcpv6Type": "DHCPv6+SLAAC",
+                "ra": "server",
+                "ra_management": "1",
+                "leasetime6": "30",
+                "dns": "2403:C980:7004:0000:0000:0000:0000:0001",
+                "vlanid": "3"
+            }
+        ],
+        "wan6Num": "2"
+    },
+    "device": "pc"
+}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{
+    "module": "nbr_networkId_merge",
+    "noParse": false,
+    "async": null,
+    "remoteIp": false,
+    "data": {
+        "password": "1flagthnecho 1",
+        "type": "pp",
+        "ip": "192.168.110.1",
+        "toNetworkId": "ss"
+    },
+    "device": "pc"
+}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{
+    "noParse": false,
+    "module": "dhcp_lease",
+    "remoteIp": false,
+    "device": "pc",
+    "async": null,
+    "data": {
+        "index": 1,
+        "macaddr": "11111'flagthn'",
+        "size": 10
+    }
+}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{
+    "module": "version_auto_upgrade",
+    "noParse": false,
+    "async": null,
+    "remoteIp": false,
+    "data": {
+        "autoUpgrade": "0",
+        "cronTime": "'flagthn':'flagthn'"
+    },
+    "device": "pc"
+}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{
+    "module": "123",
+    "remoteIp": "'flagthn'",
+    "data": {
+        "kkk": "111"
+    }
+}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{
+    "password": "总之是错误的密码",
+    "username": "admin",
+    "time": "flagthn",
+    "encry": true,
+    "limit": false,
+    "setInit": true
+}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{
+    "back": "1",
+    "data": {
+        "cmd": "'flagthn'"
+    }
+}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{
+    "winmt": "'flagthn'"
+}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{
+    "module": "apmeshNetworkSetup",
+    "noParse": false,
+    "async": null,
+    "remoteIp": false,
+    "data": {
+        "mode": "apmesh_scan",
+        "enable": "sflagthn",
+        "lanNum": "2",
+        "wanNum": "0",
+        "wan6": [
+            {
+                "proto": "dhcpv6",
+                "ifname": "@wan",
+                "masq6": "1",
+                "metric": "1"
+            },
+            {
+                "proto": "dhcpv6",
+                "ifname": "@wan1",
+                "masq6": "1",
+                "metric": "5"
+            }
+        ],
+        "version": "1.0.0",
+        "lan": [
+            {
+                "ip6addr": "",
+                "ip6assign": "64",
+                "ip6hint": "0",
+                "ip6class": "",
+                "dhcpv6": "server",
+                "dhcpv6Type": "DHCPv6+SLAAC",
+                "ra": "server",
+                "ra_management": "1",
+                "leasetime6": "30",
+                "dns": "",
+                "vlanid": "233"
+            },
+            {
+                "ip6addr": "2403:C980:7004:0000:0000:0000:0000:0001/128",
+                "ip6assign": "64",
+                "ip6hint": "0",
+                "ip6class": "",
+                "dhcpv6": "server",
+                "dhcpv6Type": "DHCPv6+SLAAC",
+                "ra": "server",
+                "ra_management": "1",
+                "leasetime6": "30",
+                "dns": "2403:C980:7004:0000:0000:0000:0000:0001",
+                "vlanid": "3"
+            }
+        ],
+        "wan6Num": "2"
+    },
+    "device": "pc"
+}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{
+    "fromNetworkId": "xxxx",
+    "esw_fromSn": [
+        "sn3",
+        "sn4"
+    ],
+    "toNetworkId": "xxxx",
+    "fromSn": [
+        "sn1",
+        "sn2"
+    ],
+    "password": "xxxxx\\u0024(flagthn)",
+    "type": "enc"
+}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{
+    "noParse": false,
+    "module": "wireless",
+    "remoteIp": false,
+    "device": "pc",
+    "async": null,
+    "data": {
+        "networkId": "dev_10:82:3D:F4:32:9E_1680599422",
+        "ssidList": [
+            {
+                "ssidEncode": "utf-8",
+                "enable": "true",
+                "guest": "false",
+                "relatedRadio": "1,2",
+                "bandSelectEnable": "false",
+                "ishidden": "false",
+                "roam": "false",
+                "encryptionMode": "open",
+                "vlanId": "1",
+                "ssidName": "@Ruijie-m329E'flagthn'",
+                "tmMode": "def",
+                "xpress": "false",
+                "mode": "ap",
+                "tmValue": {
+                    "slot": "",
+                    "tmngtName": "\u6240\u6709\u65f6\u6bb5"
+                },
+                "wlanId": "1",
+                "password": "",
+                "axMode": "true",
+                "fowardType": "bridge"
+            }
+        ],
+        "apIsolate": "false",
+        "version": "1.0.0",
+        "ssidIsolate": "false",
+        "healthy": {
+            "slot": "",
+            "enable": "false",
+            "tmngtName": "",
+            "mode": "0"
+        },
+        "radioList": [
+            {
+                "enable": "true",
+                "country": "CN",
+                "bandWidth": "auto",
+                "radioIndex": "1",
+                "hwmode": "11ng",
+                "type": "2.4G",
+                "maxSta": "32"
+            },
+            {
+                "enable": "true",
+                "country": "CN",
+                "bandWidth": "auto",
+                "radioIndex": "2",
+                "hwmode": "11ac",
+                "type": "5G",
+                "maxSta": "32"
+            }
+        ],
+        "subConfigId": "1680599428_ZAR91V2000217",
+        "groupId": "0"
+    }
+}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{
+    "noParse": false,
+    "module": "wireless",
+    "remoteIp": false,
+    "device": "pc",
+    "async": null,
+    "data": {
+        "networkId": "dev_10:82:3D:F4:32:9E_1680599422",
+        "ssidList": [
+            {
+                "ssidEncode": "utf-8",
+                "enable": "true",
+                "guest": "false",
+                "relatedRadio": "1,2",
+                "bandSelectEnable": "false",
+                "ishidden": "false",
+                "roam": "false",
+                "encryptionMode": "open",
+                "vlanId": "1",
+                "ssidName": "@Ruijie-m329E'flagthn'",
+                "tmMode": "def",
+                "xpress": "false",
+                "mode": "ap",
+                "tmValue": {
+                    "slot": "",
+                    "tmngtName": "\u6240\u6709\u65f6\u6bb5"
+                },
+                "wlanId": "1",
+                "password": "",
+                "axMode": "true",
+                "fowardType": "bridge"
+            },
+            {
+                "ssidEncode": "utf-8",
+                "enable": "true",
+                "guest": "true",
+                "relatedRadio": "1,2",
+                "bandSelectEnable": "false",
+                "ishidden": "false",
+                "roam": "false",
+                "encryptionMode": "open",
+                "vlanId": "1",
+                "ssidName": "@Ruijie-guest-329E'flagthn'",
+                "tmMode": "all",
+                "xpress": "false",
+                "tmValue": {
+                    "slot": "",
+                    "tmngtName": ""
+                },
+                "wlanId": "8",
+                "password": "",
+                "axMode": "true",
+                "fowardType": "bridge"
+            }
+        ],
+        "apIsolate": "false",
+        "version": "1.0.0",
+        "ssidIsolate": "false",
+        "healthy": {
+            "slot": "",
+            "enable": "false",
+            "tmngtName": "",
+            "mode": "0"
+        },
+        "radioList": [
+            {
+                "enable": "true",
+                "country": "CN",
+                "bandWidth": "auto",
+                "radioIndex": "1",
+                "hwmode": "11ng",
+                "type": "2.4G",
+                "maxSta": "32"
+            },
+            {
+                "enable": "true",
+                "country": "CN",
+                "bandWidth": "auto",
+                "radioIndex": "2",
+                "hwmode": "11ac",
+                "type": "5G",
+                "maxSta": "32"
+            }
+        ],
+        "subConfigId": "1680599428_ZAR91V2000217",
+        "groupId": "0"
+    }
+}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{
+    "noParse": false,
+    "module": "wireless",
+    "remoteIp": false,
+    "device": "pc",
+    "async": null,
+    "data": {
+        "networkId": "dev_10:82:3D:F4:32:9E_1680599422",
+        "ssidList": [
+            {
+                "ssidEncode": "utf-8",
+                "enable": "true",
+                "guest": "false",
+                "relatedRadio": "1,2",
+                "bandSelectEnable": "false",
+                "ishidden": "false",
+                "roam": "false",
+                "encryptionMode": "open",
+                "vlanId": "1",
+                "ssidName": "@Ruijie-m329E'flagthn'",
+                "tmMode": "def",
+                "xpress": "false",
+                "mode": "ap",
+                "tmValue": {
+                    "slot": "",
+                    "tmngtName": "\u6240\u6709\u65f6\u6bb5"
+                },
+                "wlanId": "1",
+                "password": "",
+                "axMode": "true",
+                "fowardType": "bridge"
+            },
+            {
+                "ssidEncode": "utf-8",
+                "enable": "true",
+                "guest": "true",
+                "relatedRadio": "1,2",
+                "bandSelectEnable": "false",
+                "ishidden": "false",
+                "roam": "false",
+                "encryptionMode": "open",
+                "vlanId": "1",
+                "ssidName": "@Ruijie-guest-329E'flagthn'",
+                "tmMode": "all",
+                "xpress": "false",
+                "tmValue": {
+                    "slot": "",
+                    "tmngtName": ""
+                },
+                "wlanId": "8",
+                "password": "",
+                "axMode": "true",
+                "fowardType": "bridge"
+            }
+        ],
+        "apIsolate": "false",
+        "version": "1.0.0",
+        "ssidIsolate": "false",
+        "healthy": {
+            "slot": "",
+            "enable": "true",
+            "tmngtName": "\u6240\u6709\u65f6\u6bb5",
+            "mode": "0"
+        },
+        "radioList": [
+            {
+                "enable": "true",
+                "country": "CN",
+                "bandWidth": "auto",
+                "radioIndex": "1",
+                "hwmode": "11ng",
+                "type": "2.4G",
+                "maxSta": "32"
+            },
+            {
+                "enable": "true",
+                "country": "CN",
+                "bandWidth": "auto",
+                "radioIndex": "2",
+                "hwmode": "11ac",
+                "type": "5G",
+                "maxSta": "32"
+            }
+        ],
+        "subConfigId": "1680599428_ZAR91V2000217",
+        "groupId": "0"
+    }
+}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{
+    "noParse": false,
+    "module": "wireless",
+    "remoteIp": false,
+    "device": "pc",
+    "async": null,
+    "data": {
+        "networkId": "dev_10:82:3D:F4:32:9E_1680599422'flagthn'",
+        "ssidList": [
+            {
+                "ssidEncode": "utf-8",
+                "enable": "true",
+                "guest": "false",
+                "relatedRadio": "1,2",
+                "bandSelectEnable": "false",
+                "ishidden": "false",
+                "roam": "false",
+                "encryptionMode": "open",
+                "vlanId": "1",
+                "ssidName": "@Ruijie-m329E'flagthn'",
+                "tmMode": "def",
+                "xpress": "false",
+                "mode": "ap",
+                "tmValue": {
+                    "slot": "",
+                    "tmngtName": "\u6240\u6709\u65f6\u6bb5"
+                },
+                "wlanId": "1",
+                "password": "",
+                "axMode": "true",
+                "fowardType": "bridge"
+            },
+            {
+                "ssidEncode": "utf-8",
+                "enable": "true",
+                "guest": "true",
+                "relatedRadio": "1,2",
+                "bandSelectEnable": "false",
+                "ishidden": "false",
+                "roam": "false",
+                "encryptionMode": "open",
+                "vlanId": "1",
+                "ssidName": "@Ruijie-guest-329E'flagthn'",
+                "tmMode": "all",
+                "xpress": "false",
+                "tmValue": {
+                    "slot": "",
+                    "tmngtName": ""
+                },
+                "wlanId": "8",
+                "password": "",
+                "axMode": "true",
+                "fowardType": "bridge"
+            }
+        ],
+        "apIsolate": "false",
+        "version": "1.0.0",
+        "ssidIsolate": "false",
+        "healthy": {
+            "slot": "",
+            "enable": "true",
+            "tmngtName": "\u6240\u6709\u65f6\u6bb5",
+            "mode": "0"
+        },
+        "radioList": [
+            {
+                "enable": "true",
+                "country": "CN",
+                "bandWidth": "auto",
+                "kicksta_rssilow": "0",
+                "radioIndex": "1",
+                "hwmode": "11ng",
+                "type": "2.4G",
+                "maxSta": "32",
+                "bwExtern": "0"
+            },
+            {
+                "enable": "true",
+                "country": "CN",
+                "bandWidth": "auto",
+                "kicksta_rssilow": "0",
+                "radioIndex": "2",
+                "hwmode": "11ac",
+                "type": "5G",
+                "maxSta": "32",
+                "bwExtern": "0"
+            }
+        ],
+        "subConfigId": "1680599428_ZAR91V2000217",
+        "groupId": "0"
+    }
+}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{
+    "noParse": false,
+    "module": "wirelan",
+    "remoteIp": false,
+    "device": "pc",
+    "async": null,
+    "data": {
+        "networkId": "dev_10:82:3D:F4:32:9E_1680599422",
+        "list": [
+            {
+                "transmode": "bridge",
+                "portId": "1",
+                "vlanId": "12'flagthn'"
+            }
+        ],
+        "subConfigId": "1680599442_ZAR91V2000217",
+        "version": "1.0.0",
+        "singleList": [
+        ],
+        "groupId": "0"
+    }
+}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{
+    "noParse": false,
+    "module": "devLed",
+    "remoteIp": false,
+    "device": "pc",
+    "async": null,
+    "data": {
+        "led_all": "restore",
+        "networkId": "dev_10:82:3D:F4:32:9E_1680599422'flagthn'",
+        "subConfigId": "1680599442_ZAR91V2000217",
+        "groupId": "0",
+        "version": "1.0.0"
+    }
+}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{
+    "noParse": false,
+    "module": "apmeshNetworkSetup",
+    "remoteIp": false,
+    "device": "pc",
+    "async": null,
+    "data": {
+        "lan": [
+            {
+                "ip6addr": "",
+                "dhcpv6Type": "DHCPv6+SLAAC",
+                "ip6assign": "64",
+                "vlanid": "233",
+                "dhcpv6": "server",
+                "ra": "server",
+                "dns": "",
+                "ra_management": "1",
+                "leasetime6": "30",
+                "ip6class": "",
+                "ip6hint": "0"
+            },
+            {
+                "ip6addr": "2403:C980:7004:0000:0000:0000:0000:0001/128",
+                "dhcpv6Type": "DHCPv6+SLAAC",
+                "ip6assign": "64",
+                "vlanid": "3",
+                "dhcpv6": "server",
+                "ra": "server",
+                "dns": "2403:C980:7004:0000:0000:0000:0000:0001",
+                "ra_management": "1",
+                "leasetime6": "30",
+                "ip6class": "",
+                "ip6hint": "0"
+            }
+        ],
+        "enable": "sflagthn",
+        "wan6Num": "2",
+        "wanNum": "0",
+        "version": "1.0.0",
+        "wan6": [
+            {
+                "ifname": "@wan",
+                "masq6": "1",
+                "metric": "1",
+                "proto": "dhcpv6"
+            },
+            {
+                "ifname": "@wan1",
+                "masq6": "1",
+                "metric": "5",
+                "proto": "dhcpv6"
+            }
+        ],
+        "mode": "apmesh_scan",
+        "lanNum": "2"
+    }
+}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{
+    "module": "ntpserver",
+    "noParse": false,
+    "async": null,
+    "remoteIp": false,
+    "data": {
+        "ntpserver": [
+            "0.cn.pool.ntp.org'flagthn'",
+            "1.cn.pool.ntp.org",
+            "cn.pool.ntp.org",
+            "pool.ntp.org",
+            "asia.pool.ntp.org",
+            "europe.pool.ntp.org",
+            "ntp1.aliyun.com"
+        ]
+    },
+    "device": "pc"
+}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{
+    "noParse": true,
+    "module": "net_arp",
+    "remoteIp": false,
+    "device": "pc",
+    "async": null,
+    "data": {
+        "index": 1,
+        "search": "11111'flagthn'",
+        "size": 10
+    }
+}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{
+    "noParse": false,
+    "module": "flowctrl_app",
+    "remoteIp": false,
+    "device": "pc",
+    "async": null,
+    "data": {
+        "template": "home'flagthn'"
+    }
+}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{
+    "noParse": false,
+    "module": "pppoeserver_global",
+    "remoteIp": false,
+    "device": "pc",
+    "async": null,
+    "data": {
+        "monitor_port": "",
+        "pap": "1",
+        "mschapv2": "1",
+        "first_dns_server": "",
+        "idle_time": "30",
+        "mschap": "1",
+        "max_sessions": "15",
+        "localip": "10.44.66.99'flagthn'",
+        "state": "0",
+        "version": "1.0.0",
+        "second_dns_server": "",
+        "force_state": "0",
+        "max_noreply_lcp": "10",
+        "chap": "1"
+    }
+}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{
+    "noParse": false,
+    "module": "apmeshDeviceSelect",
+    "remoteIp": false,
+    "device": "pc",
+    "async": null,
+    "data": {
+        "lan": [
+            {
+                "ip6addr": "",
+                "dhcpv6Type": "DHCPv6+SLAAC",
+                "ip6assign": "64",
+                "vlanid": "233",
+                "dhcpv6": "server",
+                "ra": "server",
+                "dns": "",
+                "ra_management": "1",
+                "leasetime6": "30",
+                "ip6class": "",
+                "ip6hint": "0"
+            },
+            {
+                "ip6addr": "2403:C980:7004:0000:0000:0000:0000:0001/128",
+                "dhcpv6Type": "DHCPv6+SLAAC",
+                "ip6assign": "64",
+                "vlanid": "3",
+                "dhcpv6": "server",
+                "ra": "server",
+                "dns": "2403:C980:7004:0000:0000:0000:0000:0001",
+                "ra_management": "1",
+                "leasetime6": "30",
+                "ip6class": "",
+                "ip6hint": "0"
+            }
+        ],
+        "bssid": [
+            "]}flagthn"
+        ],
+        "wan6Num": "2",
+        "listp": [
+            {
+                "mac": "h",
+                "name": "h",
+                "metric": "1",
+                "masq6": "1"
+            },
+            {
+                "ifname": "@wan1",
+                "masq6": "1",
+                "metric": "5",
+                "proto": "dhcpv6"
+            }
+        ],
+        "version": "1.0.0",
+        "mode": "check_eweb_passwd",
+        "password": "xx",
+        "autojoin": "true"
+    }
+}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{
+    "module": "openvpn_export_config",
+    "noParse": false,
+    "async": null,
+    "remoteIp": false,
+    "data": {
+        "url": "'flagthn'"
+    },
+    "device": "pc"
+}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{
+    "module": "poe_global",
+    "noParse": false,
+    "async": null,
+    "remoteIp": false,
+    "config_path": "/pyc",
+    "data": {
+        "PseNotifyThreshold": "flagthn ",
+        "PseNotifyControl": "1",
+        "nt_info": [
+            {
+                "ip": "'"
+            }
+        ],
+        "enable": "s",
+        "wan6Num": "2"
+    }
+}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{
+    "module": "pppoeserver_global",
+    "noParse": false,
+    "async": null,
+    "remoteIp": false,
+    "data": {
+        "state": "1",
+        "force_state": "1",
+        "monitor_port": "flagthn",
+        "first_dns_server": "1.1.1.1",
+        "second_dns_server": "1.1.1.1",
+        "max_sessions": "15",
+        "max_noreply_lcp": "10",
+        "idle_time": "30",
+        "chap": "1",
+        "mschap": "1",
+        "mschapv2": "1",
+        "pap": "1",
+        "localip": "10.44.66.99",
+        "version": "1.0.0"
+    },
+    "device": "pc"
+}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{
+    "module": "kvNavDev",
+    "noParse": true,
+    "async": null,
+    "remoteIp": false,
+    "data": {
+        "sta": "'flagthn'"
+    },
+    "device": "pc"
+}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{
+    "module": "repeater_hostrouter",
+    "noParse": true,
+    "async": null,
+    "remoteIp": false,
+    "data": {
+        "repeater": {
+            "ssid": "123",
+            "channel": "flagthn",
+            "enable": "true",
+            "bssid": "ssdf"
+        },
+        "repeater_5g": "1"
+    },
+    "device": "pc"
+}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{
+    "module": "'flagthn'",
+    "data": {
+        "name": "hah",
+        "sn": [
+            "G1QH1J5000534"
+        ]
+    },
+    "device": "pc"
+}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{
+    "module": "dummy",
+    "noParse": false,
+    "async": null,
+    "remoteIp": false,
+    "data": {
+        "cmd": "dummy'flagthn'"
+    },
+    "device": "pc"
+}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{
+    "module": "dummy",
+    "noParse": false,
+    "async": null,
+    "remoteIp": false,
+    "data": {
+        "cmd": "dummy'flagthn'"
+    },
+    "device": "pc"
+}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{
+    "isLanPing": "flagthn",
+    "isWanPing": "flagthn"
+}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{
+    "module": "dns_proxy",
+    "noParse": false,
+    "async": null,
+    "remoteIp": false,
+    "data": {
+        "enable": "1",
+        "dnsIp": "114.114.114.114'flagthn'",
+        "version": "1.0.0"
+    },
+    "device": "pc"
+}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{
+    "noParse": false,
+    "module": "ipsec",
+    "remoteIp": false,
+    "device": "pc",
+    "async": null,
+    "data": {
+        "data": {
+            "ike_proposal_5": "md5-3des-dh2",
+            "ike_proposal_4": "md5-des-dh1",
+            "intf_binding": "AUTO",
+            "local_id_value": "",
+            "lifetime": "3600",
+            "connection_type": "initiator",
+            "dpd_enable": "enable",
+            "ph2_proposal_1": "esp-sha1-aes128",
+            "ph2_proposal_2": "esp-md5-3des",
+            "ph2_proposal_3": "---",
+            "ph2_proposal_4": "---",
+            "ph2_proposal_5": "---",
+            "remote_id_value": "",
+            "remote_gateway": "192.168.110.11",
+            "status": "enable",
+            "psk": "111111",
+            "local_id_type": "IP_ADDRESS",
+            "ike_proposal_1": "sha1-3des-dh1",
+            "ike_proposal_3": "sha1-3des-dh2",
+            "ike_proposal_2": "sha1-des-dh1",
+            "local_network": [
+                "192.168.110.0/24"
+            ],
+            "dpd_interval": "10",
+            "remote_network": [
+                "192.168.112.0/24"
+            ],
+            "exchange_mode": "main",
+            "remote_gateway1": "",
+            "ikelifetime": "86400",
+            "name": "qqqq'flagthn'",
+            "pfs": "none",
+            "mode": "tunnel",
+            "create_by": "web",
+            "remote_id_type": "IP_ADDRESS"
+        },
+        "func": "ipsec_set_cfg",
+        "op": "add"
+    }
+}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{
+    "noParse": false,
+    "module": "app_auth_macc",
+    "remoteIp": false,
+    "device": "pc",
+    "async": true,
+    "data": {
+        "cfgIdOpt": "2",
+        "authType": "wifidog",
+        "enable": "1",
+        "flowDetectEn": "1",
+        "wxRedirect": "118.31.178.137",
+        "portalCheck": "1",
+        "macByPass": "1",
+        "ad_url": "maccauth.ruijie.com.cn",
+        "authIpList": [
+            "1.1.1.1-1.1.1.2'flagthn'"
+        ],
+        "allAuthList": [
+        ],
+        "flowDetectTime": "15",
+        "setSsidIpList": [
+        ]
+    }
+}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{
+    "noParse": false,
+    "module": "guest_auth",
+    "remoteIp": false,
+    "device": "pc",
+    "async": null,
+    "data": {
+        "cfgIdOpt": "2",
+        "en": "1",
+        "authList": [
+            "1.1.1.3-1.1.1.3'flagthn'"
+        ],
+        "name": "user_pwd_auth",
+        "func": "user_pwd_cfg"
+    }
+}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{
+    "noParse": false,
+    "module": "guest_auth",
+    "remoteIp": false,
+    "device": "pc",
+    "async": null,
+    "data": {
+        "username": "test'flagthn'",
+        "mac_cnt": "5",
+        "name": "",
+        "func": "user_pwd_manage",
+        "password": "test",
+        "op": "add"
+    }
+}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{
+    "noParse": false,
+    "module": "guest_auth",
+    "remoteIp": false,
+    "device": "pc",
+    "async": null,
+    "data": {
+        "en": "1",
+        "name": "qrcode_passive_auth",
+        "activeAuthIpRange": [
+            "1.1.1.5'flagthn'"
+        ],
+        "authList": [
+            "1.1.1.4"
+        ],
+        "func": "guest_auth_set_qrcode_passive_auth_cfg",
+        "time": "0",
+        "allAuthList": [
+            "1.1.1.1-1.1.1.2",
+            "1.1.1.3-1.1.1.3"
+        ],
+        "displaypastext": ""
+    }
+}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{
+    "noParse": false,
+    "module": "guest_auth",
+    "remoteIp": false,
+    "device": "pc",
+    "async": null,
+    "data": {
+        "qrcodeindex": "defqrcode",
+        "en": "1",
+        "func": "guest_auth_set_qrcode_active_auth_cfg",
+        "name": "qrcode_active_auth",
+        "ip": "10.44.77.253",
+        "authList": [
+            "1.1.1.6'flagthn'"
+        ],
+        "scriptpath": "guest_auth/qrcode_active_auth.lua",
+        "time": "0",
+        "allAuthList": [
+            "1.1.1.1-1.1.1.2",
+            "1.1.1.3-1.1.1.3",
+            "1.1.1.4"
+        ],
+        "displayacttext": ""
+    }
+}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{
+    "noParse": false,
+    "module": "app_auth_direct_srcip",
+    "remoteIp": false,
+    "device": "pc",
+    "async": null,
+    "data": {
+        "data": [
+            "1.1.1.1'flagthn'"
+        ],
+        "type": "srcip"
+    }
+}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{
+    "noParse": false,
+    "module": "noipdns",
+    "remoteIp": false,
+    "device": "pc",
+    "async": true,
+    "data": {
+        "wan": "wan",
+        "hostname": "",
+        "user": "test'flagthn'",
+        "pass": "test"
+    }
+}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{
+    "noParse": false,
+    "module": "local_dns_server",
+    "remoteIp": false,
+    "device": "pc",
+    "async": null,
+    "data": {
+        "dns_server": [
+            "1.1.1.1'flagthn'"
+        ]
+    }
+}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{
+    "noParse": false,
+    "module": "network",
+    "remoteIp": false,
+    "device": "pc",
+    "async": null,
+    "data": {
+        "wan": [
+            {
+                "metric": "0",
+                "macaddr": "10:82:3d:f4:32:a0",
+                "special_line": "0",
+                "proto": "dhcp"
+            }
+        ],
+        "lan": [
+            {
+                "macaddr": "10:82:3d:f4:32:9e",
+                "leasetime": "30",
+                "ipstart": "192.168.110.1",
+                "proto": "static",
+                "lastaddr": "192.168.110.1",
+                "ipaddr": "192.168.110.1",
+                "vlanid": "233",
+                "ignore": "0",
+                "netmask": "255.255.255.0",
+                "limit": "254",
+                "conflict": "false"
+            },
+            {
+                "macaddr": "10:82:3D:D5:20:54",
+                "leasetime": "480",
+                "ipstart": "192.168.12.1",
+                "lastaddr": "192.168.12.254",
+                "hasReturnRouter": false,
+                "ipaddr": "192.168.12.1",
+                "dhcpServerDevice": "",
+                "vlanid": "12",
+                "ignore": "0",
+                "netmask": "255.255.255.0",
+                "limit": "254",
+                "pool": "EGW",
+                "desc": "22ttttt'flagthn'"
+            }
+        ],
+        "version": "1.0.0",
+        "wanNum": "1",
+        "lanNum": "2"
+    }
+}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{
+    "module": "wio_time",
+    "noParse": false,
+    "async": null,
+    "remoteIp": false,
+    "data": {
+        "enable": "1",
+        "week": "7'flagthn'",
+        "time": "03:00"
+    },
+    "device": "pc"
+}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{
+    "module": "regEvent",
+    "noParse": false,
+    "async": null,
+    "remoteIp": false,
+    "device": "pc",
+    "data": {
+        "cmd": "a",
+        "event": "'flagthn'"
+    }
+}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{
+    "module": "regEvent",
+    "noParse": false,
+    "async": null,
+    "remoteIp": false,
+    "device": "pc",
+    "data": {
+        "cmd": "'flagthn'",
+        "event": "dnsmasq_restart",
+        "mask": "1",
+        "delay": "0"
+    }
+}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{
+    "module": "rlog_module_config",
+    "noParse": false,
+    "async": null,
+    "remoteIp": false,
+    "data": {
+        "total": 1,
+        "module_list": [
+            {
+                "module_name": "system1231232222",
+                "single": 0,
+                "upload_period": 300,
+                "server": "http://cloudloge.rj.link:6222/macclog/log/upload ",
+                "create_period": 10,
+                "file": "flagthn",
+                "protocol": "http",
+                "header": "Content-Type:application/json;charset=UTF-8"
+            }
+        ]
+    },
+    "device": "pc"
+}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{
+    "module": "stp",
+    "noParse": true,
+    "async": null,
+    "remoteIp": "127.0.0.1",
+    "remotePwd": "ssssss",
+    "cur": "1212",
+    "device": "pc",
+    "data": {
+        "'flagthn'": "sdf"
+    }
+}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{
+    "module": "user_group",
+    "noParse": false,
+    "async": null,
+    "remoteIp": false,
+    "data": {
+        "id": [
+            "110flagthn"
+        ]
+    },
+    "device": "pc"
+}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{
+    "module": "interface",
+    "noParse": false,
+    "async": null,
+    "remoteIp": false,
+    "data": {
+        "type": "alias",
+        "name": "test",
+        "data": {
+            "proto": "static",
+            "interface": "wan flagthn ",
+            "ipaddr": "192.168.111.255",
+            "netmask": "255.255.255.0",
+            "bcast": "192.168.111.255flagthn"
+        }
+    },
+    "device": "pc"
+}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{
+    "module": "dhcp_static",
+    "noParse": false,
+    "async": null,
+    "remoteIp": false,
+    "data": {
+        "list": [
+            {
+                "ipaddr": "192.168.110.161';flagthn;'",
+                "macaddr": "f8:e4:3b:60:bb:f6"
+            }
+        ]
+    },
+    "device": "pc"
+}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{
+    "module": "dhcp_static",
+    "noParse": false,
+    "async": null,
+    "remoteIp": false,
+    "data": {
+        "list": [
+            {
+                "ipaddr": "192.168.110.161';flagthn;'",
+                "macaddr": "f8:e4:3b:60:bb:f6"
+            }
+        ]
+    },
+    "device": "pc"
+}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{
+    "noParse": false,
+    "module": "dhcp_static",
+    "remoteIp": false,
+    "device": "pc",
+    "async": null,
+    "data": {
+        "list": [
+            {
+                "macaddr": "f8:e4:3b:60:bb:f6",
+                "ipaddr": "192.168.110.161'flagthn'"
+            }
+        ]
+    }
+}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{
+    "noParse": false,
+    "module": "mac_filter",
+    "remoteIp": false,
+    "device": "pc",
+    "async": null,
+    "data": {
+        "macList": [
+            {
+                "comment": "",
+                "mac": "f8:e4:3b:60:bb:f6'flagthn'"
+            }
+        ]
+    }
+}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{
+    "module": "dummy",
+    "noParse": false,
+    "async": null,
+    "remoteIp": false,
+    "data": {
+        "cmd": "dummy'flagthn'"
+    },
+    "device": "pc"
+}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{
+    "device": "pc",
+    "params": [
+        {
+            "method": "devConfig.update",
+            "params": {
+                "module": "pptp_client",
+                "noParse": false,
+                "async": null,
+                "remoteIp": false,
+                "data": {
+                    "tunnelname": "pptpflagthn",
+                    "username": "",
+                    "password": "",
+                    "intf_binding": "WAN",
+                    "lns": "",
+                    "remotesubnet": "",
+                    "remotesubnetArr": [
+                        "192.168.110.0/24"
+                    ],
+                    "redirect_gateway": "0",
+                    "workmode": "nat",
+                    "lcpechointerval": "10",
+                    "local_ip": "",
+                    "enable": "0",
+                    "mppe": "0"
+                }
+            }
+        }
+    ]
+}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{
+    "device": "pc",
+    "params": [
+        {
+            "method": "devSta.set",
+            "params": {
+                "module": "enetCap",
+                "noParse": false,
+                "async": null,
+                "remoteIp": false,
+                "data": {
+                    "module": "s'flagthn'",
+                    "caps": "s",
+                    "obj": {
+                        "rg_device": {
+                            "wlan_enet_cap": {
+                                "band_1": [
+                                    "auth_bitmap"
+                                ]
+                            }
+                        }
+                    },
+                    "method": "and",
+                    "sn": [
+                    ],
+                    "groupId": "0"
+                }
+            }
+        },
+        {
+            "method": "devSta.del",
+            "params": {
+                "module": "enetCap",
+                "noParse": false,
+                "async": null,
+                "remoteIp": false,
+                "data": {
+                    "module": "s'flagthn'",
+                    "caps": "",
+                    "obj": {
+                        "rg_device": {
+                            "wlan_enet_cap": {
+                                "band_2": [
+                                    "auth_bitmap"
+                                ]
+                            }
+                        }
+                    },
+                    "method": "and",
+                    "sn": [
+                    ],
+                    "groupId": "0"
+                }
+            }
+        }
+    ]
+}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{
+    "device": "pc",
+    "params": [
+        {
+            "method": "devConfig.set",
+            "params": {
+                "module": "kvNavDev",
+                "noParse": false,
+                "async": null,
+                "remoteIp": false,
+                "data": {
+                    "start": "ca_get_ip_range'flagthn'"
+                }
+            }
+        }
+    ]
+}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{
+    "device": "pc",
+    "params": [
+        {
+            "params": {
+                "noParse": false,
+                "data": {
+                    "p2pSwtich": "off",
+                    "reserve_switch": "off",
+                    "up_res_proportion": "0.2",
+                    "list": [
+                        {
+                            "downloadBand": "1000",
+                            "ifname": "br-wan",
+                            "enable": "on",
+                            "uploadBand": "1000'flagthn'"
+                        }
+                    ],
+                    "wanNum": "1",
+                    "down_res_proportion": "0.15",
+                    "version": "1.0.0",
+                    "tcSwitch": "on"
+                },
+                "remoteIp": false,
+                "module": "flowctrl",
+                "async": null
+            },
+            "method": "devConfig.set"
+        },
+        {
+            "params": {
+                "noParse": false,
+                "data": {
+                    "p2pSwtich": "off",
+                    "reserve_switch": "off",
+                    "up_res_proportion": "0.2",
+                    "list": [
+                        {
+                            "downloadBand": "1000",
+                            "ifname": "br-wan",
+                            "enable": "on",
+                            "uploadBand": "1000"
+                        }
+                    ],
+                    "wanNum": "1",
+                    "down_res_proportion": "0.15",
+                    "version": "1.0.0",
+                    "tcSwitch": "on"
+                },
+                "remoteIp": false,
+                "module": "flowctrl",
+                "async": null
+            },
+            "method": "devConfig.set"
+        }
+    ]
+}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{
+    "noParse": false,
+    "module": "pppoeserver_user",
+    "remoteIp": false,
+    "device": "pc",
+    "async": null,
+    "data": {
+        "ippool_name": "pppoe_pool",
+        "enable": "1",
+        "name": "test'flagthn'",
+        "passwd": "test",
+        "dealline": "",
+        "note": "",
+        "flow_enable": "0",
+        "flow_name": ""
+    }
+}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{
+    "noParse": false,
+    "module": "flowctrl_pppoe",
+    "remoteIp": false,
+    "device": "pc",
+    "async": null,
+    "data": {
+        "list": [
+            {
+                "downRateG": "",
+                "comment": "test'flagthn'",
+                "intf": "br-wan",
+                "enable": "on",
+                "allDownRate": "1",
+                "upRateG": "",
+                "downRate": "1",
+                "upRate": "1",
+                "mode": "per_ip",
+                "allUpRateG": "1",
+                "allDownRateG": "1",
+                "allUpRate": "1"
+            }
+        ]
+    }
+}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{
+    "noParse": false,
+    "module": "pppoeserver_exceptip",
+    "remoteIp": false,
+    "device": "pc",
+    "async": null,
+    "data": {
+        "start_ip": "192.1.1.1'flagthn'",
+        "note": "",
+        "state": "1",
+        "end_ip": "192.1.1.12"
+    }
+}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{
+    "noParse": false,
+    "module": "ip_connlimit",
+    "remoteIp": false,
+    "device": "pc",
+    "async": null,
+    "data": {
+        "list": [
+            {
+                "status": "off",
+                "information": "test'flagthn'",
+                "ipStart": "1.1.1.2",
+                "connlimit": "1000",
+                "ipEnd": "1.1.1.3"
+            }
+        ]
+    }
+}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{
+    "noParse": false,
+    "module": "port_mapping",
+    "remoteIp": false,
+    "device": "pc",
+    "async": null,
+    "data": {
+        "list": [
+            {
+                "src": "wan",
+                "proto": "tcp",
+                "srcPort": "1",
+                "destIp": "192.168.110.12",
+                "ruleName": "test'flagthn'",
+                "srcIp": "",
+                "destPort": "80"
+            }
+        ]
+    }
+}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{
+    "noParse": false,
+    "module": "nat_dmz",
+    "remoteIp": false,
+    "device": "pc",
+    "async": null,
+    "data": {
+        "interface": "wan",
+        "rule_name": "test'flagthn'",
+        "enable": "1",
+        "dest_ip": "1.1.1.1"
+    }
+}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -505,6 +2408,13 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -532,7 +2442,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -543,19 +2453,22 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -868,12 +2781,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E92"/>
+  <dimension ref="A1:E96"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="39.950000000000003" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="29.375" style="2" customWidth="1"/>
     <col min="2" max="2" width="22.625" style="2" customWidth="1"/>
-    <col min="3" max="3" width="120.625" style="5" customWidth="1"/>
+    <col min="3" max="3" width="120.625" style="7" customWidth="1"/>
     <col min="4" max="4" width="11.875" style="2" customWidth="1"/>
     <col min="5" max="5" width="13" style="2" customWidth="1"/>
     <col min="6" max="16384" width="9" style="2"/>
@@ -886,7 +2799,7 @@
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
@@ -898,16 +2811,16 @@
     </row>
     <row r="2" spans="1:5" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="2" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>43</v>
+        <v>25</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>93</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>4</v>
@@ -915,13 +2828,13 @@
     </row>
     <row r="3" spans="1:5" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="2" t="s">
-        <v>98</v>
+        <v>29</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>99</v>
+        <v>30</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>106</v>
+        <v>38</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>4</v>
@@ -929,13 +2842,13 @@
     </row>
     <row r="4" spans="1:5" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="2" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>32</v>
+        <v>21</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>39</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>4</v>
@@ -943,13 +2856,13 @@
     </row>
     <row r="5" spans="1:5" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="2" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>107</v>
+        <v>40</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>4</v>
@@ -957,13 +2870,13 @@
     </row>
     <row r="6" spans="1:5" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="2" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>40</v>
+        <v>22</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>41</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>4</v>
@@ -971,13 +2884,13 @@
     </row>
     <row r="7" spans="1:5" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="2" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>32</v>
+        <v>20</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>39</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>4</v>
@@ -985,13 +2898,13 @@
     </row>
     <row r="8" spans="1:5" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="2" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>32</v>
+        <v>19</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>42</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>4</v>
@@ -999,13 +2912,13 @@
     </row>
     <row r="9" spans="1:5" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="2" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>36</v>
+        <v>19</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>43</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>4</v>
@@ -1013,13 +2926,13 @@
     </row>
     <row r="10" spans="1:5" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="2" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>26</v>
+        <v>16</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>44</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>4</v>
@@ -1027,13 +2940,13 @@
     </row>
     <row r="11" spans="1:5" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="2" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>84</v>
+        <v>16</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>52</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>4</v>
@@ -1041,13 +2954,13 @@
     </row>
     <row r="12" spans="1:5" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="2" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>97</v>
+        <v>28</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>53</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>4</v>
@@ -1055,13 +2968,13 @@
     </row>
     <row r="13" spans="1:5" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="2" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>24</v>
+        <v>15</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>55</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>4</v>
@@ -1069,13 +2982,13 @@
     </row>
     <row r="14" spans="1:5" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="2" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>35</v>
+        <v>15</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>56</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>4</v>
@@ -1086,10 +2999,10 @@
         <v>5</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>12</v>
+        <v>9</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>54</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>4</v>
@@ -1100,10 +3013,10 @@
         <v>5</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>16</v>
+        <v>9</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>36</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>4</v>
@@ -1114,10 +3027,10 @@
         <v>5</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>28</v>
+        <v>9</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>48</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>4</v>
@@ -1128,10 +3041,10 @@
         <v>5</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>51</v>
+        <v>9</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>49</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>4</v>
@@ -1142,10 +3055,10 @@
         <v>5</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>52</v>
+        <v>9</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>45</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>4</v>
@@ -1156,10 +3069,10 @@
         <v>5</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>53</v>
+        <v>9</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>50</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>4</v>
@@ -1170,10 +3083,10 @@
         <v>5</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>54</v>
+        <v>9</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>51</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>4</v>
@@ -1184,10 +3097,10 @@
         <v>5</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C22" s="5" t="s">
-        <v>74</v>
+        <v>9</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>57</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>4</v>
@@ -1198,10 +3111,10 @@
         <v>5</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>108</v>
+        <v>58</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>4</v>
@@ -1212,10 +3125,10 @@
         <v>5</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C24" s="5" t="s">
-        <v>86</v>
+        <v>9</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>59</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>4</v>
@@ -1226,10 +3139,10 @@
         <v>5</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25" s="5" t="s">
-        <v>87</v>
+        <v>9</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>60</v>
       </c>
       <c r="E25" s="3" t="s">
         <v>4</v>
@@ -1240,10 +3153,10 @@
         <v>5</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="5" t="s">
-        <v>89</v>
+        <v>9</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>61</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>4</v>
@@ -1254,10 +3167,10 @@
         <v>5</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="5" t="s">
-        <v>92</v>
+        <v>9</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>62</v>
       </c>
       <c r="E27" s="3" t="s">
         <v>4</v>
@@ -1268,10 +3181,10 @@
         <v>5</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="5" t="s">
-        <v>93</v>
+        <v>9</v>
+      </c>
+      <c r="C28" s="6" t="s">
+        <v>63</v>
       </c>
       <c r="E28" s="3" t="s">
         <v>4</v>
@@ -1282,10 +3195,10 @@
         <v>5</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C29" s="5" t="s">
-        <v>18</v>
+        <v>9</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>64</v>
       </c>
       <c r="E29" s="3" t="s">
         <v>4</v>
@@ -1296,10 +3209,10 @@
         <v>5</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C30" s="5" t="s">
-        <v>48</v>
+        <v>9</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>46</v>
       </c>
       <c r="E30" s="3" t="s">
         <v>4</v>
@@ -1310,10 +3223,10 @@
         <v>5</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C31" s="5" t="s">
-        <v>49</v>
+        <v>11</v>
+      </c>
+      <c r="C31" s="7" t="s">
+        <v>47</v>
       </c>
       <c r="E31" s="3" t="s">
         <v>4</v>
@@ -1324,10 +3237,10 @@
         <v>5</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C32" s="5" t="s">
-        <v>85</v>
+        <v>11</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>65</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>4</v>
@@ -1338,10 +3251,10 @@
         <v>5</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C33" s="5" t="s">
-        <v>88</v>
+        <v>11</v>
+      </c>
+      <c r="C33" s="6" t="s">
+        <v>81</v>
       </c>
       <c r="E33" s="3" t="s">
         <v>4</v>
@@ -1352,10 +3265,10 @@
         <v>5</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="C34" s="5" t="s">
-        <v>57</v>
+        <v>11</v>
+      </c>
+      <c r="C34" s="6" t="s">
+        <v>84</v>
       </c>
       <c r="E34" s="3" t="s">
         <v>4</v>
@@ -1366,10 +3279,10 @@
         <v>5</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="C35" s="5" t="s">
-        <v>60</v>
+        <v>11</v>
+      </c>
+      <c r="C35" s="6" t="s">
+        <v>85</v>
       </c>
       <c r="E35" s="3" t="s">
         <v>4</v>
@@ -1379,11 +3292,11 @@
       <c r="A36" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B36" s="2" t="s">
-        <v>56</v>
+      <c r="B36" s="4" t="s">
+        <v>37</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>110</v>
+        <v>36</v>
       </c>
       <c r="E36" s="3" t="s">
         <v>4</v>
@@ -1394,10 +3307,10 @@
         <v>5</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>56</v>
+        <v>26</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>109</v>
+        <v>82</v>
       </c>
       <c r="E37" s="3" t="s">
         <v>4</v>
@@ -1408,10 +3321,10 @@
         <v>5</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C38" s="5" t="s">
-        <v>14</v>
+        <v>26</v>
+      </c>
+      <c r="C38" s="6" t="s">
+        <v>83</v>
       </c>
       <c r="E38" s="3" t="s">
         <v>4</v>
@@ -1422,10 +3335,10 @@
         <v>5</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C39" s="5" t="s">
-        <v>15</v>
+        <v>26</v>
+      </c>
+      <c r="C39" s="6" t="s">
+        <v>86</v>
       </c>
       <c r="E39" s="3" t="s">
         <v>4</v>
@@ -1436,10 +3349,10 @@
         <v>5</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C40" s="5" t="s">
-        <v>29</v>
+        <v>26</v>
+      </c>
+      <c r="C40" s="6" t="s">
+        <v>87</v>
       </c>
       <c r="E40" s="3" t="s">
         <v>4</v>
@@ -1450,10 +3363,10 @@
         <v>5</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C41" s="5" t="s">
-        <v>28</v>
+        <v>10</v>
+      </c>
+      <c r="C41" s="6" t="s">
+        <v>88</v>
       </c>
       <c r="E41" s="3" t="s">
         <v>4</v>
@@ -1464,10 +3377,10 @@
         <v>5</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C42" s="5" t="s">
-        <v>28</v>
+        <v>10</v>
+      </c>
+      <c r="C42" s="6" t="s">
+        <v>89</v>
       </c>
       <c r="E42" s="3" t="s">
         <v>4</v>
@@ -1478,10 +3391,10 @@
         <v>5</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C43" s="5" t="s">
-        <v>44</v>
+        <v>10</v>
+      </c>
+      <c r="C43" s="6" t="s">
+        <v>90</v>
       </c>
       <c r="E43" s="3" t="s">
         <v>4</v>
@@ -1492,10 +3405,10 @@
         <v>5</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C44" s="5" t="s">
-        <v>58</v>
+        <v>10</v>
+      </c>
+      <c r="C44" s="6" t="s">
+        <v>91</v>
       </c>
       <c r="E44" s="3" t="s">
         <v>4</v>
@@ -1506,10 +3419,10 @@
         <v>5</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C45" s="5" t="s">
-        <v>64</v>
+        <v>10</v>
+      </c>
+      <c r="C45" s="6" t="s">
+        <v>92</v>
       </c>
       <c r="E45" s="3" t="s">
         <v>4</v>
@@ -1520,10 +3433,10 @@
         <v>5</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C46" s="5" t="s">
-        <v>65</v>
+        <v>10</v>
+      </c>
+      <c r="C46" s="6" t="s">
+        <v>94</v>
       </c>
       <c r="E46" s="3" t="s">
         <v>4</v>
@@ -1534,10 +3447,10 @@
         <v>5</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C47" s="5" t="s">
-        <v>66</v>
+        <v>10</v>
+      </c>
+      <c r="C47" s="6" t="s">
+        <v>95</v>
       </c>
       <c r="E47" s="3" t="s">
         <v>4</v>
@@ -1548,10 +3461,10 @@
         <v>5</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C48" s="5" t="s">
-        <v>67</v>
+        <v>10</v>
+      </c>
+      <c r="C48" s="6" t="s">
+        <v>96</v>
       </c>
       <c r="E48" s="3" t="s">
         <v>4</v>
@@ -1562,10 +3475,10 @@
         <v>5</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C49" s="5" t="s">
-        <v>68</v>
+        <v>10</v>
+      </c>
+      <c r="C49" s="6" t="s">
+        <v>97</v>
       </c>
       <c r="E49" s="3" t="s">
         <v>4</v>
@@ -1576,10 +3489,10 @@
         <v>5</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C50" s="5" t="s">
-        <v>69</v>
+        <v>10</v>
+      </c>
+      <c r="C50" s="6" t="s">
+        <v>98</v>
       </c>
       <c r="E50" s="3" t="s">
         <v>4</v>
@@ -1590,10 +3503,10 @@
         <v>5</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C51" s="5" t="s">
-        <v>73</v>
+        <v>10</v>
+      </c>
+      <c r="C51" s="6" t="s">
+        <v>99</v>
       </c>
       <c r="E51" s="3" t="s">
         <v>4</v>
@@ -1604,10 +3517,10 @@
         <v>5</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C52" s="5" t="s">
-        <v>75</v>
+        <v>10</v>
+      </c>
+      <c r="C52" s="6" t="s">
+        <v>100</v>
       </c>
       <c r="E52" s="3" t="s">
         <v>4</v>
@@ -1618,10 +3531,10 @@
         <v>5</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C53" s="5" t="s">
-        <v>76</v>
+        <v>10</v>
+      </c>
+      <c r="C53" s="6" t="s">
+        <v>101</v>
       </c>
       <c r="E53" s="3" t="s">
         <v>4</v>
@@ -1632,10 +3545,10 @@
         <v>5</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C54" s="5" t="s">
-        <v>80</v>
+        <v>10</v>
+      </c>
+      <c r="C54" s="6" t="s">
+        <v>102</v>
       </c>
       <c r="E54" s="3" t="s">
         <v>4</v>
@@ -1646,10 +3559,10 @@
         <v>5</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C55" s="5" t="s">
-        <v>90</v>
+        <v>10</v>
+      </c>
+      <c r="C55" s="6" t="s">
+        <v>103</v>
       </c>
       <c r="E55" s="3" t="s">
         <v>4</v>
@@ -1660,10 +3573,10 @@
         <v>5</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C56" s="5" t="s">
-        <v>91</v>
+        <v>10</v>
+      </c>
+      <c r="C56" s="6" t="s">
+        <v>104</v>
       </c>
       <c r="E56" s="3" t="s">
         <v>4</v>
@@ -1674,10 +3587,10 @@
         <v>5</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="E57" s="3" t="s">
         <v>4</v>
@@ -1688,10 +3601,10 @@
         <v>5</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C58" s="5" t="s">
         <v>10</v>
+      </c>
+      <c r="C58" s="6" t="s">
+        <v>106</v>
       </c>
       <c r="E58" s="3" t="s">
         <v>4</v>
@@ -1702,10 +3615,10 @@
         <v>5</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>95</v>
+        <v>10</v>
       </c>
       <c r="C59" s="6" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="E59" s="3" t="s">
         <v>4</v>
@@ -1716,10 +3629,10 @@
         <v>5</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>39</v>
+        <v>10</v>
       </c>
       <c r="C60" s="6" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="E60" s="3" t="s">
         <v>4</v>
@@ -1730,10 +3643,10 @@
         <v>5</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C61" s="5" t="s">
-        <v>46</v>
+        <v>10</v>
+      </c>
+      <c r="C61" s="6" t="s">
+        <v>35</v>
       </c>
       <c r="E61" s="3" t="s">
         <v>4</v>
@@ -1744,10 +3657,10 @@
         <v>5</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C62" s="5" t="s">
-        <v>47</v>
+        <v>8</v>
+      </c>
+      <c r="C62" s="6" t="s">
+        <v>109</v>
       </c>
       <c r="E62" s="3" t="s">
         <v>4</v>
@@ -1758,10 +3671,10 @@
         <v>5</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C63" s="5" t="s">
-        <v>50</v>
+        <v>27</v>
+      </c>
+      <c r="C63" s="6" t="s">
+        <v>110</v>
       </c>
       <c r="E63" s="3" t="s">
         <v>4</v>
@@ -1772,10 +3685,10 @@
         <v>5</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C64" s="5" t="s">
-        <v>59</v>
+        <v>23</v>
+      </c>
+      <c r="C64" s="6" t="s">
+        <v>111</v>
       </c>
       <c r="E64" s="3" t="s">
         <v>4</v>
@@ -1786,10 +3699,10 @@
         <v>5</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C65" s="5" t="s">
-        <v>61</v>
+        <v>23</v>
+      </c>
+      <c r="C65" s="6" t="s">
+        <v>112</v>
       </c>
       <c r="E65" s="3" t="s">
         <v>4</v>
@@ -1800,10 +3713,10 @@
         <v>5</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C66" s="5" t="s">
-        <v>62</v>
+        <v>23</v>
+      </c>
+      <c r="C66" s="6" t="s">
+        <v>113</v>
       </c>
       <c r="E66" s="3" t="s">
         <v>4</v>
@@ -1814,10 +3727,10 @@
         <v>5</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C67" s="5" t="s">
-        <v>63</v>
+        <v>23</v>
+      </c>
+      <c r="C67" s="6" t="s">
+        <v>114</v>
       </c>
       <c r="E67" s="3" t="s">
         <v>4</v>
@@ -1828,10 +3741,10 @@
         <v>5</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C68" s="5" t="s">
-        <v>70</v>
+        <v>23</v>
+      </c>
+      <c r="C68" s="6" t="s">
+        <v>115</v>
       </c>
       <c r="E68" s="3" t="s">
         <v>4</v>
@@ -1842,10 +3755,10 @@
         <v>5</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C69" s="5" t="s">
-        <v>71</v>
+        <v>23</v>
+      </c>
+      <c r="C69" s="6" t="s">
+        <v>121</v>
       </c>
       <c r="E69" s="3" t="s">
         <v>4</v>
@@ -1856,10 +3769,10 @@
         <v>5</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C70" s="5" t="s">
-        <v>72</v>
+        <v>23</v>
+      </c>
+      <c r="C70" s="6" t="s">
+        <v>122</v>
       </c>
       <c r="E70" s="3" t="s">
         <v>4</v>
@@ -1870,10 +3783,10 @@
         <v>5</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="C71" s="6" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="E71" s="3" t="s">
         <v>4</v>
@@ -1884,10 +3797,10 @@
         <v>5</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C72" s="5" t="s">
-        <v>7</v>
+        <v>23</v>
+      </c>
+      <c r="C72" s="6" t="s">
+        <v>124</v>
       </c>
       <c r="E72" s="3" t="s">
         <v>4</v>
@@ -1898,10 +3811,10 @@
         <v>5</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C73" s="5" t="s">
-        <v>38</v>
+        <v>23</v>
+      </c>
+      <c r="C73" s="6" t="s">
+        <v>125</v>
       </c>
       <c r="E73" s="3" t="s">
         <v>4</v>
@@ -1912,10 +3825,10 @@
         <v>5</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C74" s="5" t="s">
-        <v>55</v>
+        <v>23</v>
+      </c>
+      <c r="C74" s="6" t="s">
+        <v>126</v>
       </c>
       <c r="E74" s="3" t="s">
         <v>4</v>
@@ -1926,10 +3839,10 @@
         <v>5</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C75" s="5" t="s">
-        <v>94</v>
+        <v>23</v>
+      </c>
+      <c r="C75" s="6" t="s">
+        <v>34</v>
       </c>
       <c r="E75" s="3" t="s">
         <v>4</v>
@@ -1940,10 +3853,10 @@
         <v>5</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C76" s="5" t="s">
-        <v>28</v>
+        <v>6</v>
+      </c>
+      <c r="C76" s="6" t="s">
+        <v>119</v>
       </c>
       <c r="E76" s="3" t="s">
         <v>4</v>
@@ -1954,10 +3867,10 @@
         <v>5</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C77" s="5" t="s">
-        <v>45</v>
+        <v>6</v>
+      </c>
+      <c r="C77" s="6" t="s">
+        <v>118</v>
       </c>
       <c r="E77" s="3" t="s">
         <v>4</v>
@@ -1968,10 +3881,10 @@
         <v>5</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C78" s="5" t="s">
-        <v>77</v>
+        <v>6</v>
+      </c>
+      <c r="C78" s="6" t="s">
+        <v>120</v>
       </c>
       <c r="E78" s="3" t="s">
         <v>4</v>
@@ -1982,10 +3895,10 @@
         <v>5</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C79" s="5" t="s">
-        <v>78</v>
+        <v>6</v>
+      </c>
+      <c r="C79" s="6" t="s">
+        <v>117</v>
       </c>
       <c r="E79" s="3" t="s">
         <v>4</v>
@@ -1996,10 +3909,10 @@
         <v>5</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C80" s="5" t="s">
-        <v>79</v>
+        <v>17</v>
+      </c>
+      <c r="C80" s="6" t="s">
+        <v>116</v>
       </c>
       <c r="E80" s="3" t="s">
         <v>4</v>
@@ -2010,10 +3923,10 @@
         <v>5</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C81" s="5" t="s">
-        <v>81</v>
+        <v>17</v>
+      </c>
+      <c r="C81" s="6" t="s">
+        <v>80</v>
       </c>
       <c r="E81" s="3" t="s">
         <v>4</v>
@@ -2024,10 +3937,10 @@
         <v>5</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C82" s="5" t="s">
-        <v>82</v>
+        <v>17</v>
+      </c>
+      <c r="C82" s="6" t="s">
+        <v>73</v>
       </c>
       <c r="E82" s="3" t="s">
         <v>4</v>
@@ -2038,10 +3951,10 @@
         <v>5</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C83" s="5" t="s">
-        <v>83</v>
+        <v>17</v>
+      </c>
+      <c r="C83" s="6" t="s">
+        <v>74</v>
       </c>
       <c r="E83" s="3" t="s">
         <v>4</v>
@@ -2052,10 +3965,10 @@
         <v>5</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="C84" s="6" t="s">
-        <v>115</v>
+        <v>75</v>
       </c>
       <c r="E84" s="3" t="s">
         <v>4</v>
@@ -2066,10 +3979,10 @@
         <v>5</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="C85" s="6" t="s">
-        <v>114</v>
+        <v>76</v>
       </c>
       <c r="E85" s="3" t="s">
         <v>4</v>
@@ -2077,123 +3990,174 @@
     </row>
     <row r="86" spans="1:5" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A86" s="2" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C86" s="6" t="s">
-        <v>103</v>
+        <v>77</v>
       </c>
       <c r="E86" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="87" spans="1:5" s="1" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="87" spans="1:5" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A87" s="2" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C87" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="D87" s="2"/>
+        <v>17</v>
+      </c>
+      <c r="C87" s="6" t="s">
+        <v>78</v>
+      </c>
       <c r="E87" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="88" spans="1:5" s="1" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="88" spans="1:5" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A88" s="2" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C88" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="D88" s="2"/>
+        <v>79</v>
+      </c>
       <c r="E88" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="89" spans="1:5" s="1" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="89" spans="1:5" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A89" s="2" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>102</v>
+        <v>17</v>
       </c>
       <c r="C89" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="D89" s="2"/>
-      <c r="E89" s="3"/>
+        <v>71</v>
+      </c>
+      <c r="E89" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="90" spans="1:5" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A90" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B90" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C90" s="7" t="s">
-        <v>116</v>
-      </c>
-      <c r="D90" s="1"/>
+      <c r="A90" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B90" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C90" s="6" t="s">
+        <v>70</v>
+      </c>
       <c r="E90" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="91" spans="1:5" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A91" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B91" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="C91" s="7" t="s">
-        <v>117</v>
-      </c>
-      <c r="D91" s="1"/>
+    <row r="91" spans="1:5" s="1" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A91" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C91" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="D91" s="2"/>
       <c r="E91" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="92" spans="1:5" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A92" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="B92" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="C92" s="8" t="s">
-        <v>101</v>
-      </c>
-      <c r="D92" s="3" t="s">
-        <v>101</v>
-      </c>
+    <row r="92" spans="1:5" s="1" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A92" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C92" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="D92" s="2"/>
       <c r="E92" s="3" t="s">
         <v>4</v>
       </c>
     </row>
+    <row r="93" spans="1:5" s="1" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A93" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B93" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C93" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="D93" s="2"/>
+      <c r="E93" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A94" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C94" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="D94" s="1"/>
+      <c r="E94" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A95" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C95" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="D95" s="1"/>
+      <c r="E95" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A96" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B96" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C96" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="D96" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D92">
+  <autoFilter ref="A1:D96">
     <sortState ref="A2:D91">
       <sortCondition descending="1" ref="A1:A91"/>
     </sortState>
   </autoFilter>
   <phoneticPr fontId="2" type="noConversion"/>
-  <hyperlinks>
-    <hyperlink ref="C29" r:id="rId1" tooltip="http://www.baidu.com/"/>
-    <hyperlink ref="C9" r:id="rId2" tooltip="http://www.google.com/"/>
-    <hyperlink ref="C20" r:id="rId3" tooltip="http://www.baidu.com/"/>
-    <hyperlink ref="C45" r:id="rId4" tooltip="http://maccauth.ruijie.com.cn/" display="{u&quot;noParse&quot;: False, u&quot;module&quot;: u&quot;app_auth_macc&quot;, u&quot;remoteIp&quot;: False, u&quot;device&quot;: u&quot;pc&quot;, u&quot;async&quot;: True, u&quot;data&quot;: {u&quot;cfgIdOpt&quot;: u&quot;2&quot;, u&quot;authType&quot;: u&quot;wifidog&quot;, u&quot;enable&quot;: u&quot;1&quot;, u&quot;flowDetectEn&quot;: u&quot;1&quot;, u&quot;wxRedirect&quot;: u&quot;118.31.178.137&quot;, u&quot;portalCheck&quot;: u&quot;1&quot;, u&quot;macByPass&quot;: u&quot;1&quot;, u&quot;ad_url&quot;: u&quot;maccauth.ruijie.com.cn&quot;, u&quot;authIpList&quot;: [u&quot;1.1.1.1-1.1.1.2'flagthn'&quot;], u&quot;allAuthList&quot;: [], u&quot;flowDetectTime&quot;: u&quot;15&quot;, u&quot;setSsidIpList&quot;: []}}"/>
-    <hyperlink ref="C57" r:id="rId5" tooltip="http://cloudloge.rj.link:6222/macclog/log/upload" display="{_x000a_&quot;module&quot;:&quot;rlog_module_config&quot;,_x000a_&quot;noParse&quot;:false,_x000a_&quot;async&quot;:null,_x000a_&quot;remoteIp&quot;:false,_x000a_&quot;data&quot;:{_x000a_&quot;total&quot;:1,_x000a_&quot;module_list&quot;:[_x000a_{_x000a_&quot;module_name&quot;:&quot;system1231232222&quot;,_x000a_&quot;single&quot;:0,_x000a_&quot;upload_period&quot;:300,_x000a_&quot;server&quot;:&quot;http://cloudloge.rj.link:6222/macclog/log/upload &quot;,_x000a_&quot;create_period&quot;:10,_x000a_&quot;file&quot;:&quot;flagthn&quot;,_x000a_&quot;protocol&quot;:&quot;http&quot;,_x000a_&quot;header&quot;:&quot;Content-Type:application/json;charset=UTF-8&quot;_x000a_}_x000a_]_x000a_},_x000a_&quot;device&quot;:&quot;pc&quot;_x000a_}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId6"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/408/OS/2024/ModularAutomation/reports/testcases.xlsx
+++ b/408/OS/2024/ModularAutomation/reports/testcases.xlsx
@@ -15,7 +15,7 @@
     <sheet name="#TEMP" sheetId="4" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'#TEMP'!$A$1:$D$96</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'#TEMP'!$A$1:$D$77</definedName>
   </definedNames>
   <calcPr calcId="152511"/>
   <extLst>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="387" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="109">
   <si>
     <t>接口</t>
   </si>
@@ -159,21 +159,6 @@
   </si>
   <si>
     <t>{
-    u"noParse": False, u"module": u"access_ctrl", u"remoteIp": False, u"device": u"pc", u"async": True, u"data": {
-        u"list": [
-            {
-                u"src": u"lan", u"tmngtName": u"\u5de5\u4f5c\u65e5", u"target": u"ACCEPT", u"proto": u"allflagthn",
-                u"dest": u"wanflagthn", u"srcPort": u"'flagthn'", u"destPort": u"",
-                u"destIP": u"192.168.110.33\x0cflagthn", u"mac": u"00:11:22:33:33:22flagthn", u"ruleName": u"222",
-                u"srcIP": u"192.168.110.33\x0cflagthn", u"by": u"mac"
-            }
-        ]
-    }
-}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>{
     "module": "config_retain",
     "noParse": false,
     "async": null,
@@ -261,34 +246,6 @@
   </si>
   <si>
     <t>{
-    "iface": "eth0 flagthn",
-    "protocal": "flagthn",
-    "size": "2",
-    "ip": "flagthn",
-    "package": "flagthn"
-}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>{
-    "iface": "flagthn",
-    "protocal": "flagthn",
-    "size": "2",
-    "ip": "flagthn",
-    "package": "flagthn"
-}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>{
-    "count": "1",
-    "size": "1",
-    "target": "baidu.comflagthn"
-}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>{
     "type": "3",
     "count": "4",
     "size": "64",
@@ -301,54 +258,6 @@
   </si>
   <si>
     <t>{
-    "time": "1",
-    "force": "'flagthn'"
-}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">{
-    u"noParse": False,
-    u"module": u"content_audit",
-    u"remoteIp": False,
-    u"device": u"pc",
-    u"async": True,
-    u"data": {
-        u"comment": u"",
-        u"enable": u"1",
-        u"ip_slots": [
-            u"1.1.1.1'flagthn'"
-        ],
-        u"ip_group": u"",
-        u"tr_slots": {},
-        u"applist": [
-            u"\u793e\u4ea4\u8f6f\u4ef6"
-        ],
-        u"func": u"ca_set_app_policy",
-        u"policy": u"",
-        u"tr_group": u"\u6240\u6709\u65f6\u6bb5",
-        u"time_mode": u"calendar",
-        u"user_group_list": []
-    }
-}
-</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>{
-    "module": "recov_network",
-    "noParse": false,
-    "async": null,
-    "remoteIp": false,
-    "data": {
-        "": "}'&amp;&amp;flagthn&amp;&amp;echo'{fuckyou"
-    },
-    "device": "pc"
-}</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>{
     "module": "host_access_delay",
     "noParse": false,
     "async": null,
@@ -383,63 +292,6 @@
         "cmd": "dummy'flagthn'"
     },
     "device": "pc"
-}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>{
-    "noParse": false,
-    "module": "content_audit",
-    "remoteIp": false,
-    "device": "pc",
-    "async": true,
-    "data": {
-        "comment": "",
-        "enable": "1",
-        "ip_slots": [
-            "1.1.1.1'flagthn'"
-        ],
-        "ip_group": "",
-        "tr_slots": {
-        },
-        "action": "deny",
-        "func": "ca_set_url_policy",
-        "url_class": [
-            "games"
-        ],
-        "policy": "",
-        "tr_group": "\u6240\u6709\u65f6\u6bb5",
-        "time_mode": "calendar",
-        "user_group_list": [
-        ]
-    }
-}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>{
-    "noParse": false,
-    "module": "content_audit",
-    "remoteIp": false,
-    "device": "pc",
-    "async": true,
-    "data": {
-        "entry_name": "",
-        "url_list": [
-            "www.baidu.com"
-        ],
-        "alias_name": "1111'flagthn'",
-        "func": "ca_set_url_list"
-    }
-}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>{
-    "force": "\"'flagthn'",
-    "time": "20230426",
-    "pwdTip": "x",
-    "setQuick": false
 }</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -454,57 +306,7 @@
   </si>
   <si>
     <t>{
-    "module": "enetCap",
-    "noParse": true,
-    "async": null,
-    "remoteIp": false,
-    "data": {
-        "caps": "flagthn",
-        "module": "..///.//..//.///../////../root/test1111"
-    },
-    "device": "pc"
-}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>{
     "search": "'flagthn"
-}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>{
-    "search": "'flagthn'"
-}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>{
-    "noParse": false,
-    "module": "content_audit",
-    "remoteIp": false,
-    "device": "pc",
-    "async": true,
-    "data": {
-        "comment": "",
-        "model": "black",
-        "account": [
-            "111111"
-        ],
-        "enable": "1",
-        "ip_slots": [
-            "1.1.1.1'flagthn'"
-        ],
-        "ip_group": "",
-        "tr_slots": {
-        },
-        "func": "ca_set_im_policy",
-        "policy": "",
-        "tr_group": "\u6240\u6709\u65f6\u6bb5",
-        "time_mode": "calendar",
-        "user_group_list": [
-        ]
-    }
 }</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -527,6 +329,21 @@
   </si>
   <si>
     <t>{
+    "module": "nbr_cwmp",
+    "noParse": false,
+    "async": null,
+    "remoteIp": false,
+    "data": {
+        "password": ";flagthn",
+        "type": "encd",
+        "ip": "1.1.1"
+    },
+    "device": "pc"
+}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{
     "module": "fw_networkId_merge",
     "noParse": false,
     "async": null,
@@ -534,7 +351,7 @@
     "data": {
         "type": "s",
         "stamac": "testp1",
-        "password": "1flagthn ",
+        "password": "flagthn",
         "toNetworkId": "true",
         "listp": [
             {
@@ -587,27 +404,12 @@
   </si>
   <si>
     <t>{
-    "module": "nbr_cwmp",
-    "noParse": false,
-    "async": null,
-    "remoteIp": false,
-    "data": {
-        "password": ";flagthn",
-        "type": "encd",
-        "ip": "1.1.1"
-    },
-    "device": "pc"
-}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>{
     "module": "nbr_networkId_merge",
     "noParse": false,
     "async": null,
     "remoteIp": false,
     "data": {
-        "password": "1;flagthn;echo 1",
+        "password": "1flagthnecho 1",
         "type": "pp",
         "ip": "192.168.110.1",
         "toNetworkId": "ss"
@@ -618,18 +420,28 @@
   </si>
   <si>
     <t>{
-    "module": "redbscontrl",
-    "noParse": false,
-    "async": null,
-    "remoteIp": false,
-    "data": {
-        "networkid": "hss",
-        "selfsn": "s",
-        "dispinfo": {
-            "l1": [
-                "]}'flagthn'{["
-            ]
-        }
+    "noParse": false,
+    "module": "dhcp_lease",
+    "remoteIp": false,
+    "device": "pc",
+    "async": null,
+    "data": {
+        "index": 1,
+        "macaddr": "11111'flagthn'",
+        "size": 10
+    }
+}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{
+    "module": "version_auto_upgrade",
+    "noParse": false,
+    "async": null,
+    "remoteIp": false,
+    "data": {
+        "autoUpgrade": "0",
+        "cronTime": "'flagthn':'flagthn'"
     },
     "device": "pc"
 }</t>
@@ -637,19 +449,46 @@
   </si>
   <si>
     <t>{
-    "module": "fw_networkId_merge",
-    "noParse": false,
-    "async": null,
-    "remoteIp": false,
-    "data": {
-        "type": "s",
-        "stamac": "testp1",
-        "password": "flagthn",
-        "toNetworkId": "true",
-        "listp": [
-            {
-                "name": "h",
-                "mac": "h",
+    "module": "123",
+    "remoteIp": "'flagthn'",
+    "data": {
+        "kkk": "111"
+    }
+}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{
+    "password": "总之是错误的密码",
+    "username": "admin",
+    "time": "flagthn",
+    "encry": true,
+    "limit": false,
+    "setInit": true
+}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{
+    "winmt": "'flagthn'"
+}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{
+    "module": "apmeshNetworkSetup",
+    "noParse": false,
+    "async": null,
+    "remoteIp": false,
+    "data": {
+        "mode": "apmesh_scan",
+        "enable": "sflagthn",
+        "lanNum": "2",
+        "wanNum": "0",
+        "wan6": [
+            {
+                "proto": "dhcpv6",
+                "ifname": "@wan",
                 "masq6": "1",
                 "metric": "1"
             },
@@ -697,147 +536,6 @@
   </si>
   <si>
     <t>{
-    "module": "nbr_networkId_merge",
-    "noParse": false,
-    "async": null,
-    "remoteIp": false,
-    "data": {
-        "password": "1flagthnecho 1",
-        "type": "pp",
-        "ip": "192.168.110.1",
-        "toNetworkId": "ss"
-    },
-    "device": "pc"
-}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>{
-    "noParse": false,
-    "module": "dhcp_lease",
-    "remoteIp": false,
-    "device": "pc",
-    "async": null,
-    "data": {
-        "index": 1,
-        "macaddr": "11111'flagthn'",
-        "size": 10
-    }
-}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>{
-    "module": "version_auto_upgrade",
-    "noParse": false,
-    "async": null,
-    "remoteIp": false,
-    "data": {
-        "autoUpgrade": "0",
-        "cronTime": "'flagthn':'flagthn'"
-    },
-    "device": "pc"
-}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>{
-    "module": "123",
-    "remoteIp": "'flagthn'",
-    "data": {
-        "kkk": "111"
-    }
-}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>{
-    "password": "总之是错误的密码",
-    "username": "admin",
-    "time": "flagthn",
-    "encry": true,
-    "limit": false,
-    "setInit": true
-}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>{
-    "back": "1",
-    "data": {
-        "cmd": "'flagthn'"
-    }
-}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>{
-    "winmt": "'flagthn'"
-}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>{
-    "module": "apmeshNetworkSetup",
-    "noParse": false,
-    "async": null,
-    "remoteIp": false,
-    "data": {
-        "mode": "apmesh_scan",
-        "enable": "sflagthn",
-        "lanNum": "2",
-        "wanNum": "0",
-        "wan6": [
-            {
-                "proto": "dhcpv6",
-                "ifname": "@wan",
-                "masq6": "1",
-                "metric": "1"
-            },
-            {
-                "proto": "dhcpv6",
-                "ifname": "@wan1",
-                "masq6": "1",
-                "metric": "5"
-            }
-        ],
-        "version": "1.0.0",
-        "lan": [
-            {
-                "ip6addr": "",
-                "ip6assign": "64",
-                "ip6hint": "0",
-                "ip6class": "",
-                "dhcpv6": "server",
-                "dhcpv6Type": "DHCPv6+SLAAC",
-                "ra": "server",
-                "ra_management": "1",
-                "leasetime6": "30",
-                "dns": "",
-                "vlanid": "233"
-            },
-            {
-                "ip6addr": "2403:C980:7004:0000:0000:0000:0000:0001/128",
-                "ip6assign": "64",
-                "ip6hint": "0",
-                "ip6class": "",
-                "dhcpv6": "server",
-                "dhcpv6Type": "DHCPv6+SLAAC",
-                "ra": "server",
-                "ra_management": "1",
-                "leasetime6": "30",
-                "dns": "2403:C980:7004:0000:0000:0000:0000:0001",
-                "vlanid": "3"
-            }
-        ],
-        "wan6Num": "2"
-    },
-    "device": "pc"
-}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>{
     "fromNetworkId": "xxxx",
     "esw_fromSn": [
         "sn3",
@@ -850,75 +548,6 @@
     ],
     "password": "xxxxx\\u0024(flagthn)",
     "type": "enc"
-}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>{
-    "noParse": false,
-    "module": "wireless",
-    "remoteIp": false,
-    "device": "pc",
-    "async": null,
-    "data": {
-        "networkId": "dev_10:82:3D:F4:32:9E_1680599422",
-        "ssidList": [
-            {
-                "ssidEncode": "utf-8",
-                "enable": "true",
-                "guest": "false",
-                "relatedRadio": "1,2",
-                "bandSelectEnable": "false",
-                "ishidden": "false",
-                "roam": "false",
-                "encryptionMode": "open",
-                "vlanId": "1",
-                "ssidName": "@Ruijie-m329E'flagthn'",
-                "tmMode": "def",
-                "xpress": "false",
-                "mode": "ap",
-                "tmValue": {
-                    "slot": "",
-                    "tmngtName": "\u6240\u6709\u65f6\u6bb5"
-                },
-                "wlanId": "1",
-                "password": "",
-                "axMode": "true",
-                "fowardType": "bridge"
-            }
-        ],
-        "apIsolate": "false",
-        "version": "1.0.0",
-        "ssidIsolate": "false",
-        "healthy": {
-            "slot": "",
-            "enable": "false",
-            "tmngtName": "",
-            "mode": "0"
-        },
-        "radioList": [
-            {
-                "enable": "true",
-                "country": "CN",
-                "bandWidth": "auto",
-                "radioIndex": "1",
-                "hwmode": "11ng",
-                "type": "2.4G",
-                "maxSta": "32"
-            },
-            {
-                "enable": "true",
-                "country": "CN",
-                "bandWidth": "auto",
-                "radioIndex": "2",
-                "hwmode": "11ac",
-                "type": "5G",
-                "maxSta": "32"
-            }
-        ],
-        "subConfigId": "1680599428_ZAR91V2000217",
-        "groupId": "0"
-    }
 }</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1016,192 +645,6 @@
   <si>
     <t>{
     "noParse": false,
-    "module": "wireless",
-    "remoteIp": false,
-    "device": "pc",
-    "async": null,
-    "data": {
-        "networkId": "dev_10:82:3D:F4:32:9E_1680599422",
-        "ssidList": [
-            {
-                "ssidEncode": "utf-8",
-                "enable": "true",
-                "guest": "false",
-                "relatedRadio": "1,2",
-                "bandSelectEnable": "false",
-                "ishidden": "false",
-                "roam": "false",
-                "encryptionMode": "open",
-                "vlanId": "1",
-                "ssidName": "@Ruijie-m329E'flagthn'",
-                "tmMode": "def",
-                "xpress": "false",
-                "mode": "ap",
-                "tmValue": {
-                    "slot": "",
-                    "tmngtName": "\u6240\u6709\u65f6\u6bb5"
-                },
-                "wlanId": "1",
-                "password": "",
-                "axMode": "true",
-                "fowardType": "bridge"
-            },
-            {
-                "ssidEncode": "utf-8",
-                "enable": "true",
-                "guest": "true",
-                "relatedRadio": "1,2",
-                "bandSelectEnable": "false",
-                "ishidden": "false",
-                "roam": "false",
-                "encryptionMode": "open",
-                "vlanId": "1",
-                "ssidName": "@Ruijie-guest-329E'flagthn'",
-                "tmMode": "all",
-                "xpress": "false",
-                "tmValue": {
-                    "slot": "",
-                    "tmngtName": ""
-                },
-                "wlanId": "8",
-                "password": "",
-                "axMode": "true",
-                "fowardType": "bridge"
-            }
-        ],
-        "apIsolate": "false",
-        "version": "1.0.0",
-        "ssidIsolate": "false",
-        "healthy": {
-            "slot": "",
-            "enable": "true",
-            "tmngtName": "\u6240\u6709\u65f6\u6bb5",
-            "mode": "0"
-        },
-        "radioList": [
-            {
-                "enable": "true",
-                "country": "CN",
-                "bandWidth": "auto",
-                "radioIndex": "1",
-                "hwmode": "11ng",
-                "type": "2.4G",
-                "maxSta": "32"
-            },
-            {
-                "enable": "true",
-                "country": "CN",
-                "bandWidth": "auto",
-                "radioIndex": "2",
-                "hwmode": "11ac",
-                "type": "5G",
-                "maxSta": "32"
-            }
-        ],
-        "subConfigId": "1680599428_ZAR91V2000217",
-        "groupId": "0"
-    }
-}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>{
-    "noParse": false,
-    "module": "wireless",
-    "remoteIp": false,
-    "device": "pc",
-    "async": null,
-    "data": {
-        "networkId": "dev_10:82:3D:F4:32:9E_1680599422'flagthn'",
-        "ssidList": [
-            {
-                "ssidEncode": "utf-8",
-                "enable": "true",
-                "guest": "false",
-                "relatedRadio": "1,2",
-                "bandSelectEnable": "false",
-                "ishidden": "false",
-                "roam": "false",
-                "encryptionMode": "open",
-                "vlanId": "1",
-                "ssidName": "@Ruijie-m329E'flagthn'",
-                "tmMode": "def",
-                "xpress": "false",
-                "mode": "ap",
-                "tmValue": {
-                    "slot": "",
-                    "tmngtName": "\u6240\u6709\u65f6\u6bb5"
-                },
-                "wlanId": "1",
-                "password": "",
-                "axMode": "true",
-                "fowardType": "bridge"
-            },
-            {
-                "ssidEncode": "utf-8",
-                "enable": "true",
-                "guest": "true",
-                "relatedRadio": "1,2",
-                "bandSelectEnable": "false",
-                "ishidden": "false",
-                "roam": "false",
-                "encryptionMode": "open",
-                "vlanId": "1",
-                "ssidName": "@Ruijie-guest-329E'flagthn'",
-                "tmMode": "all",
-                "xpress": "false",
-                "tmValue": {
-                    "slot": "",
-                    "tmngtName": ""
-                },
-                "wlanId": "8",
-                "password": "",
-                "axMode": "true",
-                "fowardType": "bridge"
-            }
-        ],
-        "apIsolate": "false",
-        "version": "1.0.0",
-        "ssidIsolate": "false",
-        "healthy": {
-            "slot": "",
-            "enable": "true",
-            "tmngtName": "\u6240\u6709\u65f6\u6bb5",
-            "mode": "0"
-        },
-        "radioList": [
-            {
-                "enable": "true",
-                "country": "CN",
-                "bandWidth": "auto",
-                "kicksta_rssilow": "0",
-                "radioIndex": "1",
-                "hwmode": "11ng",
-                "type": "2.4G",
-                "maxSta": "32",
-                "bwExtern": "0"
-            },
-            {
-                "enable": "true",
-                "country": "CN",
-                "bandWidth": "auto",
-                "kicksta_rssilow": "0",
-                "radioIndex": "2",
-                "hwmode": "11ac",
-                "type": "5G",
-                "maxSta": "32",
-                "bwExtern": "0"
-            }
-        ],
-        "subConfigId": "1680599428_ZAR91V2000217",
-        "groupId": "0"
-    }
-}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>{
-    "noParse": false,
     "module": "wirelan",
     "remoteIp": false,
     "device": "pc",
@@ -1237,66 +680,6 @@
         "subConfigId": "1680599442_ZAR91V2000217",
         "groupId": "0",
         "version": "1.0.0"
-    }
-}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>{
-    "noParse": false,
-    "module": "apmeshNetworkSetup",
-    "remoteIp": false,
-    "device": "pc",
-    "async": null,
-    "data": {
-        "lan": [
-            {
-                "ip6addr": "",
-                "dhcpv6Type": "DHCPv6+SLAAC",
-                "ip6assign": "64",
-                "vlanid": "233",
-                "dhcpv6": "server",
-                "ra": "server",
-                "dns": "",
-                "ra_management": "1",
-                "leasetime6": "30",
-                "ip6class": "",
-                "ip6hint": "0"
-            },
-            {
-                "ip6addr": "2403:C980:7004:0000:0000:0000:0000:0001/128",
-                "dhcpv6Type": "DHCPv6+SLAAC",
-                "ip6assign": "64",
-                "vlanid": "3",
-                "dhcpv6": "server",
-                "ra": "server",
-                "dns": "2403:C980:7004:0000:0000:0000:0000:0001",
-                "ra_management": "1",
-                "leasetime6": "30",
-                "ip6class": "",
-                "ip6hint": "0"
-            }
-        ],
-        "enable": "sflagthn",
-        "wan6Num": "2",
-        "wanNum": "0",
-        "version": "1.0.0",
-        "wan6": [
-            {
-                "ifname": "@wan",
-                "masq6": "1",
-                "metric": "1",
-                "proto": "dhcpv6"
-            },
-            {
-                "ifname": "@wan1",
-                "masq6": "1",
-                "metric": "5",
-                "proto": "dhcpv6"
-            }
-        ],
-        "mode": "apmesh_scan",
-        "lanNum": "2"
     }
 }</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -1500,70 +883,12 @@
   </si>
   <si>
     <t>{
-    "module": "kvNavDev",
-    "noParse": true,
-    "async": null,
-    "remoteIp": false,
-    "data": {
-        "sta": "'flagthn'"
-    },
-    "device": "pc"
-}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>{
-    "module": "repeater_hostrouter",
-    "noParse": true,
-    "async": null,
-    "remoteIp": false,
-    "data": {
-        "repeater": {
-            "ssid": "123",
-            "channel": "flagthn",
-            "enable": "true",
-            "bssid": "ssdf"
-        },
-        "repeater_5g": "1"
-    },
-    "device": "pc"
-}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>{
     "module": "'flagthn'",
     "data": {
         "name": "hah",
         "sn": [
             "G1QH1J5000534"
         ]
-    },
-    "device": "pc"
-}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>{
-    "module": "dummy",
-    "noParse": false,
-    "async": null,
-    "remoteIp": false,
-    "data": {
-        "cmd": "dummy'flagthn'"
-    },
-    "device": "pc"
-}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>{
-    "module": "dummy",
-    "noParse": false,
-    "async": null,
-    "remoteIp": false,
-    "data": {
-        "cmd": "dummy'flagthn'"
     },
     "device": "pc"
 }</t>
@@ -1692,79 +1017,6 @@
   <si>
     <t>{
     "noParse": false,
-    "module": "guest_auth",
-    "remoteIp": false,
-    "device": "pc",
-    "async": null,
-    "data": {
-        "username": "test'flagthn'",
-        "mac_cnt": "5",
-        "name": "",
-        "func": "user_pwd_manage",
-        "password": "test",
-        "op": "add"
-    }
-}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>{
-    "noParse": false,
-    "module": "guest_auth",
-    "remoteIp": false,
-    "device": "pc",
-    "async": null,
-    "data": {
-        "en": "1",
-        "name": "qrcode_passive_auth",
-        "activeAuthIpRange": [
-            "1.1.1.5'flagthn'"
-        ],
-        "authList": [
-            "1.1.1.4"
-        ],
-        "func": "guest_auth_set_qrcode_passive_auth_cfg",
-        "time": "0",
-        "allAuthList": [
-            "1.1.1.1-1.1.1.2",
-            "1.1.1.3-1.1.1.3"
-        ],
-        "displaypastext": ""
-    }
-}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>{
-    "noParse": false,
-    "module": "guest_auth",
-    "remoteIp": false,
-    "device": "pc",
-    "async": null,
-    "data": {
-        "qrcodeindex": "defqrcode",
-        "en": "1",
-        "func": "guest_auth_set_qrcode_active_auth_cfg",
-        "name": "qrcode_active_auth",
-        "ip": "10.44.77.253",
-        "authList": [
-            "1.1.1.6'flagthn'"
-        ],
-        "scriptpath": "guest_auth/qrcode_active_auth.lua",
-        "time": "0",
-        "allAuthList": [
-            "1.1.1.1-1.1.1.2",
-            "1.1.1.3-1.1.1.3",
-            "1.1.1.4"
-        ],
-        "displayacttext": ""
-    }
-}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>{
-    "noParse": false,
     "module": "app_auth_direct_srcip",
     "remoteIp": false,
     "device": "pc",
@@ -1893,22 +1145,6 @@
   </si>
   <si>
     <t>{
-    "module": "regEvent",
-    "noParse": false,
-    "async": null,
-    "remoteIp": false,
-    "device": "pc",
-    "data": {
-        "cmd": "'flagthn'",
-        "event": "dnsmasq_restart",
-        "mask": "1",
-        "delay": "0"
-    }
-}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>{
     "module": "rlog_module_config",
     "noParse": false,
     "async": null,
@@ -1998,42 +1234,6 @@
         ]
     },
     "device": "pc"
-}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>{
-    "module": "dhcp_static",
-    "noParse": false,
-    "async": null,
-    "remoteIp": false,
-    "data": {
-        "list": [
-            {
-                "ipaddr": "192.168.110.161';flagthn;'",
-                "macaddr": "f8:e4:3b:60:bb:f6"
-            }
-        ]
-    },
-    "device": "pc"
-}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>{
-    "noParse": false,
-    "module": "dhcp_static",
-    "remoteIp": false,
-    "device": "pc",
-    "async": null,
-    "data": {
-        "list": [
-            {
-                "macaddr": "f8:e4:3b:60:bb:f6",
-                "ipaddr": "192.168.110.161'flagthn'"
-            }
-        ]
-    }
 }</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -2167,26 +1367,6 @@
     "device": "pc",
     "params": [
         {
-            "method": "devConfig.set",
-            "params": {
-                "module": "kvNavDev",
-                "noParse": false,
-                "async": null,
-                "remoteIp": false,
-                "data": {
-                    "start": "ca_get_ip_range'flagthn'"
-                }
-            }
-        }
-    ]
-}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>{
-    "device": "pc",
-    "params": [
-        {
             "params": {
                 "noParse": false,
                 "data": {
@@ -2352,6 +1532,79 @@
   </si>
   <si>
     <t>{
+    "module": "kvNavDev",
+    "noParse": true,
+    "async": null,
+    "remoteIp": false,
+    "data": {
+        "sta": "'flagthn'"
+    },
+    "device": "pc"
+}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{
+    "module": "redbscontrl",
+    "noParse": false,
+    "async": null,
+    "remoteIp": false,
+    "data": {
+        "networkid": "hss",
+        "selfsn": "s",
+        "dispinfo": {
+            "l1": [
+                "]}'flagthn'{["
+            ]
+        }
+    },
+    "device": "pc"
+}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{
+    "back": "1",
+    "data": {
+        "cmd": "'flagthn'"
+    }
+}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{
+    "module": "repeater_hostrouter",
+    "noParse": true,
+    "async": null,
+    "remoteIp": false,
+    "data": {
+        "repeater": {
+            "ssid": "123",
+            "channel": "flagthn",
+            "enable": "true",
+            "bssid": "ssdf"
+        },
+        "repeater_5g": "1"
+    },
+    "device": "pc"
+}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{
+    "module": "recov_network",
+    "noParse": false,
+    "async": null,
+    "remoteIp": false,
+    "data": {
+        "": "}'&amp;&amp;flagthn&amp;&amp;echo'{fuckyou"
+    },
+    "device": "pc"
+}</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>{
     "noParse": false,
     "module": "nat_dmz",
     "remoteIp": false,
@@ -2362,6 +1615,258 @@
         "rule_name": "test'flagthn'",
         "enable": "1",
         "dest_ip": "1.1.1.1"
+    }
+}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{
+    "noParse": false,
+    "module": "access_ctrl",
+    "remoteIp": false,
+    "device": "pc",
+    "async": true,
+    "data": {
+        "list": [
+            {
+                "src": "lan",
+                "tmngtName": "\u5de5\u4f5c\u65e5",
+                "target": "ACCEPT",
+                "proto": "allflagthn",
+                "dest": "wanflagthn",
+                "srcPort": "'flagthn'",
+                "destPort": "",
+                "destIP": "192.168.110.33",
+                "mac": "00:11:22:33:33:22flagthn",
+                "ruleName": "222",
+                "srcIP": "192.168.110.33",
+                "by": "mac"
+            }
+        ]
+    }
+}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{
+    "iface": "eth0 flagthn",
+    "protocal": "flagthn",
+    "size": "2",
+    "ip": "flagthn",
+    "package": "flagthn"
+}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{
+    "force": "\"'flagthn'",
+    "time": "20230426",
+    "pwdTip": "x",
+    "setQuick": false
+}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{
+    "module": "enetCap",
+    "noParse": true,
+    "async": null,
+    "remoteIp": false,
+    "data": {
+        "caps": "x",
+        "module": "flagthn"
+    },
+    "device": "pc"
+}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{
+    "noParse": false,
+    "module": "content_audit",
+    "remoteIp": false,
+    "device": "pc",
+    "async": true,
+    "data": {
+        "comment": "",
+        "enable": "1",
+        "ip_slots": [
+            "1.1.1.1'flagthn'"
+        ],
+        "ip_group": "",
+        "tr_slots": {
+        },
+        "applist": [
+            "\u793e\u4ea4\u8f6f\u4ef6"
+        ],
+        "func": "ca_set_app_policy",
+        "policy": "",
+        "tr_group": "\u6240\u6709\u65f6\u6bb5",
+        "time_mode": "calendar",
+        "user_group_list": [
+        ]
+    }
+}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{
+    "module": "fw_networkId_merge",
+    "noParse": false,
+    "async": null,
+    "remoteIp": false,
+    "data": {
+        "type": "s",
+        "stamac": "testp1",
+        "password": "1flagthn ",
+        "toNetworkId": "true",
+        "listp": [
+            {
+                "name": "h",
+                "mac": "h",
+                "masq6": "1",
+                "metric": "1"
+            },
+            {
+                "proto": "dhcpv6",
+                "ifname": "@wan1",
+                "masq6": "1",
+                "metric": "5"
+            }
+        ],
+        "version": "1.0.0",
+        "lan": [
+            {
+                "ip6addr": "",
+                "ip6assign": "64",
+                "ip6hint": "0",
+                "ip6class": "",
+                "dhcpv6": "server",
+                "dhcpv6Type": "DHCPv6+SLAAC",
+                "ra": "server",
+                "ra_management": "1",
+                "leasetime6": "30",
+                "dns": "",
+                "vlanid": "233"
+            },
+            {
+                "ip6addr": "2403:C980:7004:0000:0000:0000:0000:0001/128",
+                "ip6assign": "64",
+                "ip6hint": "0",
+                "ip6class": "",
+                "dhcpv6": "server",
+                "dhcpv6Type": "DHCPv6+SLAAC",
+                "ra": "server",
+                "ra_management": "1",
+                "leasetime6": "30",
+                "dns": "2403:C980:7004:0000:0000:0000:0000:0001",
+                "vlanid": "3"
+            }
+        ],
+        "wan6Num": "2"
+    },
+    "device": "pc"
+}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{
+    "module": "dummy",
+    "noParse": false,
+    "async": null,
+    "remoteIp": false,
+    "data": {
+        "cmd": "dummy'flagthn'"
+    },
+    "device": "pc"
+}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{
+    "device": "pc",
+    "params": [
+        {
+            "method": "devConfig.set",
+            "params": {
+                "module": "kvNavDev",
+                "noParse": false,
+                "async": null,
+                "remoteIp": false,
+                "data": {
+                    "start": "ca_get_ip_range'flagthn'"
+                }
+            }
+        }
+    ]
+}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{
+    "noParse": false,
+    "module": "wireless",
+    "remoteIp": false,
+    "device": "pc",
+    "async": null,
+    "data": {
+        "networkId": "dev_10:82:3D:F4:32:9E_1680599422",
+        "ssidList": [
+            {
+                "ssidEncode": "utf-8",
+                "enable": "true",
+                "guest": "false",
+                "relatedRadio": "1,2",
+                "bandSelectEnable": "false",
+                "ishidden": "false",
+                "roam": "false",
+                "encryptionMode": "open",
+                "vlanId": "1",
+                "ssidName": "@Ruijie-m329E'flagthn'",
+                "tmMode": "def",
+                "xpress": "false",
+                "mode": "ap",
+                "tmValue": {
+                    "slot": "",
+                    "tmngtName": "\u6240\u6709\u65f6\u6bb5"
+                },
+                "wlanId": "1",
+                "password": "",
+                "axMode": "true",
+                "fowardType": "bridge"
+            }
+        ],
+        "apIsolate": "false",
+        "version": "1.0.0",
+        "ssidIsolate": "false",
+        "healthy": {
+            "slot": "",
+            "enable": "false",
+            "tmngtName": "",
+            "mode": "0"
+        },
+        "radioList": [
+            {
+                "enable": "true",
+                "country": "CN",
+                "bandWidth": "auto",
+                "radioIndex": "1",
+                "hwmode": "11ng",
+                "type": "2.4G",
+                "maxSta": "32"
+            },
+            {
+                "enable": "true",
+                "country": "CN",
+                "bandWidth": "auto",
+                "radioIndex": "2",
+                "hwmode": "11ac",
+                "type": "5G",
+                "maxSta": "32"
+            }
+        ],
+        "subConfigId": "1680599428_ZAR91V2000217",
+        "groupId": "0"
     }
 }</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -2781,7 +2286,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E96"/>
+  <dimension ref="A1:E77"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="39.950000000000003" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="29.375" style="2" customWidth="1"/>
@@ -2817,7 +2322,7 @@
         <v>25</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>93</v>
+        <v>68</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>7</v>
@@ -2834,7 +2339,7 @@
         <v>30</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>4</v>
@@ -2848,7 +2353,7 @@
         <v>21</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>4</v>
@@ -2862,7 +2367,7 @@
         <v>22</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>40</v>
+        <v>101</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>4</v>
@@ -2873,10 +2378,10 @@
         <v>18</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>4</v>
@@ -2887,7 +2392,7 @@
         <v>18</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C7" s="6" t="s">
         <v>39</v>
@@ -2898,13 +2403,13 @@
     </row>
     <row r="8" spans="1:5" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="2" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>42</v>
+        <v>102</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>4</v>
@@ -2912,10 +2417,10 @@
     </row>
     <row r="9" spans="1:5" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="2" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="C9" s="6" t="s">
         <v>43</v>
@@ -2929,7 +2434,7 @@
         <v>14</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>44</v>
@@ -2940,13 +2445,13 @@
     </row>
     <row r="11" spans="1:5" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="2" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>52</v>
+        <v>103</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>4</v>
@@ -2954,13 +2459,13 @@
     </row>
     <row r="12" spans="1:5" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="2" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>4</v>
@@ -2968,13 +2473,13 @@
     </row>
     <row r="13" spans="1:5" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="2" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>4</v>
@@ -2982,13 +2487,13 @@
     </row>
     <row r="14" spans="1:5" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="2" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>56</v>
+        <v>104</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>4</v>
@@ -3002,7 +2507,7 @@
         <v>9</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>4</v>
@@ -3016,7 +2521,7 @@
         <v>9</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>36</v>
+        <v>105</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>4</v>
@@ -3030,7 +2535,7 @@
         <v>9</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>4</v>
@@ -3044,7 +2549,7 @@
         <v>9</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>49</v>
+        <v>95</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>4</v>
@@ -3058,7 +2563,7 @@
         <v>9</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>4</v>
@@ -3072,7 +2577,7 @@
         <v>9</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>4</v>
@@ -3086,7 +2591,7 @@
         <v>9</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>51</v>
+        <v>98</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>4</v>
@@ -3097,10 +2602,10 @@
         <v>5</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C22" s="6" t="s">
-        <v>57</v>
+        <v>11</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>40</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>4</v>
@@ -3111,10 +2616,10 @@
         <v>5</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>4</v>
@@ -3125,10 +2630,10 @@
         <v>5</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>4</v>
@@ -3139,10 +2644,10 @@
         <v>5</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="E25" s="3" t="s">
         <v>4</v>
@@ -3153,10 +2658,10 @@
         <v>5</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>4</v>
@@ -3166,11 +2671,11 @@
       <c r="A27" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B27" s="2" t="s">
-        <v>9</v>
+      <c r="B27" s="4" t="s">
+        <v>36</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>62</v>
+        <v>35</v>
       </c>
       <c r="E27" s="3" t="s">
         <v>4</v>
@@ -3181,10 +2686,10 @@
         <v>5</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E28" s="3" t="s">
         <v>4</v>
@@ -3195,10 +2700,10 @@
         <v>5</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E29" s="3" t="s">
         <v>4</v>
@@ -3209,10 +2714,10 @@
         <v>5</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="E30" s="3" t="s">
         <v>4</v>
@@ -3223,10 +2728,10 @@
         <v>5</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C31" s="7" t="s">
-        <v>47</v>
+        <v>26</v>
+      </c>
+      <c r="C31" s="6" t="s">
+        <v>66</v>
       </c>
       <c r="E31" s="3" t="s">
         <v>4</v>
@@ -3237,10 +2742,10 @@
         <v>5</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>65</v>
+        <v>94</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>4</v>
@@ -3251,10 +2756,10 @@
         <v>5</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>81</v>
+        <v>97</v>
       </c>
       <c r="E33" s="3" t="s">
         <v>4</v>
@@ -3265,10 +2770,10 @@
         <v>5</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>84</v>
+        <v>67</v>
       </c>
       <c r="E34" s="3" t="s">
         <v>4</v>
@@ -3279,10 +2784,10 @@
         <v>5</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>85</v>
+        <v>106</v>
       </c>
       <c r="E35" s="3" t="s">
         <v>4</v>
@@ -3292,11 +2797,11 @@
       <c r="A36" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B36" s="4" t="s">
-        <v>37</v>
+      <c r="B36" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>36</v>
+        <v>69</v>
       </c>
       <c r="E36" s="3" t="s">
         <v>4</v>
@@ -3307,10 +2812,10 @@
         <v>5</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="E37" s="3" t="s">
         <v>4</v>
@@ -3321,10 +2826,10 @@
         <v>5</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="E38" s="3" t="s">
         <v>4</v>
@@ -3335,10 +2840,10 @@
         <v>5</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>86</v>
+        <v>72</v>
       </c>
       <c r="E39" s="3" t="s">
         <v>4</v>
@@ -3349,10 +2854,10 @@
         <v>5</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="E40" s="3" t="s">
         <v>4</v>
@@ -3366,7 +2871,7 @@
         <v>10</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="E41" s="3" t="s">
         <v>4</v>
@@ -3380,7 +2885,7 @@
         <v>10</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="E42" s="3" t="s">
         <v>4</v>
@@ -3394,7 +2899,7 @@
         <v>10</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>90</v>
+        <v>76</v>
       </c>
       <c r="E43" s="3" t="s">
         <v>4</v>
@@ -3408,7 +2913,7 @@
         <v>10</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="E44" s="3" t="s">
         <v>4</v>
@@ -3422,7 +2927,7 @@
         <v>10</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="E45" s="3" t="s">
         <v>4</v>
@@ -3436,7 +2941,7 @@
         <v>10</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="E46" s="3" t="s">
         <v>4</v>
@@ -3450,7 +2955,7 @@
         <v>10</v>
       </c>
       <c r="C47" s="6" t="s">
-        <v>95</v>
+        <v>34</v>
       </c>
       <c r="E47" s="3" t="s">
         <v>4</v>
@@ -3461,10 +2966,10 @@
         <v>5</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C48" s="6" t="s">
-        <v>96</v>
+        <v>80</v>
       </c>
       <c r="E48" s="3" t="s">
         <v>4</v>
@@ -3475,10 +2980,10 @@
         <v>5</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>97</v>
+        <v>81</v>
       </c>
       <c r="E49" s="3" t="s">
         <v>4</v>
@@ -3489,10 +2994,10 @@
         <v>5</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="C50" s="6" t="s">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="E50" s="3" t="s">
         <v>4</v>
@@ -3503,10 +3008,10 @@
         <v>5</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="C51" s="6" t="s">
-        <v>99</v>
+        <v>83</v>
       </c>
       <c r="E51" s="3" t="s">
         <v>4</v>
@@ -3517,10 +3022,10 @@
         <v>5</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>100</v>
+        <v>84</v>
       </c>
       <c r="E52" s="3" t="s">
         <v>4</v>
@@ -3531,10 +3036,10 @@
         <v>5</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="C53" s="6" t="s">
-        <v>101</v>
+        <v>89</v>
       </c>
       <c r="E53" s="3" t="s">
         <v>4</v>
@@ -3545,10 +3050,10 @@
         <v>5</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="C54" s="6" t="s">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="E54" s="3" t="s">
         <v>4</v>
@@ -3559,10 +3064,10 @@
         <v>5</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="C55" s="6" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="E55" s="3" t="s">
         <v>4</v>
@@ -3573,10 +3078,10 @@
         <v>5</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="C56" s="6" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="E56" s="3" t="s">
         <v>4</v>
@@ -3587,10 +3092,10 @@
         <v>5</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>105</v>
+        <v>93</v>
       </c>
       <c r="E57" s="3" t="s">
         <v>4</v>
@@ -3601,10 +3106,10 @@
         <v>5</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="C58" s="6" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="E58" s="3" t="s">
         <v>4</v>
@@ -3615,10 +3120,10 @@
         <v>5</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="C59" s="6" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="E59" s="3" t="s">
         <v>4</v>
@@ -3629,10 +3134,10 @@
         <v>5</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C60" s="6" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E60" s="3" t="s">
         <v>4</v>
@@ -3643,10 +3148,10 @@
         <v>5</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C61" s="6" t="s">
-        <v>35</v>
+        <v>87</v>
       </c>
       <c r="E61" s="3" t="s">
         <v>4</v>
@@ -3657,10 +3162,10 @@
         <v>5</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C62" s="6" t="s">
-        <v>109</v>
+        <v>88</v>
       </c>
       <c r="E62" s="3" t="s">
         <v>4</v>
@@ -3671,10 +3176,10 @@
         <v>5</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>27</v>
+        <v>6</v>
       </c>
       <c r="C63" s="6" t="s">
-        <v>110</v>
+        <v>86</v>
       </c>
       <c r="E63" s="3" t="s">
         <v>4</v>
@@ -3685,10 +3190,10 @@
         <v>5</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="C64" s="6" t="s">
-        <v>111</v>
+        <v>85</v>
       </c>
       <c r="E64" s="3" t="s">
         <v>4</v>
@@ -3699,10 +3204,10 @@
         <v>5</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="C65" s="6" t="s">
-        <v>112</v>
+        <v>59</v>
       </c>
       <c r="E65" s="3" t="s">
         <v>4</v>
@@ -3713,10 +3218,10 @@
         <v>5</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="C66" s="6" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="E66" s="3" t="s">
         <v>4</v>
@@ -3727,10 +3232,10 @@
         <v>5</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="C67" s="6" t="s">
-        <v>114</v>
+        <v>56</v>
       </c>
       <c r="E67" s="3" t="s">
         <v>4</v>
@@ -3741,10 +3246,10 @@
         <v>5</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="C68" s="6" t="s">
-        <v>115</v>
+        <v>57</v>
       </c>
       <c r="E68" s="3" t="s">
         <v>4</v>
@@ -3755,10 +3260,10 @@
         <v>5</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="C69" s="6" t="s">
-        <v>121</v>
+        <v>58</v>
       </c>
       <c r="E69" s="3" t="s">
         <v>4</v>
@@ -3769,10 +3274,10 @@
         <v>5</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="C70" s="6" t="s">
-        <v>122</v>
+        <v>54</v>
       </c>
       <c r="E70" s="3" t="s">
         <v>4</v>
@@ -3780,378 +3285,112 @@
     </row>
     <row r="71" spans="1:5" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A71" s="2" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="C71" s="6" t="s">
-        <v>123</v>
+        <v>53</v>
       </c>
       <c r="E71" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="72" spans="1:5" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:5" s="1" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A72" s="2" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="C72" s="6" t="s">
-        <v>124</v>
-      </c>
+        <v>96</v>
+      </c>
+      <c r="D72" s="2"/>
       <c r="E72" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="73" spans="1:5" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:5" s="1" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A73" s="2" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="C73" s="6" t="s">
-        <v>125</v>
-      </c>
+        <v>55</v>
+      </c>
+      <c r="D73" s="2"/>
       <c r="E73" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="74" spans="1:5" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:5" s="1" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A74" s="2" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="C74" s="6" t="s">
-        <v>126</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="D74" s="2"/>
       <c r="E74" s="3" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="75" spans="1:5" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A75" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B75" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C75" s="6" t="s">
-        <v>34</v>
-      </c>
+      <c r="A75" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C75" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="D75" s="1"/>
       <c r="E75" s="3" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="76" spans="1:5" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A76" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B76" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C76" s="6" t="s">
-        <v>119</v>
-      </c>
+      <c r="A76" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C76" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="D76" s="1"/>
       <c r="E76" s="3" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="77" spans="1:5" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A77" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B77" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C77" s="6" t="s">
-        <v>118</v>
+      <c r="A77" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B77" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C77" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="D77" s="3" t="s">
+        <v>32</v>
       </c>
       <c r="E77" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="78" spans="1:5" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A78" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B78" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C78" s="6" t="s">
-        <v>120</v>
-      </c>
-      <c r="E78" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A79" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B79" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C79" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="E79" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A80" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B80" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C80" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="E80" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A81" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B81" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C81" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="E81" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A82" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B82" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C82" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="E82" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A83" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B83" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C83" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="E83" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="84" spans="1:5" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A84" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B84" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C84" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="E84" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="85" spans="1:5" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A85" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B85" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C85" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="E85" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="86" spans="1:5" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A86" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B86" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C86" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="E86" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="87" spans="1:5" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A87" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B87" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C87" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="E87" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="88" spans="1:5" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A88" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B88" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C88" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="E88" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="89" spans="1:5" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A89" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B89" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C89" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="E89" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="90" spans="1:5" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A90" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B90" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C90" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="E90" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="91" spans="1:5" s="1" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A91" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B91" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C91" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="D91" s="2"/>
-      <c r="E91" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="92" spans="1:5" s="1" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A92" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B92" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C92" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="D92" s="2"/>
-      <c r="E92" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="93" spans="1:5" s="1" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A93" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B93" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C93" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="D93" s="2"/>
-      <c r="E93" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="94" spans="1:5" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A94" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B94" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C94" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="D94" s="1"/>
-      <c r="E94" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="95" spans="1:5" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A95" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B95" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C95" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="D95" s="1"/>
-      <c r="E95" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="96" spans="1:5" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A96" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="B96" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C96" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="D96" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="E96" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:D96">
+  <autoFilter ref="A1:D77">
     <sortState ref="A2:D91">
       <sortCondition descending="1" ref="A1:A91"/>
     </sortState>

--- a/408/OS/2024/ModularAutomation/reports/testcases.xlsx
+++ b/408/OS/2024/ModularAutomation/reports/testcases.xlsx
@@ -48,6 +48,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -58,6 +59,7 @@
         <sz val="11"/>
         <color rgb="FFFF0000"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -186,54 +188,6 @@
   </si>
   <si>
     <t>devSta.del</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>{
-    "network": {
-        "wan": [
-            {
-                "metric": "0",
-                "macaddr": "10:82:3d:f4:32:a0'flagthn'",
-                "special_line": "0",
-                "proto": "dhcp"
-            }
-        ],
-        "lan": [
-            {
-                "macaddr": "10:82:3d:f4:32:9e",
-                "lastaddr": "192.168.110.1",
-                "netmask": "255.255.255.0",
-                "leasetime": "30",
-                "ipstart": "192.168.110.1",
-                "proto": "static",
-                "ipaddr": "192.168.110.1",
-                "vlanid": "233",
-                "ignore": "0",
-                "limit": "254",
-                "conflict": "false"
-            },
-            {
-                "ignore": "0",
-                "netmask": "255.255.255.0",
-                "macaddr": "10:82:3D:9E:21:50",
-                "leasetime": "30",
-                "ovlanid": "",
-                "ipstart": "192.161.12.1",
-                "lastaddr": "192.161.12.2",
-                "limit": "254",
-                "ipaddr": "192.161.12.2",
-                "vlanid": "33"
-            }
-        ],
-        "version": "1.0.0",
-        "configTime": "1680599423",
-        "configId": "1680599423",
-        "currentTime": "1680599423",
-        "wanNum": "1",
-        "lanNum": "2"
-    }
-}</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -1871,6 +1825,54 @@
 }</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
+  <si>
+    <t>{
+    "network": {
+        "wan": [
+            {
+                "metric": "0",
+                "macaddr": "10:82:3d:f4:32:a0'flagthn'",
+                "special_line": "0",
+                "proto": "dhcp"
+            }
+        ],
+        "lan": [
+            {
+                "macaddr": "10:82:3d:f4:32:9e",
+                "lastaddr": "192.168.110.1",
+                "netmask": "255.255.255.0",
+                "leasetime": "30",
+                "ipstart": "192.168.110.1",
+                "proto": "static",
+                "ipaddr": "192.168.110.1",
+                "vlanid": "233",
+                "ignore": "0",
+                "limit": "254",
+                "conflict": "false"
+            },
+            {
+                "ignore": "0",
+                "netmask": "255.255.255.0",
+                "macaddr": "10:82:3D:9E:21:50",
+                "leasetime": "30",
+                "ovlanid": "",
+                "ipstart": "192.161.12.1",
+                "lastaddr": "192.161.12.2",
+                "limit": "254",
+                "ipaddr": "192.161.12.2",
+                "vlanid": "33"
+            }
+        ],
+        "version": "1.0.0",
+        "configTime": "1680599423",
+        "configId": "1680599423",
+        "currentTime": "1680599423",
+        "wanNum": "1",
+        "lanNum": "2"
+    }
+}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -1888,12 +1890,14 @@
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -2322,7 +2326,7 @@
         <v>25</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>7</v>
@@ -2339,7 +2343,7 @@
         <v>30</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>37</v>
+        <v>108</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>4</v>
@@ -2353,7 +2357,7 @@
         <v>21</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>4</v>
@@ -2367,7 +2371,7 @@
         <v>22</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>4</v>
@@ -2381,7 +2385,7 @@
         <v>20</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>4</v>
@@ -2395,7 +2399,7 @@
         <v>19</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>4</v>
@@ -2409,7 +2413,7 @@
         <v>16</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>4</v>
@@ -2423,7 +2427,7 @@
         <v>28</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>4</v>
@@ -2437,7 +2441,7 @@
         <v>15</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>4</v>
@@ -2451,7 +2455,7 @@
         <v>9</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>4</v>
@@ -2465,7 +2469,7 @@
         <v>9</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>4</v>
@@ -2479,7 +2483,7 @@
         <v>9</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>4</v>
@@ -2493,7 +2497,7 @@
         <v>9</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>4</v>
@@ -2507,7 +2511,7 @@
         <v>9</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>4</v>
@@ -2521,7 +2525,7 @@
         <v>9</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>4</v>
@@ -2535,7 +2539,7 @@
         <v>9</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>4</v>
@@ -2549,7 +2553,7 @@
         <v>9</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>4</v>
@@ -2563,7 +2567,7 @@
         <v>9</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>4</v>
@@ -2577,7 +2581,7 @@
         <v>9</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>4</v>
@@ -2591,7 +2595,7 @@
         <v>9</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>4</v>
@@ -2605,7 +2609,7 @@
         <v>11</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>4</v>
@@ -2619,7 +2623,7 @@
         <v>11</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>4</v>
@@ -2633,7 +2637,7 @@
         <v>11</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>4</v>
@@ -2647,7 +2651,7 @@
         <v>11</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E25" s="3" t="s">
         <v>4</v>
@@ -2661,7 +2665,7 @@
         <v>11</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>4</v>
@@ -2689,7 +2693,7 @@
         <v>26</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E28" s="3" t="s">
         <v>4</v>
@@ -2703,7 +2707,7 @@
         <v>26</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E29" s="3" t="s">
         <v>4</v>
@@ -2717,7 +2721,7 @@
         <v>26</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E30" s="3" t="s">
         <v>4</v>
@@ -2731,7 +2735,7 @@
         <v>26</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E31" s="3" t="s">
         <v>4</v>
@@ -2745,7 +2749,7 @@
         <v>10</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>4</v>
@@ -2759,7 +2763,7 @@
         <v>10</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E33" s="3" t="s">
         <v>4</v>
@@ -2773,7 +2777,7 @@
         <v>10</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E34" s="3" t="s">
         <v>4</v>
@@ -2787,7 +2791,7 @@
         <v>10</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E35" s="3" t="s">
         <v>4</v>
@@ -2801,7 +2805,7 @@
         <v>10</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E36" s="3" t="s">
         <v>4</v>
@@ -2815,7 +2819,7 @@
         <v>10</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E37" s="3" t="s">
         <v>4</v>
@@ -2829,7 +2833,7 @@
         <v>10</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E38" s="3" t="s">
         <v>4</v>
@@ -2843,7 +2847,7 @@
         <v>10</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E39" s="3" t="s">
         <v>4</v>
@@ -2857,7 +2861,7 @@
         <v>10</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E40" s="3" t="s">
         <v>4</v>
@@ -2871,7 +2875,7 @@
         <v>10</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E41" s="3" t="s">
         <v>4</v>
@@ -2885,7 +2889,7 @@
         <v>10</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E42" s="3" t="s">
         <v>4</v>
@@ -2899,7 +2903,7 @@
         <v>10</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E43" s="3" t="s">
         <v>4</v>
@@ -2913,7 +2917,7 @@
         <v>10</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E44" s="3" t="s">
         <v>4</v>
@@ -2927,7 +2931,7 @@
         <v>10</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E45" s="3" t="s">
         <v>4</v>
@@ -2941,7 +2945,7 @@
         <v>10</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E46" s="3" t="s">
         <v>4</v>
@@ -2969,7 +2973,7 @@
         <v>8</v>
       </c>
       <c r="C48" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E48" s="3" t="s">
         <v>4</v>
@@ -2983,7 +2987,7 @@
         <v>27</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E49" s="3" t="s">
         <v>4</v>
@@ -2997,7 +3001,7 @@
         <v>23</v>
       </c>
       <c r="C50" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E50" s="3" t="s">
         <v>4</v>
@@ -3011,7 +3015,7 @@
         <v>23</v>
       </c>
       <c r="C51" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E51" s="3" t="s">
         <v>4</v>
@@ -3025,7 +3029,7 @@
         <v>23</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E52" s="3" t="s">
         <v>4</v>
@@ -3039,7 +3043,7 @@
         <v>23</v>
       </c>
       <c r="C53" s="6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E53" s="3" t="s">
         <v>4</v>
@@ -3053,7 +3057,7 @@
         <v>23</v>
       </c>
       <c r="C54" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E54" s="3" t="s">
         <v>4</v>
@@ -3067,7 +3071,7 @@
         <v>23</v>
       </c>
       <c r="C55" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E55" s="3" t="s">
         <v>4</v>
@@ -3081,7 +3085,7 @@
         <v>23</v>
       </c>
       <c r="C56" s="6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E56" s="3" t="s">
         <v>4</v>
@@ -3095,7 +3099,7 @@
         <v>23</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E57" s="3" t="s">
         <v>4</v>
@@ -3109,7 +3113,7 @@
         <v>23</v>
       </c>
       <c r="C58" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E58" s="3" t="s">
         <v>4</v>
@@ -3123,7 +3127,7 @@
         <v>23</v>
       </c>
       <c r="C59" s="6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E59" s="3" t="s">
         <v>4</v>
@@ -3137,7 +3141,7 @@
         <v>6</v>
       </c>
       <c r="C60" s="6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E60" s="3" t="s">
         <v>4</v>
@@ -3151,7 +3155,7 @@
         <v>6</v>
       </c>
       <c r="C61" s="6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E61" s="3" t="s">
         <v>4</v>
@@ -3165,7 +3169,7 @@
         <v>6</v>
       </c>
       <c r="C62" s="6" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E62" s="3" t="s">
         <v>4</v>
@@ -3179,7 +3183,7 @@
         <v>6</v>
       </c>
       <c r="C63" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E63" s="3" t="s">
         <v>4</v>
@@ -3193,7 +3197,7 @@
         <v>17</v>
       </c>
       <c r="C64" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E64" s="3" t="s">
         <v>4</v>
@@ -3207,7 +3211,7 @@
         <v>17</v>
       </c>
       <c r="C65" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E65" s="3" t="s">
         <v>4</v>
@@ -3221,7 +3225,7 @@
         <v>17</v>
       </c>
       <c r="C66" s="6" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E66" s="3" t="s">
         <v>4</v>
@@ -3235,7 +3239,7 @@
         <v>17</v>
       </c>
       <c r="C67" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E67" s="3" t="s">
         <v>4</v>
@@ -3249,7 +3253,7 @@
         <v>17</v>
       </c>
       <c r="C68" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E68" s="3" t="s">
         <v>4</v>
@@ -3263,7 +3267,7 @@
         <v>17</v>
       </c>
       <c r="C69" s="6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E69" s="3" t="s">
         <v>4</v>
@@ -3277,7 +3281,7 @@
         <v>17</v>
       </c>
       <c r="C70" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E70" s="3" t="s">
         <v>4</v>
@@ -3291,7 +3295,7 @@
         <v>13</v>
       </c>
       <c r="C71" s="6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E71" s="3" t="s">
         <v>4</v>
@@ -3305,7 +3309,7 @@
         <v>13</v>
       </c>
       <c r="C72" s="6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D72" s="2"/>
       <c r="E72" s="3" t="s">
@@ -3320,7 +3324,7 @@
         <v>13</v>
       </c>
       <c r="C73" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D73" s="2"/>
       <c r="E73" s="3" t="s">
@@ -3335,7 +3339,7 @@
         <v>33</v>
       </c>
       <c r="C74" s="6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D74" s="2"/>
       <c r="E74" s="3" t="s">
@@ -3350,7 +3354,7 @@
         <v>8</v>
       </c>
       <c r="C75" s="8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D75" s="1"/>
       <c r="E75" s="3" t="s">
@@ -3365,7 +3369,7 @@
         <v>31</v>
       </c>
       <c r="C76" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D76" s="1"/>
       <c r="E76" s="3" t="s">

--- a/408/OS/2024/ModularAutomation/reports/testcases.xlsx
+++ b/408/OS/2024/ModularAutomation/reports/testcases.xlsx
@@ -281,25 +281,6 @@
                 "]}'flagthn'{["
             ]
         }
-    },
-    "device": "pc"
-}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>{
-    "module": "repeater_hostrouter",
-    "noParse": true,
-    "async": null,
-    "remoteIp": false,
-    "data": {
-        "repeater": {
-            "ssid": "123",
-            "channel": "flagthn",
-            "enable": "true",
-            "bssid": "ssdf"
-        },
-        "repeater_5g": "1"
     },
     "device": "pc"
 }</t>
@@ -1728,6 +1709,33 @@
     ],
     "password": "x",
     "type": "enc"
+}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{
+    "module": "repeater_hostrouter",
+    "noParse": true,
+    "async": null,
+    "remoteIp": false,
+    "data": {
+        "repeater": {
+            "ssid": "LostXmas20291224",
+            "channel": "36",
+            "authMode": "OPEN",
+            "encrypType": "NONE",
+            "enable": "true",
+            "bssid": "58:69:ab:31:1b:93",
+            "ssidEncode": "gbk"
+        },
+        "repeater_5g": {
+            "radio": "5G",
+            "enable": "true"
+        },
+        "mode": "wisp",
+        "radop": "5G"
+    },
+    "device": "pc"
 }</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -2176,7 +2184,7 @@
         <v>24</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>7</v>
@@ -2193,7 +2201,7 @@
         <v>29</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>4</v>
@@ -2207,7 +2215,7 @@
         <v>20</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>4</v>
@@ -2221,7 +2229,7 @@
         <v>21</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>4</v>
@@ -2235,7 +2243,7 @@
         <v>19</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>4</v>
@@ -2249,7 +2257,7 @@
         <v>18</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>4</v>
@@ -2263,7 +2271,7 @@
         <v>15</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>4</v>
@@ -2277,7 +2285,7 @@
         <v>27</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>4</v>
@@ -2288,10 +2296,10 @@
         <v>14</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>4</v>
@@ -2305,7 +2313,7 @@
         <v>9</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>4</v>
@@ -2319,7 +2327,7 @@
         <v>9</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>4</v>
@@ -2333,7 +2341,7 @@
         <v>9</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>4</v>
@@ -2347,7 +2355,7 @@
         <v>9</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>4</v>
@@ -2361,7 +2369,7 @@
         <v>9</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>4</v>
@@ -2375,7 +2383,7 @@
         <v>9</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>4</v>
@@ -2389,7 +2397,7 @@
         <v>9</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>4</v>
@@ -2417,7 +2425,7 @@
         <v>9</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>4</v>
@@ -2431,7 +2439,7 @@
         <v>9</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>4</v>
@@ -2445,7 +2453,7 @@
         <v>9</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>4</v>
@@ -2459,7 +2467,7 @@
         <v>11</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>4</v>
@@ -2473,7 +2481,7 @@
         <v>11</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>4</v>
@@ -2501,7 +2509,7 @@
         <v>33</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E25" s="3" t="s">
         <v>4</v>
@@ -2515,7 +2523,7 @@
         <v>25</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>4</v>
@@ -2543,7 +2551,7 @@
         <v>25</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E28" s="3" t="s">
         <v>4</v>
@@ -2571,7 +2579,7 @@
         <v>10</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>39</v>
+        <v>101</v>
       </c>
       <c r="E30" s="3" t="s">
         <v>4</v>
@@ -2585,7 +2593,7 @@
         <v>10</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E31" s="3" t="s">
         <v>4</v>
@@ -2599,7 +2607,7 @@
         <v>10</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>4</v>
@@ -2613,7 +2621,7 @@
         <v>10</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E33" s="3" t="s">
         <v>4</v>
@@ -2627,7 +2635,7 @@
         <v>10</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E34" s="3" t="s">
         <v>4</v>
@@ -2641,7 +2649,7 @@
         <v>10</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E35" s="3" t="s">
         <v>4</v>
@@ -2655,7 +2663,7 @@
         <v>10</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E36" s="3" t="s">
         <v>4</v>
@@ -2669,7 +2677,7 @@
         <v>10</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E37" s="3" t="s">
         <v>4</v>
@@ -2683,7 +2691,7 @@
         <v>10</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E38" s="3" t="s">
         <v>4</v>
@@ -2697,7 +2705,7 @@
         <v>10</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E39" s="3" t="s">
         <v>4</v>
@@ -2711,7 +2719,7 @@
         <v>10</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E40" s="3" t="s">
         <v>4</v>
@@ -2725,7 +2733,7 @@
         <v>10</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E41" s="3" t="s">
         <v>4</v>
@@ -2739,7 +2747,7 @@
         <v>10</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E42" s="3" t="s">
         <v>4</v>
@@ -2753,7 +2761,7 @@
         <v>10</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E43" s="3" t="s">
         <v>4</v>
@@ -2767,7 +2775,7 @@
         <v>8</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E44" s="3" t="s">
         <v>4</v>
@@ -2781,7 +2789,7 @@
         <v>26</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E45" s="3" t="s">
         <v>4</v>
@@ -2795,7 +2803,7 @@
         <v>22</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E46" s="3" t="s">
         <v>4</v>
@@ -2809,7 +2817,7 @@
         <v>22</v>
       </c>
       <c r="C47" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E47" s="3" t="s">
         <v>4</v>
@@ -2823,7 +2831,7 @@
         <v>22</v>
       </c>
       <c r="C48" s="6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E48" s="3" t="s">
         <v>4</v>
@@ -2837,7 +2845,7 @@
         <v>22</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E49" s="3" t="s">
         <v>4</v>
@@ -2851,7 +2859,7 @@
         <v>22</v>
       </c>
       <c r="C50" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E50" s="3" t="s">
         <v>4</v>
@@ -2865,7 +2873,7 @@
         <v>22</v>
       </c>
       <c r="C51" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E51" s="3" t="s">
         <v>4</v>
@@ -2879,7 +2887,7 @@
         <v>22</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E52" s="3" t="s">
         <v>4</v>
@@ -2893,7 +2901,7 @@
         <v>22</v>
       </c>
       <c r="C53" s="6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E53" s="3" t="s">
         <v>4</v>
@@ -2907,7 +2915,7 @@
         <v>22</v>
       </c>
       <c r="C54" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E54" s="3" t="s">
         <v>4</v>
@@ -2921,7 +2929,7 @@
         <v>22</v>
       </c>
       <c r="C55" s="6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E55" s="3" t="s">
         <v>4</v>
@@ -2935,7 +2943,7 @@
         <v>6</v>
       </c>
       <c r="C56" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E56" s="3" t="s">
         <v>4</v>
@@ -2949,7 +2957,7 @@
         <v>6</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E57" s="3" t="s">
         <v>4</v>
@@ -2963,7 +2971,7 @@
         <v>16</v>
       </c>
       <c r="C58" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E58" s="3" t="s">
         <v>4</v>
@@ -2977,7 +2985,7 @@
         <v>16</v>
       </c>
       <c r="C59" s="6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E59" s="3" t="s">
         <v>4</v>
@@ -2991,7 +2999,7 @@
         <v>16</v>
       </c>
       <c r="C60" s="6" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E60" s="3" t="s">
         <v>4</v>
@@ -3005,7 +3013,7 @@
         <v>16</v>
       </c>
       <c r="C61" s="6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E61" s="3" t="s">
         <v>4</v>
@@ -3019,7 +3027,7 @@
         <v>16</v>
       </c>
       <c r="C62" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E62" s="3" t="s">
         <v>4</v>
@@ -3047,7 +3055,7 @@
         <v>13</v>
       </c>
       <c r="C64" s="6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E64" s="3" t="s">
         <v>4</v>
@@ -3061,7 +3069,7 @@
         <v>13</v>
       </c>
       <c r="C65" s="6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D65" s="2"/>
       <c r="E65" s="3" t="s">
@@ -3076,7 +3084,7 @@
         <v>13</v>
       </c>
       <c r="C66" s="6" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D66" s="2"/>
       <c r="E66" s="3" t="s">
@@ -3091,7 +3099,7 @@
         <v>32</v>
       </c>
       <c r="C67" s="6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D67" s="2"/>
       <c r="E67" s="3" t="s">
@@ -3106,7 +3114,7 @@
         <v>30</v>
       </c>
       <c r="C68" s="9" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D68" s="1"/>
       <c r="E68" s="3" t="s">

--- a/408/OS/2024/ModularAutomation/reports/testcases.xlsx
+++ b/408/OS/2024/ModularAutomation/reports/testcases.xlsx
@@ -1719,13 +1719,15 @@
     "async": null,
     "remoteIp": false,
     "data": {
+        "network": "xxx",
         "repeater": {
-            "ssid": "LostXmas20291224",
+            "radio": "2.4G",
+            "ssid": "123",
             "channel": "36",
+            "enable": "true",
+            "bssid": "58:69:ab:31:1b:93",
             "authMode": "OPEN",
             "encrypType": "NONE",
-            "enable": "true",
-            "bssid": "58:69:ab:31:1b:93",
             "ssidEncode": "gbk"
         },
         "repeater_5g": {

--- a/408/OS/2024/ModularAutomation/reports/testcases.xlsx
+++ b/408/OS/2024/ModularAutomation/reports/testcases.xlsx
@@ -232,18 +232,6 @@
     "data":{
         "enable":"1",
         "periodic_interval":"periodic_interval"
-    },
-    "device":"pc"
-}</t>
-  </si>
-  <si>
-    <t>{
-    "module":"networkConnect",
-    "noParse":true,
-    "async":null,
-    "remoteIp":false,
-    "data":{
-        "ifname":"ifname"
     },
     "device":"pc"
 }</t>
@@ -524,6 +512,18 @@
   </si>
   <si>
     <t>devSta.get</t>
+  </si>
+  <si>
+    <t>{
+    "module":"networkConnect",
+    "noParse":true,
+    "async":null,
+    "remoteIp":false,
+    "data":{
+        "ifname":"ifname"
+    },
+    "device":"pc"
+}</t>
   </si>
   <si>
     <t>{
@@ -3062,10 +3062,10 @@
         <v>28</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E25" s="5" t="s">
         <v>4</v>
@@ -3076,7 +3076,7 @@
         <v>28</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C26" s="6" t="s">
         <v>46</v>
@@ -3090,7 +3090,7 @@
         <v>28</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C27" s="6" t="s">
         <v>47</v>
@@ -3104,7 +3104,7 @@
         <v>28</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C28" s="6" t="s">
         <v>48</v>
@@ -3121,7 +3121,7 @@
         <v>49</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E29" s="5" t="s">
         <v>4</v>

--- a/408/OS/2024/ModularAutomation/reports/testcases.xlsx
+++ b/408/OS/2024/ModularAutomation/reports/testcases.xlsx
@@ -10,7 +10,7 @@
     <sheet name="#TEMP" sheetId="4" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'#TEMP'!$A$1:$D$73</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'#TEMP'!$A$1:$D$91</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="367" uniqueCount="122">
   <si>
     <t>接口</t>
   </si>
@@ -207,6 +207,77 @@
   </si>
   <si>
     <t>devSta.set</t>
+  </si>
+  <si>
+    <t>{
+    "module": "rlog_module_info",
+    "noParse": true,
+    "async": null,
+    "remoteIp": false,
+    "data": {
+        "test": "111"
+    },
+    "device": "pc"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "module": "iptv",
+    "noParse": true,
+    "async": null,
+    "remoteIp": false,
+    "data": {
+        "enable": "1",
+        "list": [
+            {
+                "port": "2",
+                "tag": "U"
+            }
+        ],
+        "vlanid": "1",
+        "force": ""
+    },
+    "device": "pc"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "module": "uu_acc",
+    "noParse": true,
+    "async": null,
+    "remoteIp": false,
+    "data": {
+        "option": "onoff",
+        "enable": "true"
+    },
+    "device": "pc"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "module": "rcgame",
+    "noParse": true,
+    "async": null,
+    "remoteIp": false,
+    "data": {
+        "enabled": "false",
+        "device_list": [],
+        "loss": "100%",
+        "study": "off",
+        "mtkhnat": "1",
+        "delay_pro": "0%",
+        "game_port": "open",
+        "games": [],
+        "switch_game": "off",
+        "device": "off",
+        "switch_game_list": [],
+        "loss_pro": "0%",
+        "game": "off",
+        "delay": "1000ms",
+        "flowctrl": "0"
+    },
+    "device": "pc"
+}</t>
   </si>
   <si>
     <t>{
@@ -511,7 +582,54 @@
 }</t>
   </si>
   <si>
+    <t>{
+    "module":"gamng",
+    "noParse":false,
+    "async":null,
+    "remoteIp":false,
+    "data":{
+        "name":"ybb_acc",
+        "option":"install"
+    },
+    "device":"pc"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "module": "firmware_exist",
+    "noParse": false,
+    "async": null,
+    "remoteIp": false,
+    "data": {
+        "user": "xxx"
+    },
+    "device": "pc"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "module": "eweb_menu",
+    "noParse": false,
+    "async": null,
+    "remoteIp": false,
+    "data": {},
+    "device": "pc"
+}</t>
+  </si>
+  <si>
     <t>devSta.get</t>
+  </si>
+  <si>
+    <t>{
+    "module": "rlog_module_enable",
+    "noParse": true,
+    "async": null,
+    "remoteIp": false,
+    "data": {
+        "module": "sta"
+    },
+    "device": "pc"
+}</t>
   </si>
   <si>
     <t>{
@@ -678,6 +796,163 @@
   </si>
   <si>
     <t>{
+    "module": "rlog_config",
+    "noParse": true,
+    "async": null,
+    "remoteIp": false,
+    "data": {
+        "enable": "0",
+        "tarsaveAll": "1"
+    },
+    "device": "pc"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "module": "pptp_lcp_client_interval",
+    "noParse": true,
+    "async": null,
+    "remoteIp": false,
+    "data": {
+        "lcpechointerval": "20"
+    },
+    "device": "pc"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "module": "pptp_client",
+    "noParse": true,
+    "async": null,
+    "remoteIp": false,
+    "data": {
+        "tunnelname": "pptpflagthn",
+        "username": "",
+        "password": "",
+        "intf_binding": "WAN",
+        "lns": "",
+        "remotesubnet": "",
+        "remotesubnetArr": [
+            "192.168.110.0/24"
+        ],
+        "redirect_gateway": "0",
+        "workmode": "nat",
+        "lcpechointerval": "10",
+        "local_ip": "",
+        "enable": "0",
+        "mppe": "0"
+    },
+    "device": "pc"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "module": "pptp_server",
+    "noParse": true,
+    "async": null,
+    "remoteIp": false,
+    "data": {
+        "enable": "0",
+        "version": "1.0.0",
+        "configId": "0",
+        "configTime": "0",
+        "currentTime": "0"
+    },
+    "device": "pc"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "module": "child_guard",
+    "noParse": true,
+    "async": null,
+    "remoteIp": false,
+    "data": {
+        "guardPolicy": [
+            {
+                "name": "be:26:03:4d:75:88_child_guard",
+                "auditPolicy": {
+                    "urlFbtEnable": "0",
+                    "appFbtList": [
+                        "Video"
+                    ],
+                    "subAppFbtList": [
+                        {
+                            "list": [],
+                            "type": "Video"
+                        },
+                        {
+                            "type": "Communication",
+                            "list": [
+                                "豆瓣"
+                            ]
+                        }
+                    ],
+                    "urlFbtList": []
+                }
+            },
+            {
+                "name": "be:26:03:ff:ff:88_child_guard",
+                "auditPolicy": {
+                    "urlFbtEnable": "0",
+                    "appFbtList": [
+                        "Video"
+                    ],
+                    "subAppFbtList": [
+                        {
+                            "list": [],
+                            "type": "Video"
+                        },
+                        {
+                            "type": "Communication",
+                            "list": [
+                                "豆瓣",
+                                "小红书"
+                            ]
+                        }
+                    ],
+                    "urlFbtList": []
+                }
+            }
+        ],
+        "guardUser": [
+            {
+                "mac": "be:26:03:4d:75:88",
+                "name": "Redmi-K60",
+                "policy": "be:26:03:4d:75:88_child_guard",
+                "pause": "0",
+                "disconnect": "0"
+            },
+            {
+                "mac": "be:26:03:ff:ff:88",
+                "name": "Redmi-K60tttttest",
+                "policy": "be:26:03:ff:ff:88_child_guard",
+                "pause": "0",
+                "disconnect": "0"
+            }
+        ]
+    },
+    "device": "pc"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "module": "igmpproxy",
+    "noParse": true,
+    "async": null,
+    "remoteIp": false,
+    "data": {
+        "enable": "0",
+        "version": "1.0.0",
+        "configId": "0",
+        "configTime": "0",
+        "currentTime": "0"
+    },
+    "device": "pc"
+}</t>
+  </si>
+  <si>
+    <t>{
     "module": "kvNavDev",
     "noParse": true,
     "async": null,
@@ -962,6 +1237,18 @@
   </si>
   <si>
     <t>{
+    "module": "config_retain",
+    "noParse": false,
+    "async": null,
+    "remoteIp": false,
+    "data": {
+        "config_retain": "x"
+    },
+    "device": "pc"
+}</t>
+  </si>
+  <si>
+    <t>{
     "module": "rlog_module_config",
     "noParse": false,
     "async": null,
@@ -986,12 +1273,12 @@
   </si>
   <si>
     <t>{
-    "module": "config_retain",
-    "noParse": false,
-    "async": null,
-    "remoteIp": false,
-    "data": {
-        "config_retain": "x"
+    "module": "lwswitch",
+    "noParse": false,
+    "async": null,
+    "remoteIp": false,
+    "data": {
+        "enable": "false"
     },
     "device": "pc"
 }</t>
@@ -1321,40 +1608,74 @@
 }</t>
   </si>
   <si>
-    <t>{
-    "device": "pc",
-    "params": [
-        {
-            "method": "devConfig.update",
-            "params": {
-                "module": "pptp_client",
-                "noParse": false,
-                "async": null,
-                "remoteIp": false,
-                "data": {
-                    "tunnelname": "pptpflagthn",
-                    "username": "",
-                    "password": "",
-                    "intf_binding": "WAN",
-                    "lns": "",
-                    "remotesubnet": "",
-                    "remotesubnetArr": [
-                        "192.168.110.0/24"
-                    ],
-                    "redirect_gateway": "0",
-                    "workmode": "nat",
-                    "lcpechointerval": "10",
-                    "local_ip": "",
-                    "enable": "0",
-                    "mppe": "0"
-                }
+    <t>acConfig.set</t>
+  </si>
+  <si>
+    <t>{
+    "module": "wirelessMacFilter",
+    "noParse": false,
+    "async": null,
+    "remoteIp": false,
+    "data": {
+        "version": "1.0.0",
+        "networkId": "dev_00:D0:F8:E3:08:49_1693561441",
+        "groupId": "0",
+        "type": "allow",
+        "macList": [],
+        "axMacList": []
+    },
+    "device": "pc"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "module": "mesh_status",
+    "noParse": false,
+    "async": null,
+    "remoteIp": false,
+    "data": {
+        "enable": "true"
+    },
+    "device": "pc"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "module": "apselect",
+    "noParse": false,
+    "async": null,
+    "remoteIp": false,
+    "data": {
+        "apselect_list": [
+            {
+                "sel_ap": "auto",
+                "sel_band": "2.4G",
+                "mac": "50:3d:c6:96:7d:45"
             }
-        }
-    ]
-}</t>
-  </si>
-  <si>
-    <t>acConfig.set</t>
+        ]
+    },
+    "device": "pc"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "module": "timezone",
+    "noParse": false,
+    "async": null,
+    "remoteIp": false,
+    "data": {
+        "timezone": "CST+8",
+        "zonename": "Asia\/Shanghai",
+        "networkId": "dev_F0:74:8D:5D:02:C4_1717491802",
+        "groupId": "0",
+        "subConfigId": "1717491822_G1SK4AR000416",
+        "version": "1.0.0",
+        "configId": "0",
+        "configTime": "0",
+        "currentTime": "0"
+    },
+    "device": "pc"
+}</t>
   </si>
   <si>
     <t>{
@@ -1707,10 +2028,16 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -2191,141 +2518,144 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2344,7 +2674,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2704,1055 +3043,1307 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E73"/>
+  <dimension ref="A1:E91"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="39.95" customHeight="1" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="29.3796296296296" style="2" customWidth="1"/>
-    <col min="2" max="2" width="22.6296296296296" style="2" customWidth="1"/>
-    <col min="3" max="3" width="120.62962962963" style="3" customWidth="1"/>
-    <col min="4" max="4" width="11.8796296296296" style="2" customWidth="1"/>
-    <col min="5" max="5" width="13" style="2" customWidth="1"/>
-    <col min="6" max="16384" width="9" style="2"/>
+    <col min="1" max="1" width="29.3796296296296" style="3" customWidth="1"/>
+    <col min="2" max="2" width="22.6296296296296" style="3" customWidth="1"/>
+    <col min="3" max="3" width="120.62962962963" style="4" customWidth="1"/>
+    <col min="4" max="4" width="11.8796296296296" style="3" customWidth="1"/>
+    <col min="5" max="5" width="13" style="3" customWidth="1"/>
+    <col min="6" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
     <row r="1" customHeight="1" spans="1:5">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2" customHeight="1" spans="1:5">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="3" customHeight="1" spans="1:5">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="4" customHeight="1" spans="1:5">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="5" customHeight="1" spans="1:5">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="E5" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="6" customHeight="1" spans="1:5">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="E6" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="7" customHeight="1" spans="1:5">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="E7" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="8" customHeight="1" spans="1:5">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="C8" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="E8" s="5" t="s">
+      <c r="E8" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="9" customHeight="1" spans="1:5">
-      <c r="A9" s="2" t="s">
+      <c r="A9" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="C9" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="E9" s="5" t="s">
+      <c r="E9" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="10" customHeight="1" spans="1:5">
-      <c r="A10" s="2" t="s">
+      <c r="A10" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="C10" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="E10" s="5" t="s">
+      <c r="E10" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="11" customHeight="1" spans="1:5">
-      <c r="A11" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B11" s="2" t="s">
+      <c r="A11" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B11" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="C11" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="E11" s="5" t="s">
+      <c r="E11" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="12" customHeight="1" spans="1:5">
-      <c r="A12" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B12" s="2" t="s">
+      <c r="A12" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B12" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C12" s="6" t="s">
+      <c r="C12" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="E12" s="5" t="s">
+      <c r="E12" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="13" customHeight="1" spans="1:5">
-      <c r="A13" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B13" s="2" t="s">
+      <c r="A13" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B13" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C13" s="6" t="s">
+      <c r="C13" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="E13" s="5" t="s">
+      <c r="E13" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="1:5">
-      <c r="A14" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B14" s="2" t="s">
+      <c r="A14" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C14" s="6" t="s">
+      <c r="C14" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="E14" s="5" t="s">
+      <c r="E14" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="1:5">
-      <c r="A15" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B15" s="2" t="s">
+      <c r="A15" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B15" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C15" s="6" t="s">
+      <c r="C15" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="E15" s="5" t="s">
+      <c r="E15" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="16" customHeight="1" spans="1:5">
-      <c r="A16" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B16" s="2" t="s">
+      <c r="A16" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B16" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C16" s="6" t="s">
+      <c r="C16" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="E16" s="5" t="s">
+      <c r="E16" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="1:5">
-      <c r="A17" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B17" s="2" t="s">
+      <c r="A17" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B17" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C17" s="6" t="s">
+      <c r="C17" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="E17" s="5" t="s">
+      <c r="E17" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="18" customHeight="1" spans="1:5">
-      <c r="A18" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B18" s="2" t="s">
+      <c r="A18" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B18" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C18" s="6" t="s">
+      <c r="C18" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="E18" s="5" t="s">
+      <c r="E18" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="19" customHeight="1" spans="1:5">
-      <c r="A19" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B19" s="2" t="s">
+      <c r="A19" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B19" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C19" s="6" t="s">
+      <c r="C19" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="E19" s="5" t="s">
+      <c r="E19" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="20" customHeight="1" spans="1:5">
-      <c r="A20" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B20" s="2" t="s">
+      <c r="A20" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B20" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C20" s="6" t="s">
+      <c r="C20" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="E20" s="5" t="s">
+      <c r="E20" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="21" customHeight="1" spans="1:5">
-      <c r="A21" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B21" s="2" t="s">
+      <c r="A21" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B21" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C21" s="6" t="s">
+      <c r="C21" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="E21" s="5" t="s">
+      <c r="E21" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="22" customHeight="1" spans="1:5">
-      <c r="A22" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B22" s="2" t="s">
+      <c r="A22" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B22" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="6" t="s">
+      <c r="C22" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="E22" s="5" t="s">
+      <c r="E22" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="23" customHeight="1" spans="1:5">
-      <c r="A23" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B23" s="2" t="s">
+      <c r="A23" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B23" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C23" s="6" t="s">
+      <c r="C23" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="E23" s="5" t="s">
+      <c r="E23" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="24" customHeight="1" spans="1:5">
-      <c r="A24" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B24" s="2" t="s">
+      <c r="A24" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B24" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C24" s="6" t="s">
+      <c r="C24" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="E24" s="5" t="s">
+      <c r="E24" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="25" customHeight="1" spans="1:5">
-      <c r="A25" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B25" s="2" t="s">
+      <c r="A25" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C25" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="C25" s="6" t="s">
+      <c r="E25" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="26" customHeight="1" spans="1:5">
+      <c r="A26" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C26" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="E25" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="26" customHeight="1" spans="1:5">
-      <c r="A26" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="C26" s="6" t="s">
+      <c r="E26" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" customHeight="1" spans="1:5">
+      <c r="A27" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C27" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="E26" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="27" customHeight="1" spans="1:5">
-      <c r="A27" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="C27" s="6" t="s">
+      <c r="E27" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" customHeight="1" spans="1:5">
+      <c r="A28" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C28" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="E27" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="28" customHeight="1" spans="1:5">
-      <c r="A28" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="C28" s="6" t="s">
+      <c r="E28" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="29" customHeight="1" spans="1:5">
+      <c r="A29" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C29" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="E28" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="29" customHeight="1" spans="1:5">
-      <c r="A29" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B29" s="7" t="s">
+      <c r="E29" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" s="1" customFormat="1" customHeight="1" spans="1:5">
+      <c r="A30" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="B30" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="C30" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="C29" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="E29" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="30" customHeight="1" spans="1:5">
-      <c r="A30" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B30" s="2" t="s">
+      <c r="E30" s="11" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="31" s="1" customFormat="1" customHeight="1" spans="1:5">
+      <c r="A31" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="B31" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="C31" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="C30" s="6" t="s">
+      <c r="E31" s="11" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="32" customHeight="1" spans="1:5">
+      <c r="A32" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B32" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="E30" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="31" customHeight="1" spans="1:5">
-      <c r="A31" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="C31" s="6" t="s">
+      <c r="C32" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="E31" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="32" customHeight="1" spans="1:5">
-      <c r="A32" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="C32" s="6" t="s">
+      <c r="E32" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" customHeight="1" spans="1:5">
+      <c r="A33" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C33" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="E32" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="33" customHeight="1" spans="1:5">
-      <c r="A33" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B33" s="2" t="s">
+      <c r="E33" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" customHeight="1" spans="1:5">
+      <c r="A34" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C34" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="C33" s="6" t="s">
+      <c r="E34" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="35" customHeight="1" spans="1:5">
+      <c r="A35" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C35" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="E33" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="34" customHeight="1" spans="1:5">
-      <c r="A34" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="C34" s="6" t="s">
+      <c r="E35" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="36" customHeight="1" spans="1:5">
+      <c r="A36" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C36" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="E34" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="35" customHeight="1" spans="1:5">
-      <c r="A35" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="C35" s="6" t="s">
+      <c r="E36" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" customHeight="1" spans="1:5">
+      <c r="A37" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B37" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="E35" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="36" customHeight="1" spans="1:5">
-      <c r="A36" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="C36" s="6" t="s">
+      <c r="C37" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="E37" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="38" customHeight="1" spans="1:5">
+      <c r="A38" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B38" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="E36" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="37" customHeight="1" spans="1:5">
-      <c r="A37" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B37" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="C37" s="6" t="s">
+      <c r="C38" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="E37" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="38" customHeight="1" spans="1:5">
-      <c r="A38" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B38" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="C38" s="6" t="s">
+      <c r="E38" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="39" customHeight="1" spans="1:5">
+      <c r="A39" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C39" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="E38" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="39" customHeight="1" spans="1:5">
-      <c r="A39" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B39" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="C39" s="6" t="s">
+      <c r="E39" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="40" customHeight="1" spans="1:5">
+      <c r="A40" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C40" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="E39" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="40" customHeight="1" spans="1:5">
-      <c r="A40" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="C40" s="6" t="s">
+      <c r="E40" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="41" customHeight="1" spans="1:5">
+      <c r="A41" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B41" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="E40" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="41" customHeight="1" spans="1:5">
-      <c r="A41" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B41" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="C41" s="6" t="s">
+      <c r="C41" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="E41" s="5" t="s">
+      <c r="E41" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="42" customHeight="1" spans="1:5">
-      <c r="A42" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B42" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="C42" s="6" t="s">
+      <c r="A42" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C42" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="E42" s="5" t="s">
+      <c r="E42" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="43" customHeight="1" spans="1:5">
-      <c r="A43" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B43" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="C43" s="6" t="s">
+      <c r="A43" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C43" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="E43" s="5" t="s">
+      <c r="E43" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="44" customHeight="1" spans="1:5">
-      <c r="A44" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B44" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="C44" s="6" t="s">
+      <c r="A44" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C44" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="E44" s="5" t="s">
+      <c r="E44" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="45" customHeight="1" spans="1:5">
-      <c r="A45" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B45" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="C45" s="6" t="s">
+      <c r="A45" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C45" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="E45" s="5" t="s">
+      <c r="E45" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="46" customHeight="1" spans="1:5">
-      <c r="A46" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B46" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="C46" s="6" t="s">
+      <c r="A46" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C46" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="E46" s="5" t="s">
+      <c r="E46" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="47" customHeight="1" spans="1:5">
-      <c r="A47" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B47" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="C47" s="6" t="s">
+      <c r="A47" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C47" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="E47" s="5" t="s">
+      <c r="E47" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="48" customHeight="1" spans="1:5">
-      <c r="A48" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B48" s="2" t="s">
+      <c r="A48" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C48" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="C48" s="6" t="s">
+      <c r="E48" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49" customHeight="1" spans="1:5">
+      <c r="A49" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C49" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="E48" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="49" customHeight="1" spans="1:5">
-      <c r="A49" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B49" s="2" t="s">
+      <c r="E49" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="50" customHeight="1" spans="1:5">
+      <c r="A50" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C50" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="C49" s="6" t="s">
+      <c r="E50" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="51" customHeight="1" spans="1:5">
+      <c r="A51" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C51" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="E49" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="50" customHeight="1" spans="1:5">
-      <c r="A50" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B50" s="2" t="s">
+      <c r="E51" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="52" customHeight="1" spans="1:5">
+      <c r="A52" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C52" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="C50" s="6" t="s">
+      <c r="E52" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" customHeight="1" spans="1:5">
+      <c r="A53" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C53" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="E50" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="51" customHeight="1" spans="1:5">
-      <c r="A51" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B51" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="C51" s="6" t="s">
+      <c r="E53" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="54" customHeight="1" spans="1:5">
+      <c r="A54" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C54" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="E51" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="52" customHeight="1" spans="1:5">
-      <c r="A52" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B52" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="C52" s="6" t="s">
+      <c r="E54" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="55" customHeight="1" spans="1:5">
+      <c r="A55" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C55" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="E52" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="53" customHeight="1" spans="1:5">
-      <c r="A53" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B53" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="C53" s="6" t="s">
+      <c r="E55" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="56" customHeight="1" spans="1:5">
+      <c r="A56" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C56" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="E53" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="54" customHeight="1" spans="1:5">
-      <c r="A54" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B54" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="C54" s="6" t="s">
+      <c r="E56" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="57" customHeight="1" spans="1:5">
+      <c r="A57" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C57" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="E54" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="55" customHeight="1" spans="1:5">
-      <c r="A55" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B55" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="C55" s="6" t="s">
+      <c r="E57" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" customHeight="1" spans="1:5">
+      <c r="A58" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C58" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="E55" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="56" customHeight="1" spans="1:5">
-      <c r="A56" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B56" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="C56" s="6" t="s">
+      <c r="E58" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="59" customHeight="1" spans="1:5">
+      <c r="A59" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C59" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="E56" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="57" customHeight="1" spans="1:5">
-      <c r="A57" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B57" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="C57" s="6" t="s">
+      <c r="E59" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60" customHeight="1" spans="1:5">
+      <c r="A60" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C60" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="E57" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="58" customHeight="1" spans="1:5">
-      <c r="A58" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B58" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="C58" s="6" t="s">
+      <c r="E60" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="61" customHeight="1" spans="1:5">
+      <c r="A61" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C61" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="E58" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="59" customHeight="1" spans="1:5">
-      <c r="A59" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B59" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="C59" s="6" t="s">
+      <c r="E61" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="62" customHeight="1" spans="1:5">
+      <c r="A62" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C62" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="E59" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="60" customHeight="1" spans="1:5">
-      <c r="A60" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B60" s="2" t="s">
+      <c r="E62" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" customHeight="1" spans="1:5">
+      <c r="A63" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B63" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="C60" s="6" t="s">
+      <c r="C63" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="E60" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="61" customHeight="1" spans="1:5">
-      <c r="A61" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B61" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="C61" s="6" t="s">
+      <c r="E63" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="64" customHeight="1" spans="1:5">
+      <c r="A64" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B64" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="E61" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="62" customHeight="1" spans="1:5">
-      <c r="A62" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B62" s="2" t="s">
+      <c r="C64" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="C62" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="E62" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="63" customHeight="1" spans="1:5">
-      <c r="A63" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B63" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="C63" s="6" t="s">
+      <c r="E64" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="65" customHeight="1" spans="1:5">
+      <c r="A65" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B65" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="E63" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="64" customHeight="1" spans="1:5">
-      <c r="A64" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B64" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="C64" s="6" t="s">
+      <c r="C65" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="E64" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="65" customHeight="1" spans="1:5">
-      <c r="A65" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B65" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="C65" s="6" t="s">
+      <c r="E65" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="66" customHeight="1" spans="1:5">
+      <c r="A66" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="C66" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="E65" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="66" customHeight="1" spans="1:5">
-      <c r="A66" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B66" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="C66" s="6" t="s">
+      <c r="E66" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="67" customHeight="1" spans="1:5">
+      <c r="A67" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="C67" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="E66" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="67" customHeight="1" spans="1:5">
-      <c r="A67" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B67" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="C67" s="6" t="s">
+      <c r="E67" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="68" customHeight="1" spans="1:5">
+      <c r="A68" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="C68" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="E67" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="68" customHeight="1" spans="1:5">
-      <c r="A68" s="2" t="s">
+      <c r="E68" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="69" customHeight="1" spans="1:5">
+      <c r="A69" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B69" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="C69" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="B68" s="2" t="s">
+      <c r="E69" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="70" customHeight="1" spans="1:5">
+      <c r="A70" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B70" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="C70" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="C68" s="6" t="s">
+      <c r="E70" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="71" customHeight="1" spans="1:5">
+      <c r="A71" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B71" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="C71" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="E68" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="69" s="1" customFormat="1" customHeight="1" spans="1:5">
-      <c r="A69" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="B69" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="C69" s="6" t="s">
+      <c r="E71" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="72" customHeight="1" spans="1:5">
+      <c r="A72" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="C72" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="D69" s="2"/>
-      <c r="E69" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="70" s="1" customFormat="1" customHeight="1" spans="1:5">
-      <c r="A70" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="B70" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="C70" s="6" t="s">
+      <c r="E72" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73" customHeight="1" spans="1:5">
+      <c r="A73" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B73" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="C73" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="D70" s="2"/>
-      <c r="E70" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="71" s="1" customFormat="1" customHeight="1" spans="1:5">
-      <c r="A71" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="B71" s="2" t="s">
+      <c r="E73" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="74" customHeight="1" spans="1:5">
+      <c r="A74" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="C74" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="C71" s="6" t="s">
+      <c r="E74" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="75" customHeight="1" spans="1:5">
+      <c r="A75" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B75" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="D71" s="2"/>
-      <c r="E71" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="72" customHeight="1" spans="1:5">
-      <c r="A72" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B72" s="1" t="s">
+      <c r="C75" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="C72" s="8" t="s">
+      <c r="E75" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="76" s="1" customFormat="1" customHeight="1" spans="1:5">
+      <c r="A76" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="B76" s="9" t="s">
         <v>102</v>
       </c>
-      <c r="D72" s="1"/>
-      <c r="E72" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="73" customHeight="1" spans="1:5">
-      <c r="A73" s="5" t="s">
+      <c r="C76" s="10" t="s">
         <v>103</v>
       </c>
-      <c r="B73" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="C73" s="9" t="s">
-        <v>103</v>
-      </c>
-      <c r="D73" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="E73" s="5" t="s">
+      <c r="E76" s="11" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="77" s="1" customFormat="1" customHeight="1" spans="1:5">
+      <c r="A77" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="B77" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="C77" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="E77" s="11" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="78" s="1" customFormat="1" customHeight="1" spans="1:5">
+      <c r="A78" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="B78" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="C78" s="10" t="s">
+        <v>105</v>
+      </c>
+      <c r="E78" s="11" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="79" customHeight="1" spans="1:5">
+      <c r="A79" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B79" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="C79" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="E79" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="80" customHeight="1" spans="1:5">
+      <c r="A80" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B80" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="C80" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="E80" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="81" customHeight="1" spans="1:5">
+      <c r="A81" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B81" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="C81" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="E81" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" customHeight="1" spans="1:5">
+      <c r="A82" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B82" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="C82" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="E82" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="83" customHeight="1" spans="1:5">
+      <c r="A83" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B83" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="C83" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="E83" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="84" customHeight="1" spans="1:5">
+      <c r="A84" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B84" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="C84" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="E84" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="85" customHeight="1" spans="1:5">
+      <c r="A85" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B85" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="C85" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="E85" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="86" customHeight="1" spans="1:5">
+      <c r="A86" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="B86" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="C86" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="E86" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="87" s="2" customFormat="1" customHeight="1" spans="1:5">
+      <c r="A87" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="B87" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="C87" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="D87" s="3"/>
+      <c r="E87" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="88" s="2" customFormat="1" customHeight="1" spans="1:5">
+      <c r="A88" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="B88" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="C88" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="D88" s="3"/>
+      <c r="E88" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="89" s="2" customFormat="1" customHeight="1" spans="1:5">
+      <c r="A89" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="B89" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="C89" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="D89" s="3"/>
+      <c r="E89" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="90" customHeight="1" spans="1:5">
+      <c r="A90" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B90" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="C90" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="D90" s="2"/>
+      <c r="E90" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="91" customHeight="1" spans="1:5">
+      <c r="A91" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="B91" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="C91" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="D91" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="E91" s="6" t="s">
         <v>4</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D73">
-    <sortState ref="A1:D73">
+  <autoFilter ref="A1:D91">
+    <sortState ref="A1:D91">
       <sortCondition ref="A1:A91" descending="1"/>
     </sortState>
     <extLst/>

--- a/408/OS/2024/ModularAutomation/reports/testcases.xlsx
+++ b/408/OS/2024/ModularAutomation/reports/testcases.xlsx
@@ -10,7 +10,7 @@
     <sheet name="#TEMP" sheetId="4" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'#TEMP'!$A$1:$D$91</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'#TEMP'!$A$1:$D$108</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="367" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="435" uniqueCount="137">
   <si>
     <t>接口</t>
   </si>
@@ -79,6 +79,267 @@
   </si>
   <si>
     <t>#results↓</t>
+  </si>
+  <si>
+    <t>/cgi-bin/luci/api/cmd</t>
+  </si>
+  <si>
+    <t>devSta.set</t>
+  </si>
+  <si>
+    <t>{
+    "module": "deleteDevice",
+    "noParse": true,
+    "async": null,
+    "remoteIp": false,
+    "data": {
+        "snList": [
+            "aaaaaa"
+        ]
+    },
+    "device": "pc"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "module": "deviceMove",
+    "noParse": true,
+    "async": null,
+    "remoteIp": false,
+    "data": {
+        "networkId": "aaa",
+        "parentGroupId": "bbb"
+    },
+    "device": "pc"
+}</t>
+  </si>
+  <si>
+    <t>devConfig.add</t>
+  </si>
+  <si>
+    <t>{
+    "module": "flowctrl_macc",
+    "noParse": false,
+    "remoteIp": false,
+    "device": "pc",
+    "async": null,
+    "data": {
+        "list": [
+            {
+                "type": "macc",
+                "comment": "555_ACCOUNT",
+                "enable": "on",
+                "effective": "1",
+                "downRate": 2048,
+                "user_group_list": [
+                    "\/auth_root\/222_ACCOUNT"
+                ],
+                "intf": "br-allwan",
+                "ipRange": "",
+                "mode": "per_ip",
+                "downRateG": "1",
+                "upRate": 1024,
+                "ip_group": "fc_rule_x",
+                "upRateG": "1"
+            }
+        ]
+    }
+}</t>
+  </si>
+  <si>
+    <t>devConfig.set</t>
+  </si>
+  <si>
+    <t>{
+    "module": "igmp_snooping",
+    "noParse": true,
+    "async": null,
+    "remoteIp": false,
+    "data": {
+        "status": "on"
+    },
+    "device": "pc"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "module": "macc_stalog",
+    "noParse": true,
+    "async": null,
+    "remoteIp": false,
+    "data": {
+        "termid_enable": "3",
+        "ipchange_enable": "0",
+        "termid_udp": "60",
+        "server": "http:\/\/cloud.ruijie.com.cn\/macclog\/api\/upload\/jsondata\/sta_info"
+    },
+    "device": "pc"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "module": "rg_syslog",
+    "noParse": true,
+    "async": null,
+    "remoteIp": false,
+    "data": {
+        "enable": "1",
+        "keyword": "",
+        "udp": "300",
+        "url": "http:\/\/cloud.ruijie.com.cn\/macclog\/api\/upload\/stream\/syslog_info",
+        "pkgnum": "20",
+        "debug_level": ""
+    },
+    "device": "pc"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "module": "policy_route",
+    "noParse": true,
+    "async": null,
+    "remoteIp": false,
+    "data": {
+        "list": [
+            {
+                "proto": "",
+                "udef_proto": "",
+                "sport": "",
+                "dport": "",
+                "sip": "",
+                "sipRange": "",
+                "dip": "",
+                "dipRange": "",
+                "intf": ""
+            }
+        ]
+    },
+    "device": "pc"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "module": "phtunnel",
+    "noParse": true,
+    "async": null,
+    "remoteIp": false,
+    "data": {
+        "enable": "1",
+        "unbind": "1"
+    },
+    "device": "pc"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "module": "phddns",
+    "noParse": true,
+    "async": null,
+    "remoteIp": false,
+    "data": {
+        "user": "xxx",
+        "pass": "xxx",
+        "wan": "xxx"
+    },
+    "device": "pc"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "module": "openvpn_server",
+    "noParse": true,
+    "async": null,
+    "remoteIp": false,
+    "data": {
+        "enable": "",
+        "role": "",
+        "service_mode": "",
+        "hostname": "",
+        "port": "",
+        "iprange": "",
+        "proto": ""
+    },
+    "device": "pc"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "module": "openvpn_client",
+    "noParse": true,
+    "async": null,
+    "remoteIp": false,
+    "data": {
+        "role": "",
+        "enable": "",
+        "cfg_ways": "",
+        "server_mode": "",
+        "user": "",
+        "passwd": ""
+    },
+    "device": "pc"
+}</t>
+  </si>
+  <si>
+    <t>acConfig.set</t>
+  </si>
+  <si>
+    <t>{
+    "module": "network_group",
+    "noParse": false,
+    "async": null,
+    "remoteIp": false,
+    "data": {
+        "networkId": "app_MACCEG3478G34_1523614186",
+        "groupInfo": [
+            {
+                "isDefault": "true",
+                "deviceList": [
+                    {
+                        "devSN": "MACCEG3478G34"
+                    }
+                ],
+                "groupName": "default",
+                "groupId": "0"
+            }
+        ],
+        "version": "1.0.0",
+        "parentGroupId": "",
+        "networkName": "Wrididxixkdebke"
+    },
+    "device": "pc"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "module": "networkId_merge",
+    "noParse": true,
+    "async": null,
+    "remoteIp": false,
+    "data": {
+        "fromNetworkid": "aaa",
+        "toNetworkid": "bbb",
+        "fromSn": [],
+        "password": "admin",
+        "typee": "noenc",
+        "esw_fromSn": []
+    },
+    "device": "pc"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "module": "networkId",
+    "noParse": true,
+    "async": null,
+    "remoteIp": false,
+    "data": {
+        "networdid": "xx",
+        "networkName": "xxxxx",
+        "groupId": "xxx",
+        "groupName": "xxxxxxx"
+    },
+    "device": "pc"
+}</t>
   </si>
   <si>
     <t>/cgi-bin/luci/api/network</t>
@@ -201,12 +462,6 @@
     <t>{
     "search": "'flagthn"
 }</t>
-  </si>
-  <si>
-    <t>/cgi-bin/luci/api/cmd</t>
-  </si>
-  <si>
-    <t>devSta.set</t>
   </si>
   <si>
     <t>{
@@ -790,9 +1045,6 @@
     },
     "device": "pc"
 }</t>
-  </si>
-  <si>
-    <t>devConfig.set</t>
   </si>
   <si>
     <t>{
@@ -1318,9 +1570,6 @@
 }</t>
   </si>
   <si>
-    <t>devConfig.add</t>
-  </si>
-  <si>
     <t>{
     "module": "interface",
     "noParse": false,
@@ -1608,7 +1857,17 @@
 }</t>
   </si>
   <si>
-    <t>acConfig.set</t>
+    <t>{
+    "module": "eweb_password",
+    "noParse": false,
+    "async": null,
+    "remoteIp": false,
+    "data": {
+        "type": "enc",
+        "password": "U2FsdGVkX18Iz6tcnffsxwxOtyka6ez/yvbTJZLxz94="
+    },
+    "device": "pc"
+}</t>
   </si>
   <si>
     <t>{
@@ -2648,7 +2907,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2671,16 +2930,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -3043,7 +3296,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E91"/>
+  <dimension ref="A1:E108"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="39.95" customHeight="1" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="29.3796296296296" style="3" customWidth="1"/>
@@ -3104,13 +3357,13 @@
     </row>
     <row r="4" customHeight="1" spans="1:5">
       <c r="A4" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="7" t="s">
         <v>12</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>14</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>4</v>
@@ -3118,13 +3371,13 @@
     </row>
     <row r="5" customHeight="1" spans="1:5">
       <c r="A5" s="3" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E5" s="6" t="s">
         <v>4</v>
@@ -3132,13 +3385,13 @@
     </row>
     <row r="6" customHeight="1" spans="1:5">
       <c r="A6" s="3" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>4</v>
@@ -3146,13 +3399,13 @@
     </row>
     <row r="7" customHeight="1" spans="1:5">
       <c r="A7" s="3" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E7" s="6" t="s">
         <v>4</v>
@@ -3160,13 +3413,13 @@
     </row>
     <row r="8" customHeight="1" spans="1:5">
       <c r="A8" s="3" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>4</v>
@@ -3174,13 +3427,13 @@
     </row>
     <row r="9" customHeight="1" spans="1:5">
       <c r="A9" s="3" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="E9" s="6" t="s">
         <v>4</v>
@@ -3188,13 +3441,13 @@
     </row>
     <row r="10" customHeight="1" spans="1:5">
       <c r="A10" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="B10" s="8" t="s">
-        <v>26</v>
+        <v>9</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>15</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>4</v>
@@ -3202,13 +3455,13 @@
     </row>
     <row r="11" customHeight="1" spans="1:5">
       <c r="A11" s="3" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E11" s="6" t="s">
         <v>4</v>
@@ -3216,13 +3469,13 @@
     </row>
     <row r="12" customHeight="1" spans="1:5">
       <c r="A12" s="3" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>4</v>
@@ -3230,13 +3483,13 @@
     </row>
     <row r="13" customHeight="1" spans="1:5">
       <c r="A13" s="3" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="E13" s="6" t="s">
         <v>4</v>
@@ -3244,13 +3497,13 @@
     </row>
     <row r="14" customHeight="1" spans="1:5">
       <c r="A14" s="3" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>4</v>
@@ -3258,27 +3511,27 @@
     </row>
     <row r="15" customHeight="1" spans="1:5">
       <c r="A15" s="3" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="E15" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="16" customHeight="1" spans="1:5">
-      <c r="A16" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C16" s="7" t="s">
-        <v>35</v>
+      <c r="A16" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>25</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>4</v>
@@ -3286,13 +3539,13 @@
     </row>
     <row r="17" customHeight="1" spans="1:5">
       <c r="A17" s="3" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="E17" s="6" t="s">
         <v>4</v>
@@ -3300,13 +3553,13 @@
     </row>
     <row r="18" customHeight="1" spans="1:5">
       <c r="A18" s="3" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>4</v>
@@ -3320,7 +3573,7 @@
         <v>29</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="E19" s="6" t="s">
         <v>4</v>
@@ -3328,13 +3581,13 @@
     </row>
     <row r="20" customHeight="1" spans="1:5">
       <c r="A20" s="3" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>4</v>
@@ -3342,13 +3595,13 @@
     </row>
     <row r="21" customHeight="1" spans="1:5">
       <c r="A21" s="3" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E21" s="6" t="s">
         <v>4</v>
@@ -3356,13 +3609,13 @@
     </row>
     <row r="22" customHeight="1" spans="1:5">
       <c r="A22" s="3" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>4</v>
@@ -3370,13 +3623,13 @@
     </row>
     <row r="23" customHeight="1" spans="1:5">
       <c r="A23" s="3" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="E23" s="6" t="s">
         <v>4</v>
@@ -3384,13 +3637,13 @@
     </row>
     <row r="24" customHeight="1" spans="1:5">
       <c r="A24" s="3" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>4</v>
@@ -3398,10 +3651,10 @@
     </row>
     <row r="25" customHeight="1" spans="1:5">
       <c r="A25" s="3" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="C25" s="7" t="s">
         <v>44</v>
@@ -3412,13 +3665,13 @@
     </row>
     <row r="26" customHeight="1" spans="1:5">
       <c r="A26" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>29</v>
+        <v>40</v>
+      </c>
+      <c r="B26" s="9" t="s">
+        <v>45</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>4</v>
@@ -3426,13 +3679,13 @@
     </row>
     <row r="27" customHeight="1" spans="1:5">
       <c r="A27" s="3" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E27" s="6" t="s">
         <v>4</v>
@@ -3440,13 +3693,13 @@
     </row>
     <row r="28" customHeight="1" spans="1:5">
       <c r="A28" s="3" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>4</v>
@@ -3454,52 +3707,52 @@
     </row>
     <row r="29" customHeight="1" spans="1:5">
       <c r="A29" s="3" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E29" s="6" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="30" s="1" customFormat="1" customHeight="1" spans="1:5">
-      <c r="A30" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="B30" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="C30" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="E30" s="11" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="31" s="1" customFormat="1" customHeight="1" spans="1:5">
-      <c r="A31" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="B31" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="C31" s="10" t="s">
+    <row r="30" customHeight="1" spans="1:5">
+      <c r="A30" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C30" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="E31" s="11" t="s">
+      <c r="E30" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="31" customHeight="1" spans="1:5">
+      <c r="A31" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C31" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="E31" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="32" customHeight="1" spans="1:5">
       <c r="A32" s="3" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>51</v>
+        <v>10</v>
       </c>
       <c r="C32" s="7" t="s">
         <v>52</v>
@@ -3510,10 +3763,10 @@
     </row>
     <row r="33" customHeight="1" spans="1:5">
       <c r="A33" s="3" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>51</v>
+        <v>10</v>
       </c>
       <c r="C33" s="7" t="s">
         <v>53</v>
@@ -3524,10 +3777,10 @@
     </row>
     <row r="34" customHeight="1" spans="1:5">
       <c r="A34" s="3" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>51</v>
+        <v>10</v>
       </c>
       <c r="C34" s="7" t="s">
         <v>54</v>
@@ -3538,10 +3791,10 @@
     </row>
     <row r="35" customHeight="1" spans="1:5">
       <c r="A35" s="3" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>51</v>
+        <v>10</v>
       </c>
       <c r="C35" s="7" t="s">
         <v>55</v>
@@ -3552,10 +3805,10 @@
     </row>
     <row r="36" customHeight="1" spans="1:5">
       <c r="A36" s="3" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>51</v>
+        <v>10</v>
       </c>
       <c r="C36" s="7" t="s">
         <v>56</v>
@@ -3566,13 +3819,13 @@
     </row>
     <row r="37" customHeight="1" spans="1:5">
       <c r="A37" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="B37" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="7" t="s">
         <v>57</v>
-      </c>
-      <c r="C37" s="7" t="s">
-        <v>37</v>
       </c>
       <c r="E37" s="6" t="s">
         <v>4</v>
@@ -3580,13 +3833,13 @@
     </row>
     <row r="38" customHeight="1" spans="1:5">
       <c r="A38" s="3" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="B38" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38" s="7" t="s">
         <v>58</v>
-      </c>
-      <c r="C38" s="7" t="s">
-        <v>59</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>4</v>
@@ -3594,13 +3847,13 @@
     </row>
     <row r="39" customHeight="1" spans="1:5">
       <c r="A39" s="3" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>58</v>
+        <v>10</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E39" s="6" t="s">
         <v>4</v>
@@ -3608,13 +3861,13 @@
     </row>
     <row r="40" customHeight="1" spans="1:5">
       <c r="A40" s="3" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>58</v>
+        <v>10</v>
       </c>
       <c r="C40" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>4</v>
@@ -3622,13 +3875,13 @@
     </row>
     <row r="41" customHeight="1" spans="1:5">
       <c r="A41" s="3" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>62</v>
+        <v>10</v>
       </c>
       <c r="C41" s="7" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E41" s="6" t="s">
         <v>4</v>
@@ -3636,13 +3889,13 @@
     </row>
     <row r="42" customHeight="1" spans="1:5">
       <c r="A42" s="3" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="B42" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C42" s="7" t="s">
         <v>62</v>
-      </c>
-      <c r="C42" s="7" t="s">
-        <v>64</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>4</v>
@@ -3650,13 +3903,13 @@
     </row>
     <row r="43" customHeight="1" spans="1:5">
       <c r="A43" s="3" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>62</v>
+        <v>10</v>
       </c>
       <c r="C43" s="7" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E43" s="6" t="s">
         <v>4</v>
@@ -3664,13 +3917,13 @@
     </row>
     <row r="44" customHeight="1" spans="1:5">
       <c r="A44" s="3" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>62</v>
+        <v>10</v>
       </c>
       <c r="C44" s="7" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>4</v>
@@ -3678,41 +3931,41 @@
     </row>
     <row r="45" customHeight="1" spans="1:5">
       <c r="A45" s="3" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>62</v>
+        <v>10</v>
       </c>
       <c r="C45" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="E45" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" s="1" customFormat="1" customHeight="1" spans="1:5">
+      <c r="A46" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C46" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="E46" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="47" s="1" customFormat="1" customHeight="1" spans="1:5">
+      <c r="A47" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C47" s="8" t="s">
         <v>67</v>
-      </c>
-      <c r="E45" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="46" customHeight="1" spans="1:5">
-      <c r="A46" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="C46" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="E46" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="47" customHeight="1" spans="1:5">
-      <c r="A47" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="C47" s="7" t="s">
-        <v>69</v>
       </c>
       <c r="E47" s="6" t="s">
         <v>4</v>
@@ -3720,13 +3973,13 @@
     </row>
     <row r="48" customHeight="1" spans="1:5">
       <c r="A48" s="3" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="C48" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>4</v>
@@ -3734,13 +3987,13 @@
     </row>
     <row r="49" customHeight="1" spans="1:5">
       <c r="A49" s="3" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="C49" s="7" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E49" s="6" t="s">
         <v>4</v>
@@ -3748,13 +4001,13 @@
     </row>
     <row r="50" customHeight="1" spans="1:5">
       <c r="A50" s="3" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="C50" s="7" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>4</v>
@@ -3762,13 +4015,13 @@
     </row>
     <row r="51" customHeight="1" spans="1:5">
       <c r="A51" s="3" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="C51" s="7" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E51" s="6" t="s">
         <v>4</v>
@@ -3776,13 +4029,13 @@
     </row>
     <row r="52" customHeight="1" spans="1:5">
       <c r="A52" s="3" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="C52" s="7" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>4</v>
@@ -3790,13 +4043,13 @@
     </row>
     <row r="53" customHeight="1" spans="1:5">
       <c r="A53" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>62</v>
+        <v>9</v>
+      </c>
+      <c r="B53" s="9" t="s">
+        <v>74</v>
       </c>
       <c r="C53" s="7" t="s">
-        <v>75</v>
+        <v>54</v>
       </c>
       <c r="E53" s="6" t="s">
         <v>4</v>
@@ -3804,10 +4057,10 @@
     </row>
     <row r="54" customHeight="1" spans="1:5">
       <c r="A54" s="3" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="C54" s="7" t="s">
         <v>76</v>
@@ -3818,10 +4071,10 @@
     </row>
     <row r="55" customHeight="1" spans="1:5">
       <c r="A55" s="3" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="C55" s="7" t="s">
         <v>77</v>
@@ -3832,10 +4085,10 @@
     </row>
     <row r="56" customHeight="1" spans="1:5">
       <c r="A56" s="3" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="C56" s="7" t="s">
         <v>78</v>
@@ -3846,10 +4099,10 @@
     </row>
     <row r="57" customHeight="1" spans="1:5">
       <c r="A57" s="3" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>62</v>
+        <v>15</v>
       </c>
       <c r="C57" s="7" t="s">
         <v>79</v>
@@ -3860,10 +4113,10 @@
     </row>
     <row r="58" customHeight="1" spans="1:5">
       <c r="A58" s="3" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>62</v>
+        <v>15</v>
       </c>
       <c r="C58" s="7" t="s">
         <v>80</v>
@@ -3874,10 +4127,10 @@
     </row>
     <row r="59" customHeight="1" spans="1:5">
       <c r="A59" s="3" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>62</v>
+        <v>15</v>
       </c>
       <c r="C59" s="7" t="s">
         <v>81</v>
@@ -3888,10 +4141,10 @@
     </row>
     <row r="60" customHeight="1" spans="1:5">
       <c r="A60" s="3" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>62</v>
+        <v>15</v>
       </c>
       <c r="C60" s="7" t="s">
         <v>82</v>
@@ -3902,10 +4155,10 @@
     </row>
     <row r="61" customHeight="1" spans="1:5">
       <c r="A61" s="3" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>62</v>
+        <v>15</v>
       </c>
       <c r="C61" s="7" t="s">
         <v>83</v>
@@ -3916,10 +4169,10 @@
     </row>
     <row r="62" customHeight="1" spans="1:5">
       <c r="A62" s="3" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>62</v>
+        <v>15</v>
       </c>
       <c r="C62" s="7" t="s">
         <v>84</v>
@@ -3930,13 +4183,13 @@
     </row>
     <row r="63" customHeight="1" spans="1:5">
       <c r="A63" s="3" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="B63" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C63" s="7" t="s">
         <v>85</v>
-      </c>
-      <c r="C63" s="7" t="s">
-        <v>86</v>
       </c>
       <c r="E63" s="6" t="s">
         <v>4</v>
@@ -3944,13 +4197,13 @@
     </row>
     <row r="64" customHeight="1" spans="1:5">
       <c r="A64" s="3" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>87</v>
+        <v>15</v>
       </c>
       <c r="C64" s="7" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>4</v>
@@ -3958,13 +4211,13 @@
     </row>
     <row r="65" customHeight="1" spans="1:5">
       <c r="A65" s="3" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>89</v>
+        <v>15</v>
       </c>
       <c r="C65" s="7" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="E65" s="6" t="s">
         <v>4</v>
@@ -3972,13 +4225,13 @@
     </row>
     <row r="66" customHeight="1" spans="1:5">
       <c r="A66" s="3" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>89</v>
+        <v>15</v>
       </c>
       <c r="C66" s="7" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>4</v>
@@ -3986,13 +4239,13 @@
     </row>
     <row r="67" customHeight="1" spans="1:5">
       <c r="A67" s="3" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="B67" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C67" s="7" t="s">
         <v>89</v>
-      </c>
-      <c r="C67" s="7" t="s">
-        <v>92</v>
       </c>
       <c r="E67" s="6" t="s">
         <v>4</v>
@@ -4000,13 +4253,13 @@
     </row>
     <row r="68" customHeight="1" spans="1:5">
       <c r="A68" s="3" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>89</v>
+        <v>15</v>
       </c>
       <c r="C68" s="7" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>4</v>
@@ -4014,13 +4267,13 @@
     </row>
     <row r="69" customHeight="1" spans="1:5">
       <c r="A69" s="3" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>89</v>
+        <v>15</v>
       </c>
       <c r="C69" s="7" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="E69" s="6" t="s">
         <v>4</v>
@@ -4028,13 +4281,13 @@
     </row>
     <row r="70" customHeight="1" spans="1:5">
       <c r="A70" s="3" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>89</v>
+        <v>15</v>
       </c>
       <c r="C70" s="7" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>4</v>
@@ -4042,13 +4295,13 @@
     </row>
     <row r="71" customHeight="1" spans="1:5">
       <c r="A71" s="3" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>89</v>
+        <v>15</v>
       </c>
       <c r="C71" s="7" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="E71" s="6" t="s">
         <v>4</v>
@@ -4056,13 +4309,13 @@
     </row>
     <row r="72" customHeight="1" spans="1:5">
       <c r="A72" s="3" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>89</v>
+        <v>15</v>
       </c>
       <c r="C72" s="7" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>4</v>
@@ -4070,13 +4323,13 @@
     </row>
     <row r="73" customHeight="1" spans="1:5">
       <c r="A73" s="3" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>89</v>
+        <v>15</v>
       </c>
       <c r="C73" s="7" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="E73" s="6" t="s">
         <v>4</v>
@@ -4084,13 +4337,13 @@
     </row>
     <row r="74" customHeight="1" spans="1:5">
       <c r="A74" s="3" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>89</v>
+        <v>15</v>
       </c>
       <c r="C74" s="7" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>4</v>
@@ -4098,69 +4351,69 @@
     </row>
     <row r="75" customHeight="1" spans="1:5">
       <c r="A75" s="3" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="B75" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C75" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="E75" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="76" customHeight="1" spans="1:5">
+      <c r="A76" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B76" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C76" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="E76" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="77" customHeight="1" spans="1:5">
+      <c r="A77" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B77" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C77" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="E77" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="78" customHeight="1" spans="1:5">
+      <c r="A78" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B78" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C78" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="C75" s="7" t="s">
-        <v>101</v>
-      </c>
-      <c r="E75" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="76" s="1" customFormat="1" customHeight="1" spans="1:5">
-      <c r="A76" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="B76" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="C76" s="10" t="s">
-        <v>103</v>
-      </c>
-      <c r="E76" s="11" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="77" s="1" customFormat="1" customHeight="1" spans="1:5">
-      <c r="A77" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="B77" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="C77" s="10" t="s">
-        <v>104</v>
-      </c>
-      <c r="E77" s="11" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="78" s="1" customFormat="1" customHeight="1" spans="1:5">
-      <c r="A78" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="B78" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="C78" s="10" t="s">
-        <v>105</v>
-      </c>
-      <c r="E78" s="11" t="s">
+      <c r="E78" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="79" customHeight="1" spans="1:5">
       <c r="A79" s="3" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="B79" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="C79" s="7" t="s">
         <v>102</v>
-      </c>
-      <c r="C79" s="7" t="s">
-        <v>106</v>
       </c>
       <c r="E79" s="6" t="s">
         <v>4</v>
@@ -4168,13 +4421,13 @@
     </row>
     <row r="80" customHeight="1" spans="1:5">
       <c r="A80" s="3" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C80" s="7" t="s">
-        <v>71</v>
+        <v>104</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>4</v>
@@ -4182,13 +4435,13 @@
     </row>
     <row r="81" customHeight="1" spans="1:5">
       <c r="A81" s="3" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>102</v>
+        <v>13</v>
       </c>
       <c r="C81" s="7" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="E81" s="6" t="s">
         <v>4</v>
@@ -4196,13 +4449,13 @@
     </row>
     <row r="82" customHeight="1" spans="1:5">
       <c r="A82" s="3" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>102</v>
+        <v>13</v>
       </c>
       <c r="C82" s="7" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>4</v>
@@ -4210,13 +4463,13 @@
     </row>
     <row r="83" customHeight="1" spans="1:5">
       <c r="A83" s="3" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>102</v>
+        <v>13</v>
       </c>
       <c r="C83" s="7" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E83" s="6" t="s">
         <v>4</v>
@@ -4224,13 +4477,13 @@
     </row>
     <row r="84" customHeight="1" spans="1:5">
       <c r="A84" s="3" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>102</v>
+        <v>13</v>
       </c>
       <c r="C84" s="7" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>4</v>
@@ -4238,13 +4491,13 @@
     </row>
     <row r="85" customHeight="1" spans="1:5">
       <c r="A85" s="3" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>102</v>
+        <v>13</v>
       </c>
       <c r="C85" s="7" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E85" s="6" t="s">
         <v>4</v>
@@ -4252,98 +4505,336 @@
     </row>
     <row r="86" customHeight="1" spans="1:5">
       <c r="A86" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B86" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C86" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="E86" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="87" customHeight="1" spans="1:5">
+      <c r="A87" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B87" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C87" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="E87" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="88" customHeight="1" spans="1:5">
+      <c r="A88" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B88" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C88" s="7" t="s">
         <v>112</v>
       </c>
-      <c r="B86" s="3" t="s">
+      <c r="E88" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="89" customHeight="1" spans="1:5">
+      <c r="A89" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B89" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C89" s="7" t="s">
         <v>113</v>
       </c>
-      <c r="C86" s="7" t="s">
+      <c r="E89" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="90" customHeight="1" spans="1:5">
+      <c r="A90" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B90" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C90" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="E86" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="87" s="2" customFormat="1" customHeight="1" spans="1:5">
-      <c r="A87" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="B87" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="C87" s="7" t="s">
+      <c r="E90" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="91" customHeight="1" spans="1:5">
+      <c r="A91" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B91" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="D87" s="3"/>
-      <c r="E87" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="88" s="2" customFormat="1" customHeight="1" spans="1:5">
-      <c r="A88" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="B88" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="C88" s="7" t="s">
+      <c r="C91" s="7" t="s">
         <v>116</v>
       </c>
-      <c r="D88" s="3"/>
-      <c r="E88" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="89" s="2" customFormat="1" customHeight="1" spans="1:5">
-      <c r="A89" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="B89" s="3" t="s">
+      <c r="E91" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="92" s="1" customFormat="1" customHeight="1" spans="1:5">
+      <c r="A92" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C92" s="8" t="s">
         <v>117</v>
       </c>
-      <c r="C89" s="7" t="s">
+      <c r="E92" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="93" s="1" customFormat="1" customHeight="1" spans="1:5">
+      <c r="A93" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C93" s="8" t="s">
         <v>118</v>
       </c>
-      <c r="D89" s="3"/>
-      <c r="E89" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="90" customHeight="1" spans="1:5">
-      <c r="A90" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B90" s="2" t="s">
+      <c r="E93" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="94" s="1" customFormat="1" customHeight="1" spans="1:5">
+      <c r="A94" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C94" s="8" t="s">
         <v>119</v>
       </c>
-      <c r="C90" s="12" t="s">
+      <c r="E94" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="95" s="1" customFormat="1" customHeight="1" spans="1:5">
+      <c r="A95" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C95" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="D90" s="2"/>
-      <c r="E90" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="91" customHeight="1" spans="1:5">
-      <c r="A91" s="6" t="s">
+      <c r="E95" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="96" customHeight="1" spans="1:5">
+      <c r="A96" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B96" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C96" s="7" t="s">
         <v>121</v>
       </c>
-      <c r="B91" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="C91" s="13" t="s">
-        <v>121</v>
-      </c>
-      <c r="D91" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="E91" s="6" t="s">
+      <c r="E96" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="97" customHeight="1" spans="1:5">
+      <c r="A97" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B97" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C97" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="E97" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="98" customHeight="1" spans="1:5">
+      <c r="A98" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B98" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C98" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="E98" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="99" customHeight="1" spans="1:5">
+      <c r="A99" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B99" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C99" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="E99" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="100" customHeight="1" spans="1:5">
+      <c r="A100" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B100" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C100" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="E100" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="101" customHeight="1" spans="1:5">
+      <c r="A101" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B101" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C101" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="E101" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="102" customHeight="1" spans="1:5">
+      <c r="A102" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B102" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C102" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="E102" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="103" customHeight="1" spans="1:5">
+      <c r="A103" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="B103" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="C103" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="E103" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="104" s="2" customFormat="1" customHeight="1" spans="1:5">
+      <c r="A104" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="B104" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="C104" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="D104" s="3"/>
+      <c r="E104" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="105" s="2" customFormat="1" customHeight="1" spans="1:5">
+      <c r="A105" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="B105" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="C105" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="D105" s="3"/>
+      <c r="E105" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="106" s="2" customFormat="1" customHeight="1" spans="1:5">
+      <c r="A106" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="B106" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="C106" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="D106" s="3"/>
+      <c r="E106" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="107" customHeight="1" spans="1:5">
+      <c r="A107" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B107" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="C107" s="10" t="s">
+        <v>135</v>
+      </c>
+      <c r="D107" s="2"/>
+      <c r="E107" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="108" customHeight="1" spans="1:5">
+      <c r="A108" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="B108" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="C108" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="D108" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="E108" s="6" t="s">
         <v>4</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D91">
-    <sortState ref="A1:D91">
+  <autoFilter ref="A1:D108">
+    <sortState ref="A1:D108">
       <sortCondition ref="A1:A91" descending="1"/>
     </sortState>
     <extLst/>

--- a/408/OS/2024/ModularAutomation/reports/testcases.xlsx
+++ b/408/OS/2024/ModularAutomation/reports/testcases.xlsx
@@ -460,7 +460,7 @@
   </si>
   <si>
     <t>{
-    "search": "'flagthn"
+    "search": "'"
 }</t>
   </si>
   <si>
@@ -743,7 +743,7 @@
         "selfsn": "s",
         "dispinfo": {
             "l1": [
-                "]}'flagthn'{["
+                "]}''{["
             ]
         }
     },
@@ -947,7 +947,7 @@
             }
         ],
         "bssid": [
-            "]}flagthn"
+            "]}"
         ],
         "wan6Num": "2",
         "listp": [
@@ -978,7 +978,7 @@
     "async": null,
     "remoteIp": false,
     "data": {
-        "url": "'flagthn'"
+        "url": "''"
     },
     "device": "pc"
 }</t>
@@ -1009,7 +1009,7 @@
     "remoteIp": false,
     "config_path": "/pyc",
     "data": {
-        "PseNotifyThreshold": "flagthn ",
+        "PseNotifyThreshold": " ",
         "PseNotifyControl": "1",
         "nt_info": [
             {
@@ -1030,7 +1030,7 @@
     "data": {
         "state": "1",
         "force_state": "1",
-        "monitor_port": "flagthn",
+        "monitor_port": "",
         "first_dns_server": "1.1.1.1",
         "second_dns_server": "1.1.1.1",
         "max_sessions": "15",
@@ -1078,7 +1078,7 @@
     "async": null,
     "remoteIp": false,
     "data": {
-        "tunnelname": "pptpflagthn",
+        "tunnelname": "pptp",
         "username": "",
         "password": "",
         "intf_binding": "WAN",
@@ -1210,7 +1210,7 @@
     "async": null,
     "remoteIp": false,
     "data": {
-        "sta": "'flagthn'"
+        "sta": "''"
     },
     "device": "pc"
 }</t>
@@ -1250,7 +1250,7 @@
     "async": null,
     "remoteIp": false,
     "data": {
-        "cmd": "dummy'flagthn'"
+        "cmd": "dummy''"
     },
     "device": "pc"
 }</t>
@@ -1308,7 +1308,7 @@
             "exchange_mode": "main",
             "remote_gateway1": "",
             "ikelifetime": "86400",
-            "name": "qqqq'flagthn'",
+            "name": "qqqq''",
             "pfs": "none",
             "mode": "tunnel",
             "create_by": "web",
@@ -1373,7 +1373,7 @@
     "async": null,
     "data": {
         "data": [
-            "1.1.1.1'flagthn'"
+            "1.1.1.1''"
         ],
         "type": "srcip"
     }
@@ -1451,7 +1451,7 @@
                 "netmask": "255.255.255.0",
                 "limit": "254",
                 "pool": "EGW",
-                "desc": "22ttttt'flagthn'"
+                "desc": "22ttttt''"
             }
         ],
         "version": "1.0.0",
@@ -1483,7 +1483,7 @@
     "device": "pc",
     "data": {
         "cmd": "a",
-        "event": "'flagthn'"
+        "event": "''"
     }
 }</t>
   </si>
@@ -1548,7 +1548,7 @@
     "cur": "1212",
     "device": "pc",
     "data": {
-        "'flagthn'": "sdf"
+        "''": "sdf"
     }
 }</t>
   </si>
@@ -1580,7 +1580,7 @@
         "name": "test",
         "data": {
             "proto": "static",
-            "interface": "wan flagthn ",
+            "interface": "wan  ",
             "ipaddr": "192.168.111.255",
             "netmask": "255.255.255.0",
             "bcast": "192.168.111.255"
@@ -1617,7 +1617,7 @@
         "macList": [
             {
                 "comment": "",
-                "mac": "f8:e4:3b:60:bb:f6'flagthn'"
+                "mac": "f8:e4:3b:60:bb:f6''"
             }
         ]
     }
@@ -1813,7 +1813,7 @@
                             "downloadBand": "1000",
                             "ifname": "br-wan",
                             "enable": "on",
-                            "uploadBand": "1000'flagthn'"
+                            "uploadBand": "1000''"
                         }
                     ],
                     "wanNum": "1",
@@ -2158,7 +2158,7 @@
     "remoteIp": false,
     "data": {
         "mode": "apmesh_scan",
-        "enable": "sflagthn",
+        "enable": "s",
         "lanNum": "2",
         "wanNum": "0",
         "wan6": [
@@ -2217,7 +2217,7 @@
   </si>
   <si>
     <t>{
-    "winmt": "'flagthn'"
+    "winmt": "''"
 }</t>
   </si>
   <si>

--- a/408/OS/2024/ModularAutomation/reports/testcases.xlsx
+++ b/408/OS/2024/ModularAutomation/reports/testcases.xlsx
@@ -485,7 +485,7 @@
         "enable": "1",
         "list": [
             {
-                "port": "2",
+                "port": "-1",
                 "tag": "U"
             }
         ],
@@ -4833,7 +4833,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D108">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:D108" etc:filterBottomFollowUsedRange="0">
     <sortState ref="A1:D108">
       <sortCondition ref="A1:A91" descending="1"/>
     </sortState>

--- a/408/OS/2024/ModularAutomation/reports/testcases.xlsx
+++ b/408/OS/2024/ModularAutomation/reports/testcases.xlsx
@@ -10,7 +10,7 @@
     <sheet name="#TEMP" sheetId="4" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'#TEMP'!$A$1:$D$108</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'#TEMP'!$A$1:$D$109</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="435" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="439" uniqueCount="138">
   <si>
     <t>接口</t>
   </si>
@@ -1422,6 +1422,66 @@
                 "macaddr": "10:82:3d:f4:32:a0",
                 "special_line": "0",
                 "proto": "dhcp"
+            }
+        ],
+        "lan": [
+            {
+                "macaddr": "10:82:3d:f4:32:9e",
+                "leasetime": "30",
+                "ipstart": "192.168.110.1",
+                "proto": "static",
+                "lastaddr": "192.168.110.1",
+                "ipaddr": "192.168.110.1",
+                "vlanid": "233",
+                "ignore": "0",
+                "netmask": "255.255.255.0",
+                "limit": "254",
+                "conflict": "false"
+            },
+            {
+                "macaddr": "10:82:3D:D5:20:54",
+                "leasetime": "480",
+                "ipstart": "192.168.12.1",
+                "lastaddr": "192.168.12.254",
+                "hasReturnRouter": false,
+                "ipaddr": "192.168.12.1",
+                "dhcpServerDevice": "",
+                "vlanid": "12",
+                "ignore": "0",
+                "netmask": "255.255.255.0",
+                "limit": "254",
+                "pool": "EGW",
+                "desc": "22ttttt''"
+            }
+        ],
+        "version": "1.0.0",
+        "wanNum": "1",
+        "lanNum": "2"
+    }
+}</t>
+  </si>
+  <si>
+    <t>{
+    "module": "network",
+    "noParse": false,
+    "remoteIp": false,
+    "device": "pc",
+    "async": null,
+    "data": {
+        "wan": [
+            {
+                "dnsType": "auto",
+                "proto": "pppoe",
+                "dns": "100.0.0.1",
+                "mtu": "1280",
+                "service": "1",
+                "vlanid": "",
+                "password": "xB3$Eavt",
+                "lcp_echo_interval": "30",
+                "lcp_echo_failure": "6",
+                "macaddr": "00:2D:12:45:85:26",
+                "username": "stefan@scoop",
+                "tag": "-1"
             }
         ],
         "lan": [
@@ -3296,7 +3356,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E108"/>
+  <dimension ref="A1:E109"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="39.95" customHeight="1" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="29.3796296296296" style="3" customWidth="1"/>
@@ -4410,10 +4470,10 @@
         <v>9</v>
       </c>
       <c r="B79" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C79" s="7" t="s">
         <v>101</v>
-      </c>
-      <c r="C79" s="7" t="s">
-        <v>102</v>
       </c>
       <c r="E79" s="6" t="s">
         <v>4</v>
@@ -4424,10 +4484,10 @@
         <v>9</v>
       </c>
       <c r="B80" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="C80" s="7" t="s">
         <v>103</v>
-      </c>
-      <c r="C80" s="7" t="s">
-        <v>104</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>4</v>
@@ -4438,7 +4498,7 @@
         <v>9</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>13</v>
+        <v>104</v>
       </c>
       <c r="C81" s="7" t="s">
         <v>105</v>
@@ -4578,23 +4638,23 @@
         <v>9</v>
       </c>
       <c r="B91" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C91" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="C91" s="7" t="s">
+      <c r="E91" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="92" customHeight="1" spans="1:5">
+      <c r="A92" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B92" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="E91" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="92" s="1" customFormat="1" customHeight="1" spans="1:5">
-      <c r="A92" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B92" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C92" s="8" t="s">
+      <c r="C92" s="7" t="s">
         <v>117</v>
       </c>
       <c r="E92" s="6" t="s">
@@ -4643,14 +4703,14 @@
         <v>4</v>
       </c>
     </row>
-    <row r="96" customHeight="1" spans="1:5">
-      <c r="A96" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B96" s="3" t="s">
+    <row r="96" s="1" customFormat="1" customHeight="1" spans="1:5">
+      <c r="A96" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B96" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C96" s="7" t="s">
+      <c r="C96" s="8" t="s">
         <v>121</v>
       </c>
       <c r="E96" s="6" t="s">
@@ -4665,7 +4725,7 @@
         <v>24</v>
       </c>
       <c r="C97" s="7" t="s">
-        <v>87</v>
+        <v>122</v>
       </c>
       <c r="E97" s="6" t="s">
         <v>4</v>
@@ -4679,7 +4739,7 @@
         <v>24</v>
       </c>
       <c r="C98" s="7" t="s">
-        <v>122</v>
+        <v>87</v>
       </c>
       <c r="E98" s="6" t="s">
         <v>4</v>
@@ -4743,39 +4803,38 @@
     </row>
     <row r="103" customHeight="1" spans="1:5">
       <c r="A103" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B103" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C103" s="7" t="s">
         <v>127</v>
       </c>
-      <c r="B103" s="3" t="s">
+      <c r="E103" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="104" customHeight="1" spans="1:5">
+      <c r="A104" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="C103" s="7" t="s">
+      <c r="B104" s="3" t="s">
         <v>129</v>
-      </c>
-      <c r="E103" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="104" s="2" customFormat="1" customHeight="1" spans="1:5">
-      <c r="A104" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="B104" s="3" t="s">
-        <v>128</v>
       </c>
       <c r="C104" s="7" t="s">
         <v>130</v>
       </c>
-      <c r="D104" s="3"/>
       <c r="E104" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="105" s="2" customFormat="1" customHeight="1" spans="1:5">
       <c r="A105" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C105" s="7" t="s">
         <v>131</v>
@@ -4787,54 +4846,69 @@
     </row>
     <row r="106" s="2" customFormat="1" customHeight="1" spans="1:5">
       <c r="A106" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B106" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="C106" s="7" t="s">
         <v>132</v>
-      </c>
-      <c r="C106" s="7" t="s">
-        <v>133</v>
       </c>
       <c r="D106" s="3"/>
       <c r="E106" s="6" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="107" customHeight="1" spans="1:5">
-      <c r="A107" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B107" s="2" t="s">
+    <row r="107" s="2" customFormat="1" customHeight="1" spans="1:5">
+      <c r="A107" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="B107" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="C107" s="7" t="s">
         <v>134</v>
       </c>
-      <c r="C107" s="10" t="s">
+      <c r="D107" s="3"/>
+      <c r="E107" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="108" customHeight="1" spans="1:5">
+      <c r="A108" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B108" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="D107" s="2"/>
-      <c r="E107" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="108" customHeight="1" spans="1:5">
-      <c r="A108" s="6" t="s">
+      <c r="C108" s="10" t="s">
         <v>136</v>
       </c>
-      <c r="B108" s="6" t="s">
-        <v>136</v>
-      </c>
-      <c r="C108" s="11" t="s">
-        <v>136</v>
-      </c>
-      <c r="D108" s="6" t="s">
-        <v>136</v>
-      </c>
+      <c r="D108" s="2"/>
       <c r="E108" s="6" t="s">
         <v>4</v>
       </c>
     </row>
+    <row r="109" customHeight="1" spans="1:5">
+      <c r="A109" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="B109" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="C109" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="D109" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="E109" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:D108" etc:filterBottomFollowUsedRange="0">
-    <sortState ref="A1:D108">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:D109" etc:filterBottomFollowUsedRange="0">
+    <sortState ref="A1:D109">
       <sortCondition ref="A1:A91" descending="1"/>
     </sortState>
     <extLst/>
